--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -47,26 +47,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,28 +143,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,51 +763,45 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>321.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>292.2</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>81.7</v>
+        <v>89.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="8" t="n">
-        <v>1564.4</v>
+        <v>152444.7</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.9</v>
+        <v>42.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N4" s="8" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n">
         <v>1.4</v>
       </c>
@@ -842,19 +809,19 @@
         <v>42.5</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="8" t="n">
-        <v>28.9</v>
+      <c r="X4" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>71</v>
+        <v>712.9</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>7.8</v>
@@ -875,26 +842,26 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E5" s="10" t="n">
+      <c r="D5" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>15.4</v>
+      <c r="G5" s="8" t="n">
+        <v>25.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.2</v>
+        <v>0.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.2</v>
@@ -902,45 +869,43 @@
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90</v>
+        <v>90.8</v>
       </c>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="n">
-        <v>2.4</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>8.6</v>
+        <v>840.5</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>20.9</v>
+        <v>26.9</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>80.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -956,19 +921,19 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>309.1</v>
-      </c>
-      <c r="D6" s="10" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>15</v>
+      <c r="F6" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -977,52 +942,52 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.1</v>
+        <v>12.1</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4</v>
+        <v>41.4</v>
       </c>
       <c r="M6" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>13.1</v>
+      <c r="N6" s="8" t="n">
+        <v>37.1</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>10.2</v>
+      <c r="P6" s="8" t="n">
+        <v>60.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="R6" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>15.8</v>
+        <v>5.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>15.3</v>
+        <v>454.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>95</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>0.9</v>
@@ -1043,45 +1008,45 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="G7" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>444.9</v>
+        <v>11.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="8" t="n">
-        <v>13.2</v>
+      <c r="L7" s="3" t="n">
+        <v>3.2</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>34.1</v>
+        <v>3.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99</v>
+        <v>99.2</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>19.3</v>
+        <v>114.3</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>16.8</v>
@@ -1090,10 +1055,10 @@
         <v>3.1</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>919</v>
+        <v>73990.89999999999</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>49.8</v>
+        <v>4.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>8.4</v>
@@ -1108,7 +1073,7 @@
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1126,53 +1091,53 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3.5</v>
+        <v>38.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>12.7</v>
+        <v>0.4</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>71.40000000000001</v>
+        <v>29.9</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>84.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>76</v>
@@ -1184,9 +1149,9 @@
         <v>18.7</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1209,68 +1174,64 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>91.90000000000001</v>
+        <v>149.7</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1289.5</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>213.9</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7.3</v>
+        <v>73.2</v>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
+        <v>13.5</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>7.7</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n">
-        <v>56.7</v>
+        <v>5.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>554.2</v>
+        <v>531.1</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>65.09999999999999</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>48421.2</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
+        <v>484912.4</v>
+      </c>
+      <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n">
-        <v>10.1</v>
+        <v>11.5</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>8.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>33.3</v>
+        <v>3.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95</v>
+        <v>935.9</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>46.8</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>414.5</v>
@@ -1294,31 +1255,34 @@
       <c r="C10" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D10" s="10" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="F10" s="10" t="n">
+      <c r="D10" s="9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+4244 3
+</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148 1
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
+      <c r="G10" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I10" s="3" t="n">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>9.1</v>
+        <v>2.4</v>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n">
-        <v>11.3</v>
+        <v>551.2</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>11</v>
@@ -1333,28 +1297,26 @@
         <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>20.3</v>
+        <v>2.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.1</v>
+        <v>17.7</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.1</v>
-      </c>
+        <v>26.7</v>
+      </c>
+      <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="n">
-        <v>19.8</v>
+        <v>29.9</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>18.2</v>
+        <v>431.2</v>
       </c>
       <c r="Y10" s="3" t="n">
         <v>82.90000000000001</v>
@@ -1374,72 +1336,87 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
-      </c>
-      <c r="D11" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>13</v>
+      <c r="E11" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
+        <v>16.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="I11" s="3" t="n">
-        <v>4.9</v>
+        <v>20.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
+        <v>6.9</v>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24242
+22
+144561919
+</t>
+        </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>23</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>266.3</v>
+        <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>17.1</v>
+        <v>12.1</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="T11" s="3" t="n">
-        <v>427.7</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>19.9</v>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6
+741
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>9.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X11" s="8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>660.1</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1455,41 +1432,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>25.9</v>
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>25.11</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>18.4</v>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>5.8</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>15.9</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>41.1</v>
-      </c>
+      <c r="L12" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>95</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.8</v>
@@ -1498,30 +1471,24 @@
         <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>15.5</v>
+        <v>25.5</v>
       </c>
       <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="n">
-        <v>21.3</v>
+        <v>22.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>14.7</v>
+        <v>43.5</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="Z12" s="3" t="n">
-        <v>2.2</v>
-      </c>
+      <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1538,72 +1505,74 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>44.4</v>
+      <c r="D13" s="11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19.4</v>
+        <v>4.9</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>191.6</v>
+        <v>11.2</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>44.1</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>4.6</v>
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>18.9</v>
+        <v>28.9</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>7.3</v>
+        <v>3.3</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>197</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="3" t="n"/>
+      <c r="V13" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="W13" s="3" t="n">
-        <v>17.7</v>
+        <v>27.7</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1619,40 +1588,38 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>10.5</v>
+        <v>27</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>12.3</v>
+      </c>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
+        <v>82.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>4.3</v>
+        <v>15.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>13</v>
+        <v>11.8</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.8</v>
+        <v>44.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
@@ -1664,27 +1631,29 @@
       <c r="R14" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="8" t="n">
-        <v>56.6</v>
+      <c r="S14" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>58</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="W14" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1700,76 +1669,74 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>639</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="10" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="F15" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>3.8</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>2.1</v>
+        <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>7.8</v>
+        <v>13.2</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>11.3</v>
+        <v>30.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>434.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>10.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>51.7</v>
+        <v>22.6</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>310.8</v>
+        <v>48</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>3</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1784,73 +1751,73 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>9994.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>128</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="G16" s="10" t="n">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+7656
+</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>466.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>39.5</v>
+        <v>3.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>3.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>139.8</v>
-      </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n">
-        <v>59.9</v>
-      </c>
+        <v>2.8</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n">
-        <v>58.2</v>
+        <v>12.3</v>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="n">
-        <v>489</v>
-      </c>
-      <c r="P16" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="n">
-        <v>1191.8</v>
+        <v>66.2</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.3</v>
+        <v>7.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>60.9</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="n">
-        <v>98.2</v>
+        <v>385.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.1</v>
+        <v>89.2</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>82.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>364</v>
+        <v>369.9</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1866,71 +1833,81 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>445.9</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E17" s="16" t="n">
+        <v>2224.9</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="9" t="n">
         <v>18.5</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>44.4</v>
       </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="8" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>44.8</v>
+      <c r="H17" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>2.2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>11.8</v>
+        <v>59.1</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>11.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>41.6</v>
+        <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>971.8</v>
+        <v>4839</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>151.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
+1
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+2
+</t>
+        </is>
       </c>
       <c r="T17" s="3" t="n">
-        <v>46.2</v>
+        <v>7.7</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>84.7</v>
+        <v>6.3</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>16.1</v>
+        <v>39.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>16.4</v>
+        <v>16.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>1.8</v>
@@ -1949,72 +1926,87 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.6</v>
-      </c>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>18.14</v>
+        <v>45.9</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>89.41</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>7.5</v>
+        <v>15</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+7648
+</t>
+        </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>29.4</v>
+        <v>23.2</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.3</v>
+        <v>0.3</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>102.2</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>56.5</v>
+        <v>11.8</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>99</v>
+        <v>97.8</v>
       </c>
       <c r="P18" s="3" t="n"/>
       <c r="Q18" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S18" s="8" t="n">
+      <c r="R18" s="8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v>17.9</v>
+        <v>456.2</v>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+224
+</t>
+        </is>
       </c>
       <c r="V18" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>22</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22254
+224
+1111
+</t>
+        </is>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>59</v>
+        <v>510.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2030,52 +2022,50 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.1</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>40.9</v>
+        <v>455.6</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>17.4</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>72.2</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M19" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>13</v>
+        <v>14.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>98</v>
+        <v>1132</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>18</v>
+        <v>25.4</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>89</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>64.2</v>
@@ -2084,19 +2074,19 @@
         <v>48.5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>3.2</v>
+        <v>5.4</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.6</v>
+        <v>14.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>6.6</v>
@@ -2115,71 +2105,78 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>531.1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>28</v>
+        <v>531.9</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>28.2</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>4.3</v>
+        <v>10.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>19.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="H20" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I20" s="8" t="n">
-        <v>33.5</v>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+2
+72
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" s="3" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="L20" s="3" t="n">
-        <v>0.2</v>
+        <v>11.2</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>28</v>
+        <v>28.2</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>51.3</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>22.4</v>
+        <v>17.2</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>221.1</v>
+        <v>22.2</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>19.9</v>
+        <v>17.8</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>44.4</v>
+        <v>21</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>7.6</v>
@@ -2197,69 +2194,73 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>28.2</v>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+3894
+</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>24.8</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>12.13</v>
+        <v>12.2</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2.1</v>
+        <v>6.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.4</v>
+        <v>3.5</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>3.1</v>
+        <v>0.2</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0.3</v>
+        <v>21.8</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>15.9</v>
+        <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>19.8</v>
+        <v>2.4</v>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v>393.8</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>48.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>20</v>
+        <v>19.2</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
@@ -2283,37 +2284,41 @@
       <c r="C22" s="3" t="n">
         <v>429</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="12" t="n">
-        <v>81.7</v>
+      <c r="D22" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.3</v>
+        <v>13.7</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>18</v>
+        <v>2.9</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>84.09999999999999</v>
+        <v>3.1</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>99.8</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
@@ -2328,25 +2333,25 @@
         <v>14.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X22" s="8" t="n">
-        <v>13.9</v>
+      <c r="W22" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>50.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>13.4</v>
+        <v>1239.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2362,72 +2367,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>945.4</v>
+        <v>232.3</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>561.1</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>94.40000000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>759.4</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>40.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N23" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="J23" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="n">
-        <v>293</v>
+        <v>99.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="3" t="n"/>
+      <c r="R23" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>2357.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>88.5</v>
+        <v>4.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>106.7</v>
+        <v>16.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>851.5</v>
+        <v>215.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>86.2</v>
+        <v>13.9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>341.5</v>
+        <v>34.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.5</v>
+        <v>60.9</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2443,48 +2452,52 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>464.1</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>81.90000000000001</v>
+        <v>46.4</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>18.9</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>8.1</v>
+        <v>40.5</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="K24" s="3" t="n"/>
+        <v>2.4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="L24" s="3" t="n">
-        <v>42.5</v>
+        <v>62.5</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="N24" s="3" t="n"/>
+        <v>61.8</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>493</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>63.1</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>17.6</v>
+        <v>88</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>15.6</v>
@@ -2492,22 +2505,24 @@
       <c r="T24" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="U24" s="8" t="n">
-        <v>177.4</v>
+      <c r="U24" s="3" t="n">
+        <v>88.5</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="X24" s="8" t="n">
-        <v>17.2</v>
+        <v>831.5</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>86.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
-      </c>
-      <c r="Z24" s="3" t="n"/>
+        <v>68.3</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>8.6</v>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2521,72 +2536,85 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>488.9</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>17.8</v>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4889
+49
+</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>7.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.6</v>
+        <v>114.7</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>8.1</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>14.9</v>
-      </c>
+        <v>29.1</v>
+      </c>
+      <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>42.5</v>
+        <v>425.5</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9.9</v>
+        <v>12.4</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>926</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>1.2</v>
+        <v>17.6</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>13.4</v>
+        <v>5.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>469.5</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W25" s="3" t="n"/>
+        <v>49.5</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>772.1</v>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">292575
+111979
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2122
+1
+1111919
+</t>
+        </is>
+      </c>
       <c r="X25" s="3" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>66</v>
+        <v>6.9</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>8.6</v>
@@ -2605,44 +2633,44 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>340.2</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F26" s="3" t="n">
+      <c r="E26" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>17</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="H26" s="8" t="n">
-        <v>1.6</v>
+      <c r="H26" s="3" t="n">
+        <v>57.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n">
-        <v>10.4</v>
+      <c r="L26" s="8" t="n">
+        <v>10.7</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>10.2</v>
+        <v>2.9</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
@@ -2657,22 +2685,22 @@
         <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>15.8</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>21.6</v>
+        <v>24.3</v>
       </c>
       <c r="W26" s="8" t="n">
-        <v>16.9</v>
+        <v>63.9</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>12.2</v>
+        <v>1.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2688,52 +2716,50 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>390.2</v>
-      </c>
-      <c r="D27" s="8" t="n">
+        <v>340.2</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="E27" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="F27" s="3" t="n">
+      <c r="E27" s="10" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F27" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>29.1</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>16.2</v>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="n">
-        <v>980.8</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>17.6</v>
+        <v>12.6</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>14.3</v>
@@ -2742,19 +2768,27 @@
         <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>18.5</v>
+        <v>21.6</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
+11737
+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78 277
+185
+</t>
+        </is>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>123</v>
+        <v>13</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2773,25 +2807,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>513.3</v>
+        <v>53.3</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>44.3</v>
+        <v>21.5</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>49.3</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>15.5</v>
+        <v>45.4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
@@ -2800,16 +2834,20 @@
         <v>5.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="N28" s="3" t="n">
-        <v>1.5</v>
+        <v>124.3</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+1554
+</t>
+        </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
@@ -2827,13 +2865,13 @@
         <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="8" t="n">
-        <v>16.7</v>
+      <c r="W28" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="X28" s="3" t="n">
         <v>17</v>
@@ -2858,23 +2896,21 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>593.3</v>
+        <v>53.3</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>8.1</v>
-      </c>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
@@ -2882,48 +2918,52 @@
         <v>6.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="8" t="n">
-        <v>790.9</v>
+        <v>1.4</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>19.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="3" t="n"/>
+      <c r="N29" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>96</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>27</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>472.8</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>8.1</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>15.5</v>
+        <v>17.3</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>16.7</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>11.2</v>
+        <v>21.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2939,43 +2979,43 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>91.7</v>
+        <v>284.8</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>522.7</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>67.8</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>79.09999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36.9</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
+        <v>19.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>57.2</v>
+        <v>5.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.9</v>
+        <v>5.7</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>32</v>
+        <v>4816.1</v>
       </c>
       <c r="P30" s="3" t="n"/>
       <c r="Q30" s="3" t="n">
@@ -2985,28 +3025,28 @@
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1.1</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>34484.5</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>551.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>99.5</v>
+        <v>29.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>17.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>83.2</v>
+        <v>23.2</v>
       </c>
       <c r="Y30" s="3" t="n">
         <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>35</v>
+        <v>35.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3022,32 +3062,32 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D31" s="16" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>10.9</v>
+        <v>451</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>19.3</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>26</v>
+        <v>12.8</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="n">
-        <v>11.9</v>
+        <v>1.3</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
@@ -3056,22 +3096,22 @@
         <v>0.3</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>4516.1</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
+      </c>
+      <c r="P31" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>22.6</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>11.1</v>
@@ -3080,16 +3120,16 @@
         <v>19.9</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>11.1</v>
+        <v>0.5</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>73</v>
+        <v>2.8</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3105,72 +3145,70 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G32" s="10" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>1.2</v>
-      </c>
+        <v>520.9</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>757.4</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>18</v>
-      </c>
+        <v>59.2</v>
+      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>11.9</v>
+        <v>1.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>11.2</v>
+        <v>16.2</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>24.8</v>
+        <v>26.1</v>
+      </c>
+      <c r="Q32" s="8" t="n">
+        <v>42.1</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>116.9</v>
+        <v>22.1</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.5</v>
+        <v>42.1</v>
       </c>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="X32" s="3" t="n"/>
+        <v>12.6</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>17.9</v>
+      </c>
       <c r="Y32" s="3" t="n">
         <v>70</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>71.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3186,76 +3224,74 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>520</v>
+        <v>3497.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>19.9</v>
+        <v>24.2</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>17.7</v>
+        <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>29.4</v>
+        <v>3.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>10.2</v>
-      </c>
+        <v>14.9</v>
+      </c>
+      <c r="M33" s="3" t="n"/>
       <c r="N33" s="3" t="n">
-        <v>12.3</v>
+        <v>16.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0.6</v>
+        <v>98.2</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>24.8</v>
+        <v>20.3</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>62.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>10.3</v>
+        <v>51</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>21.1</v>
+        <v>2.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>17.6</v>
+        <v>3.4</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>70</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3271,73 +3307,73 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>349.1</v>
-      </c>
-      <c r="D34" s="10" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F34" s="10" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="G34" s="10" t="n">
-        <v>11.4</v>
+      <c r="G34" s="3" t="n">
+        <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>65.59999999999999</v>
+        <v>4.1</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>12.3</v>
+        <v>4.3</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>16.6</v>
+        <v>16</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="N34" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>198</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>20.3</v>
+        <v>0.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0.2</v>
+        <v>78.7</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>19.9</v>
+        <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>10.3</v>
+        <v>2.6</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>18.7</v>
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>83</v>
+        <v>8582</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3356,77 +3392,75 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>329.9</v>
+        <v>56.7</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="E35" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>520.6</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="F35" s="12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>18.7</v>
-      </c>
       <c r="W35" s="3" t="n">
-        <v>16.8</v>
+        <v>846.3</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>81</v>
+        <v>278.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>68.5</v>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3441,76 +3475,76 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>506.7</v>
+        <v>53.5</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>19.8</v>
+        <v>26.3</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>39.8</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>4</v>
+        <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>9.5</v>
+        <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>13</v>
+        <v>26</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>12.9</v>
+        <v>10.5</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>19.8</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="P36" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q36" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="V36" s="3" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>6.2</v>
+        <v>14.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>16.8</v>
+        <v>434.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>68.5</v>
+        <v>9.9</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>212.2</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3526,72 +3560,101 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>535.5</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F37" s="16" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1188414042
+</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F37" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>46</v>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">614242
+149081
+</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+119019
+</t>
+        </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>3.9</v>
+        <v>14.7</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>10.6</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>422.7</v>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">714531 7
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P37" s="3" t="n">
-        <v>10.5</v>
+        <v>92</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753824
+9
+222
+11
+</t>
+        </is>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>25.5</v>
+        <v>111818.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>17.1</v>
+        <v>8.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>14.8</v>
+        <v>8.9</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>125</v>
+        <v>3169.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>4.3</v>
+        <v>541.3</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>154.6</v>
+        <v>19.2</v>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">646257
+121191
+</t>
+        </is>
       </c>
       <c r="X37" s="3" t="n">
-        <v>3.3</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>52.8</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>34.6</v>
+        <v>345.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3607,75 +3670,91 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D38" s="16" t="n">
+        <v>448.1</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>28.5</v>
       </c>
-      <c r="E38" s="16" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>99.7</v>
+      <c r="E38" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>94.7</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>46</v>
+        <v>67.59999999999999</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>69</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.1</v>
+        <v>28.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>20.8</v>
+        <v>52.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>431.7</v>
+        <v>5.5</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="O38" s="3" t="n">
-        <v>492</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>151.5</v>
+        <v>74.2</v>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+727227
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">753824
+9
+222
+11
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>115.5</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>88</v>
+        <v>17.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>216.4</v>
+        <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>0.9</v>
+        <v>12.3</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>84.7</v>
+        <v>83.2</v>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+92
+</t>
+        </is>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>359.5</v>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+        <v>24.9</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>345.6</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3690,73 +3769,82 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>4248.1</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>99.7</v>
+        <v>573.9</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>18.9</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>13.5</v>
+        <v>5.3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>42.1</v>
+        <v>7</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>13</v>
+        <v>0.2</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>431.7</v>
+        <v>22.7</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>14.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>151.5</v>
+        <v>2.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>73.09999999999999</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>216.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>10.9</v>
+        <v>78</v>
+      </c>
+      <c r="S39" s="3" t="n"/>
+      <c r="T39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81556
+15252197
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2227
+191
+</t>
+        </is>
       </c>
       <c r="V39" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>16.6</v>
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 28
+</t>
+        </is>
       </c>
       <c r="X39" s="3" t="n">
-        <v>84.7</v>
+        <v>12.5</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>741.9</v>
+        <v>6</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>5.5</v>
@@ -3775,77 +3863,80 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>42.2</v>
+        <v>35.7</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+4
+</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>71</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G40" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n">
-        <v>12.7</v>
+        <v>0.3</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>5.1</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 0
-</t>
-        </is>
+        <v>40.3</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>993.6</v>
+        <v>26.6</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>19.2</v>
+        <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>15.1</v>
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>198</v>
+        <v>63.5</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>212.1</v>
+        <v>13.7</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>88.3</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>76</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3861,76 +3952,80 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>451.2</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F41" s="10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <v>66.5</v>
+      <c r="G41" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.7</v>
+        <v>5.9</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>61.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>88.2</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>57.1</v>
+        <v>8.6</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>196</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.2</v>
+        <v>97.2</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R41" s="8" t="n">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>18.4</v>
+        <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>8</v>
+        <v>51.9</v>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2227
+191
+</t>
+        </is>
       </c>
       <c r="V41" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>16.8</v>
+        <v>22</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>17.5</v>
+        <v>0.4</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>7.2</v>
+        <v>214.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3946,76 +4041,86 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>451.2</v>
+        <v>5724.4</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>48.9</v>
+        <v>27.2</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2771
+28 1
+187
+215
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G42" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>2.2</v>
+      <c r="H42" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>88.5</v>
+        <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="N42" s="8" t="n">
-        <v>18.8</v>
+        <v>40.3</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>598</v>
+        <v>96</v>
       </c>
       <c r="P42" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>18</v>
-      </c>
       <c r="S42" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>55.9</v>
+        <v>18.4</v>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">432
+5
+</t>
+        </is>
       </c>
       <c r="U42" s="3" t="n">
-        <v>12.4</v>
+        <v>19.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
-        <v>89.3</v>
+        <v>161.3</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>88.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>839</v>
+        <v>58.9</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>18.4</v>
+        <v>7.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4031,69 +4136,96 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>524.4</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
+        <v>6666844.6</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>242.2</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>12.8</v>
+      </c>
       <c r="I43" s="3" t="n">
-        <v>13.9</v>
+        <v>3.6</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>5.7</v>
+        <v>0.2</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>43.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717774
+82
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24127
+8
+242257
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1859957
+5
+13 2
+529
+</t>
+        </is>
       </c>
       <c r="O43" s="3" t="n">
-        <v>96</v>
+        <v>0.7</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>23.9</v>
+        <v>2.6</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S43" s="3" t="n"/>
+        <v>12.4</v>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42529
+21222
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="V43" s="3" t="n">
-        <v>22</v>
+        <v>7.7</v>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v>2222.4</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="X43" s="3" t="n"/>
+        <v>161.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>58.9</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>35.2</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4107,55 +4239,88 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
-      <c r="D44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="C44" s="3" t="n">
+        <v>5724.4</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2771
+28 1
+187
+215
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+0
+2644
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n">
-        <v>43.4</v>
+        <v>3.9</v>
       </c>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="n"/>
+        <v>27.1</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="n">
-        <v>23.1</v>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+21
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.5</v>
+        <v>96</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>2.6</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2424622
+2224
+</t>
+        </is>
       </c>
       <c r="R44" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S44" s="3" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="T44" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="U44" s="3" t="n"/>
+        <v>2169.4</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>59.9</v>
+      </c>
       <c r="V44" s="3" t="n">
-        <v>1.1</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="X44" s="3" t="n"/>
+      <c r="X44" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4171,68 +4336,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>16110.9</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="E45" s="16" t="n">
+        <v>10197.9</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="3" t="n">
         <v>41.8</v>
       </c>
-      <c r="F45" s="16" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G45" s="10" t="n">
+      <c r="F45" s="3" t="n">
+        <v>754.6</v>
+      </c>
+      <c r="G45" s="3" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>56.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.4</v>
+        <v>14.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>221.9</v>
+        <v>101.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L45" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>22.9</v>
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>18.1</v>
+        <v>11.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>388</v>
+        <v>38</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>66</v>
+      <c r="R45" s="3" t="n"/>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42529
+21222
+</t>
+        </is>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.4</v>
+        <v>54.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>22222.4</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>21.3</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
+      <c r="Y45" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4248,15 +4419,19 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>477.8</v>
-      </c>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="16" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F46" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
@@ -4265,55 +4440,55 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>221.9</v>
+        <v>52.1</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>11.9</v>
+        <v>1</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>22.9</v>
+        <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>51.7</v>
+        <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>98.59999999999999</v>
+        <v>24.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>71</v>
+        <v>17.7</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>54.9</v>
+        <v>2169.4</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114 70
+          <t xml:space="preserve">197 1
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="3" t="n"/>
+      <c r="W46" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>11.1</v>
+        <v>19.5</v>
       </c>
       <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -47,14 +47,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,16 +152,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -763,68 +793,76 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>292.2</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="E4" s="3" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="10" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>89.7</v>
+      <c r="G4" s="11" t="n">
+        <v>18.2</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="I4" s="8" t="n">
-        <v>152444.7</v>
+      <c r="I4" s="3" t="n">
+        <v>3.5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>42.9</v>
+        <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="O4" s="3" t="n"/>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N4" s="16" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P4" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q4" s="16" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="S4" s="16" t="n">
+        <v>114.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
+        <v>542.5</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="W4" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="V4" s="16" t="n">
+        <v>2219.1</v>
+      </c>
+      <c r="W4" s="16" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>18.9</v>
+        <v>41.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>712.9</v>
+        <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>0.1</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -842,70 +880,68 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>25.4</v>
+      <c r="D5" s="10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.2</v>
+        <v>17.9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1</v>
+        <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L5" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M5" s="3" t="n"/>
+      <c r="L5" s="16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>190.8</v>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="16" t="n">
+        <v>19.6</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>840.5</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>26.9</v>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="S5" s="16" t="n">
+        <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>19.5</v>
+        <v>91</v>
+      </c>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="16" t="n">
+        <v>189.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.3</v>
+        <v>2.1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>8.5</v>
+        <v>180.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -921,76 +957,70 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="D6" s="3" t="n">
+        <v>309.1</v>
+      </c>
+      <c r="D6" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>18.9</v>
+      <c r="F6" s="10" t="n">
+        <v>18.4</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>12.1</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>37.1</v>
+        <v>1.4</v>
+      </c>
+      <c r="M6" s="16" t="n">
+        <v>411</v>
+      </c>
+      <c r="N6" s="16" t="n">
+        <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P6" s="8" t="n">
-        <v>60.2</v>
+        <v>199</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>16.3</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="R6" s="16" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>5.2</v>
+        <v>92</v>
+      </c>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="16" t="n">
+        <v>715.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>454.3</v>
+        <v>114.3</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>95.90000000000001</v>
+        <v>195</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.9</v>
+        <v>10.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1006,74 +1036,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>275.8</v>
-      </c>
-      <c r="D7" s="3" t="n">
+        <v>1275.8</v>
+      </c>
+      <c r="D7" s="10" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>9</v>
+      <c r="E7" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>98</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>11.9</v>
+        <v>444.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" s="3" t="n"/>
+        <v>11.2</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>45</v>
+        <v>1.3</v>
+      </c>
+      <c r="M7" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>99.2</v>
+        <v>198</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>6.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>114.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="R7" s="16" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.1</v>
+        <v>43.3</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>73990.89999999999</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>4.8</v>
+        <v>79</v>
+      </c>
+      <c r="U7" s="16" t="n">
+        <v>94.8</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>16.8</v>
+        <v>46.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.9</v>
+        <v>131.3</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>81</v>
+        <v>814.9</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>14.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1091,74 +1123,72 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0.1</v>
+      <c r="D8" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>38.5</v>
+        <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>424.4</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>78</v>
+        <v>1718</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>29.9</v>
+        <v>10.9</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>27.4</v>
+        <v>0.2</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>84.5</v>
+        <v>0.8</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
+      </c>
+      <c r="W8" s="16" t="n">
+        <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>18.9</v>
+        <v>2.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>87</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1174,70 +1204,76 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>149.7</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>1289.5</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>213.9</v>
+        <v>1749.7</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>91.90000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>73.90000000000001</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1702.6</v>
+      </c>
       <c r="I9" s="3" t="n">
-        <v>13.5</v>
+        <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K9" s="3" t="n"/>
+        <v>13.3</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>17.7</v>
+      </c>
       <c r="L9" s="3" t="n">
-        <v>5.7</v>
+        <v>56.4</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>531.1</v>
+        <v>551.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>484912.4</v>
-      </c>
-      <c r="P9" s="3" t="n"/>
+        <v>1484.8</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>11.5</v>
+        <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>85.3</v>
+        <v>185.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.5</v>
+        <v>188.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>3.3</v>
+        <v>1233.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>935.9</v>
+        <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>184.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>46.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>14154.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>19.8</v>
+        <v>119.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1255,73 +1291,73 @@
       <c r="C10" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-4244 3
-</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
+      <c r="D10" s="10" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="3" t="n">
-        <v>2.9</v>
+      <c r="G10" s="10" t="n">
+        <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7</v>
+        <v>8.1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>551.2</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>11</v>
+        <v>20.4</v>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="16" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>111</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
+        <v>196.8</v>
+      </c>
+      <c r="P10" s="16" t="n">
+        <v>1.5</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>2.3</v>
+        <v>20.3</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>0.2</v>
+        <v>17.9</v>
+      </c>
+      <c r="S10" s="16" t="n">
+        <v>12.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="U10" s="3" t="n"/>
+        <v>14167.1</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>6.7</v>
+      </c>
       <c r="V10" s="3" t="n">
-        <v>29.9</v>
+        <v>19</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>431.2</v>
+      <c r="X10" s="16" t="n">
+        <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+        <v>182.9</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>151</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1336,87 +1372,66 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>1509.3</v>
+      </c>
+      <c r="D11" s="10" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="10" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="F11" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="16" t="n">
         <v>4.2</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24242
-22
-144561919
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-1
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>26.3</v>
+      <c r="Q11" s="16" t="n">
+        <v>226.3</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>12.1</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-741
-</t>
-        </is>
+        <v>1.4</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>40.1</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="V11" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V11" s="16" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>17.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>660.1</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>9.9</v>
+        <v>19</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1432,63 +1447,77 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>25.11</v>
+        <v>1306.7</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>25.9</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>15</v>
+        <v>10.9</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>14.5</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="I12" s="3" t="n"/>
+      <c r="I12" s="16" t="n">
+        <v>94.8</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="M12" s="3" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="16" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M12" s="16" t="n">
+        <v>21.9</v>
+      </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.90000000000001</v>
+        <v>195</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.8</v>
+        <v>10.8</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n"/>
-      <c r="U12" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="S12" s="16" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="V12" s="3" t="n">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>43.5</v>
+        <v>4.3</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+        <v>1092</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1503,76 +1532,66 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>357.9</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>18.3</v>
+        <v>1357.9</v>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="11" t="n">
+        <v>18.13</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="H13" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K13" s="3" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>13.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="16" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>28.9</v>
-      </c>
+        <v>10.9</v>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
       <c r="R13" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>83.90000000000001</v>
+        <v>4.3</v>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>18.1</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
+      </c>
+      <c r="W13" s="16" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="X13" s="16" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>84</v>
+        <v>184</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>1.6</v>
+        <v>9.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1588,72 +1607,70 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>11.8</v>
+        <v>227</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>18.13</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="16" t="n">
+        <v>1182</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>44.8</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="n">
+      <c r="P14" s="16" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="Q14" s="16" t="n">
         <v>14.9</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>90.40000000000001</v>
-      </c>
+      <c r="R14" s="16" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S14" s="16" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>1.5</v>
+        <v>10.6</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="W14" s="3" t="n">
-        <v>1.2</v>
+      <c r="W14" s="16" t="n">
+        <v>11.5</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>95</v>
+        <v>195</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.2</v>
+        <v>81811</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1669,74 +1686,74 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>639</v>
-      </c>
-      <c r="D15" s="11" t="n">
+        <v>1631</v>
+      </c>
+      <c r="D15" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="10" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>372.1</v>
-      </c>
-      <c r="I15" s="3" t="n"/>
+      <c r="E15" s="11" t="n">
+        <v>1011.08</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>30.1</v>
+      <c r="L15" s="16" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M15" s="16" t="n">
+        <v>21.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>13.3</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="P15" s="16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q15" s="16" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>22.6</v>
+        <v>0.6</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>48</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>3</v>
+        <v>17.9</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>16.5</v>
+        <v>12</v>
+      </c>
+      <c r="W15" s="16" t="n">
+        <v>116.5</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1751,73 +1768,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-7656
-</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>466.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>2.5</v>
+      <c r="C16" s="3" t="n">
+        <v>2227.1</v>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>92.3</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>71.2</v>
+        <v>79.2</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.5</v>
+        <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.8</v>
+        <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.8</v>
+        <v>121.8</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L16" s="3" t="n"/>
+        <v>39.8</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>59.1</v>
+      </c>
       <c r="M16" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>58.2</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>67.90000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P16" s="3" t="n"/>
+        <v>439.8</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="Q16" s="3" t="n">
-        <v>66.2</v>
+        <v>11191</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>82.2</v>
+        <v>0.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>7.7</v>
+        <v>721.1</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="U16" s="3" t="n"/>
+        <v>310.1</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>160.9</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>385.2</v>
+        <v>921.2</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>89.2</v>
+        <v>801.9</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>182.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369.9</v>
+        <v>1364</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1833,84 +1854,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2224.9</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>44.4</v>
+        <v>245.9</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>14.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>3.9</v>
+        <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>59.1</v>
+        <v>29.4</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
+      <c r="L17" s="16" t="n">
+        <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="N17" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N17" s="16" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>4839</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>6.7</v>
+        <v>197.8</v>
+      </c>
+      <c r="P17" s="16" t="n">
+        <v>7.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-1
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-2
-</t>
-        </is>
+        <v>22.2</v>
+      </c>
+      <c r="R17" s="16" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="16" t="n">
+        <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>7.7</v>
+        <v>162</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>16.7</v>
+        <v>19.2</v>
+      </c>
+      <c r="V17" s="16" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="W17" s="16" t="n">
+        <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>16.9</v>
+        <v>14.4</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>2.8</v>
+        <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+        <v>16.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1926,87 +1937,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>1435.8</v>
+      </c>
+      <c r="D18" s="10" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>20.9</v>
+      <c r="E18" s="10" t="n">
+        <v>24.44</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>89.41</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-7648
-</t>
-        </is>
-      </c>
+        <v>25.2</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="n">
-        <v>23.2</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>11.8</v>
+        <v>0.4</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>16.5</v>
+        <v>87.59999999999999</v>
+      </c>
+      <c r="N18" s="16" t="n">
+        <v>61</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="P18" s="3" t="n"/>
+        <v>99</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="Q18" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="8" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>15.4</v>
+      <c r="R18" s="16" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="S18" s="16" t="n">
+        <v>115.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>456.2</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1238
-224
-</t>
-        </is>
+        <v>1406</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W18" s="8" t="n">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22254
-224
-1111
-</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X18" s="16" t="n">
+        <v>15.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>510.1</v>
+        <v>13791</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.4</v>
+        <v>110.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2022,74 +2020,72 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>455.6</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>1531.1</v>
+      </c>
+      <c r="D19" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F19" s="3" t="n">
+      <c r="E19" s="10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F19" s="10" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J19" s="3" t="n"/>
+        <v>3.3</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>32.9</v>
+        <v>10</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>211</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <v>711</v>
+      </c>
+      <c r="N19" s="16" t="n">
+        <v>13</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>1132</v>
+        <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>8.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>89</v>
+        <v>261.1</v>
+      </c>
+      <c r="R19" s="16" t="n">
+        <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>64.2</v>
+        <v>24.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>48.5</v>
+        <v>0.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>17.9</v>
+        <v>0.3</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>14.6</v>
+        <v>21.2</v>
+      </c>
+      <c r="X19" s="16" t="n">
+        <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>142</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>6.6</v>
+        <v>16.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2105,82 +2101,69 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>531.9</v>
-      </c>
-      <c r="D20" s="11" t="n">
+        <v>592.2</v>
+      </c>
+      <c r="D20" s="10" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="E20" s="11" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="G20" s="16" t="n">
         <v>17.8</v>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54
-2
-72
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.3</v>
+      <c r="H20" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>733.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="M20" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>43</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <v>8818.1</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>51.3</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="16" t="n">
+        <v>151.3</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>42.5</v>
+        <v>140.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>17.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="16" t="n">
+        <v>2298.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="Z20" s="3" t="n">
-        <v>7.6</v>
-      </c>
+      <c r="Z20" s="3" t="inlineStr"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2194,79 +2177,75 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-3894
-</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="n">
+      <c r="C21" s="3" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="D21" s="10" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>12.7</v>
+      <c r="E21" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6.9</v>
+        <v>42.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>3.5</v>
+        <v>12.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.1</v>
+        <v>0.3</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.2</v>
+        <v>13.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>14.9</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
       <c r="O21" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S21" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>1931</v>
+      </c>
+      <c r="U21" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v>393.8</v>
+      <c r="V21" s="16" t="n">
+        <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>18.2</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2282,76 +2261,72 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>1429</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="8" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>18.7</v>
+      <c r="E22" s="14" t="inlineStr"/>
+      <c r="F22" s="11" t="n">
+        <v>81.90000000000001</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>18.3</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>2.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="K22" s="16" t="n">
+        <v>8</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N22" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M22" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N22" s="16" t="n">
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99.8</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="16" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>14.9</v>
+      <c r="S22" s="16" t="n">
+        <v>194.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>4.9</v>
+        <v>443454.4</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="V22" s="16" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>20</v>
+      <c r="W22" s="16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X22" s="16" t="n">
+        <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>5.5</v>
+        <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1239.4</v>
+        <v>113.4</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2367,76 +2342,72 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>232.3</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>561.1</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>759.4</v>
+        <v>23203.1</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>551.4</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>75.09999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
+        <v>141.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>12.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.3</v>
+        <v>101.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>12.3</v>
+        <v>1.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>14.5</v>
-      </c>
+        <v>61.8</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>2493</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>128.9</v>
+        <v>1128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.2</v>
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2357.1</v>
+        <v>235.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>4.2</v>
+        <v>188.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>16.7</v>
+        <v>1106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>215.6</v>
+        <v>185.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>13.9</v>
+        <v>26.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>34.5</v>
+        <v>1341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>60.9</v>
+        <v>141</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2452,76 +2423,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>484.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="10" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>40.5</v>
+        <v>18.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.5</v>
+        <v>29.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>76.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="M24" s="16" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>493</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>63.1</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="S24" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="R24" s="16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S24" s="16" t="n">
         <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>88.5</v>
+        <v>1247.9</v>
+      </c>
+      <c r="U24" s="16" t="n">
+        <v>197.5</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>21.3</v>
+        <v>91.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>831.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>86.2</v>
+        <v>41.1</v>
+      </c>
+      <c r="X24" s="16" t="n">
+        <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.3</v>
+        <v>168.9</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2536,88 +2503,65 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4889
-49
-</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>114.7</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="I25" s="3" t="n">
+      <c r="C25" s="3" t="n">
+        <v>1488.9</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="L25" s="16" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Q25" s="16" t="n">
         <v>29.1</v>
       </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>425.5</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>24.7</v>
-      </c>
       <c r="R25" s="3" t="n">
-        <v>17.6</v>
+        <v>0.7</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>772.1</v>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292575
-111979
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2122
-1
-1111919
-</t>
-        </is>
+        <v>549.3</v>
+      </c>
+      <c r="U25" s="16" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="W25" s="16" t="n">
+        <v>16.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>6.9</v>
+        <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>8.6</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2633,74 +2577,70 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>340.2</v>
+        <v>1349.9</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>25.9</v>
+        <v>24.9</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>17</v>
+        <v>1.2</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>3.7</v>
+        <v>16.6</v>
+      </c>
+      <c r="I26" s="16" t="n">
+        <v>25.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="8" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>18.3</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="P26" s="3" t="inlineStr"/>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="16" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="3" t="n">
-        <v>15.7</v>
+      <c r="S26" s="16" t="n">
+        <v>547.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>63.5</v>
+        <v>163.5</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>15.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="W26" s="8" t="n">
-        <v>63.9</v>
+        <v>21.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>1.8</v>
+        <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>55</v>
+        <v>512.1</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>1.1</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2718,77 +2658,63 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>6.6</v>
-      </c>
+      <c r="D27" s="11" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="11" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>29.1</v>
+        <v>2</v>
+      </c>
+      <c r="J27" s="16" t="n">
+        <v>15.1</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N27" s="3" t="n"/>
+        <v>42.4</v>
+      </c>
+      <c r="M27" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P27" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>16.2</v>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="16" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="R27" s="16" t="n">
+        <v>161.8</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>14.3</v>
+        <v>11.7</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-11737
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78 277
-185
-</t>
-        </is>
+        <v>17.4</v>
+      </c>
+      <c r="W27" s="16" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="X27" s="16" t="n">
+        <v>187.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>0.6</v>
@@ -2807,25 +2733,25 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>53.3</v>
+        <v>15139.5</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>21.5</v>
+        <v>27</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>11.15</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>45.4</v>
+        <v>4.1</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.4</v>
+        <v>18.7</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.2</v>
+        <v>0.2</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
@@ -2833,51 +2759,43 @@
       <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="3" t="n">
-        <v>124.3</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1229
-1554
-</t>
-        </is>
+      <c r="L28" s="16" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="M28" s="16" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="N28" s="16" t="n">
+        <v>13.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.2</v>
+        <v>10.2</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S28" s="3" t="n">
-        <v>19</v>
+      <c r="R28" s="16" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>99</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>17</v>
-      </c>
+      <c r="W28" s="3" t="inlineStr"/>
+      <c r="X28" s="3" t="inlineStr"/>
       <c r="Y28" s="3" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.8</v>
@@ -2896,74 +2814,70 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>2.1</v>
+        <v>523.3</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>12.1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
+        <v>4.4</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.3</v>
+      </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.2</v>
+        <v>16.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N29" s="3" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
+      </c>
+      <c r="M29" s="16" t="n">
+        <v>910.5</v>
+      </c>
+      <c r="N29" s="16" t="n">
+        <v>122.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q29" s="16" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>12</v>
+      <c r="R29" s="16" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>472.8</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>8.1</v>
-      </c>
+        <v>47.8</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr"/>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X29" s="3" t="n">
-        <v>16.7</v>
-      </c>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
       <c r="Y29" s="3" t="n">
-        <v>6</v>
+        <v>160</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>21.2</v>
+        <v>111.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2979,45 +2893,47 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>284.8</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>322.6</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>522.7</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>67.8</v>
+        <v>22848.1</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>131.2</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>21.7</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>29.1</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36.9</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>3.8</v>
+        <v>113.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>19.5</v>
+        <v>1119.5</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>13.5</v>
+        <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>5.2</v>
+        <v>52.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>5.7</v>
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>4816.1</v>
-      </c>
-      <c r="P30" s="3" t="n"/>
+        <v>1489</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" s="3" t="n">
         <v>113.2</v>
       </c>
@@ -3025,28 +2941,28 @@
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>184.4</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.4</v>
+        <v>55.9</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>29.5</v>
+        <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>181.9</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>23.2</v>
+        <v>83.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>365</v>
+        <v>1365</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>35.9</v>
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3062,74 +2978,70 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>451</v>
-      </c>
-      <c r="D31" s="9" t="n">
+        <v>1452</v>
+      </c>
+      <c r="D31" s="10" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="10" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="11" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G31" s="3" t="n">
+      <c r="F31" s="10" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G31" s="10" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="I31" s="3" t="inlineStr"/>
       <c r="J31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>1.3</v>
+        <v>39.1</v>
+      </c>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="16" t="n">
+        <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>0.3</v>
-      </c>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>97.8</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <v>40.4</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>69.09999999999999</v>
+      <c r="R31" s="16" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="U31" s="16" t="n">
         <v>11.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="16" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>0.5</v>
+      <c r="X31" s="16" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2.8</v>
+        <v>730</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>0.2</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3145,71 +3057,71 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>520.9</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>757.4</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+        <v>520.8</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="I32" s="3" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n">
-        <v>1.5</v>
+        <v>61.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L32" s="16" t="n">
+        <v>1090.5</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>12.2</v>
-      </c>
+        <v>103.3</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
-        <v>97</v>
+        <v>97.8</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>22.1</v>
+        <v>10.6</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="R32" s="16" t="n">
+        <v>18.2</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n">
-        <v>21.1</v>
+        <v>162.5</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="16" t="n">
+        <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>17.9</v>
+        <v>18.5</v>
+      </c>
+      <c r="X32" s="16" t="n">
+        <v>27.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3224,74 +3136,64 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>3497.1</v>
+        <v>349.1</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>11.4</v>
+        <v>28.8</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>211.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>6.8</v>
-      </c>
+      <c r="K33" s="3" t="inlineStr"/>
       <c r="L33" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n">
-        <v>16.1</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
       <c r="O33" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>9.1</v>
+        <v>98.8</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="Q33" s="3" t="n">
-        <v>20.3</v>
+        <v>204.3</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="S33" s="3" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="S33" s="16" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>79.90000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="V33" s="3" t="inlineStr"/>
       <c r="W33" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>18.7</v>
-      </c>
+        <v>44.4</v>
+      </c>
+      <c r="X33" s="3" t="inlineStr"/>
       <c r="Y33" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>189</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3307,76 +3209,72 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>18.5</v>
+      <c r="E34" s="11" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>19</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>4.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L34" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L34" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>29.1</v>
-      </c>
+      <c r="M34" s="16" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N34" s="3" t="inlineStr"/>
       <c r="O34" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q34" s="16" t="n">
+        <v>21.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
+      </c>
+      <c r="S34" s="16" t="n">
+        <v>181.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>72</v>
+        <v>72.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V34" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="W34" s="3" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="V34" s="16" t="n">
+        <v>1287.1</v>
+      </c>
+      <c r="W34" s="16" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>18</v>
-      </c>
+      <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="n">
-        <v>8582</v>
+        <v>893</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3392,19 +3290,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>56.7</v>
+        <v>1506.7</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>4</v>
+        <v>23.1</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>15.4</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>9.5</v>
@@ -3413,54 +3311,52 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
+        <v>51.5</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="3" t="n">
+      <c r="M35" s="16" t="n">
         <v>12.9</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>48.1</v>
-      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>2.6</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>17.6</v>
+      <c r="R35" s="16" t="n">
+        <v>147.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>520.6</v>
-      </c>
-      <c r="U35" s="3" t="n">
+        <v>572</v>
+      </c>
+      <c r="U35" s="16" t="n">
         <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="W35" s="3" t="n">
-        <v>846.3</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>278.7</v>
+        <v>20.8</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X35" s="16" t="n">
+        <v>4116.8</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>68.5</v>
       </c>
-      <c r="Z35" s="3" t="n"/>
+      <c r="Z35" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3475,18 +3371,18 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F36" s="8" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>535.5</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="G36" s="16" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3499,52 +3395,50 @@
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>12.6</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L36" s="16" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="M36" s="16" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>29.4</v>
+        <v>18.1</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="R36" s="3" t="n">
-        <v>17.1</v>
+        <v>25.5</v>
+      </c>
+      <c r="R36" s="16" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>0.2</v>
+        <v>685</v>
+      </c>
+      <c r="U36" s="16" t="n">
+        <v>27.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>434.3</v>
+      <c r="W36" s="16" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X36" s="16" t="n">
+        <v>13.8</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>9.9</v>
+        <v>12</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>2.2</v>
+        <v>1110.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3560,101 +3454,72 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-1188414042
-</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">614242
-149081
-</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-119019
-</t>
-        </is>
+        <v>2240.4</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>991.7</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>146</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.7</v>
+        <v>116.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1.8</v>
+        <v>81.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>422.7</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">714531 7
-</t>
-        </is>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
       <c r="O37" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
-        </is>
+        <v>2492</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>111818.5</v>
+        <v>115.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>8.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>8.9</v>
+        <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>3169.4</v>
+        <v>216.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>541.3</v>
+        <v>54.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="W37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">646257
-121191
-</t>
-        </is>
+        <v>1100.9</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>183.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>84.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>345.6</v>
+        <v>394.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3670,90 +3535,68 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>69</v>
+        <v>2448.1</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-727227
-</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
-        </is>
+      <c r="J38" s="16" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="M38" s="16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
+      <c r="O38" s="3" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="S38" s="3" t="n">
-        <v>17.6</v>
-      </c>
+        <v>23.1</v>
+      </c>
+      <c r="R38" s="3" t="inlineStr"/>
+      <c r="S38" s="3" t="inlineStr"/>
       <c r="T38" s="3" t="n">
         <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>12.3</v>
+        <v>424.3</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-92
-</t>
-        </is>
+        <v>20.2</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X38" s="16" t="n">
+        <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>24.9</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>345.6</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3769,85 +3612,64 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>573.9</v>
+        <v>3599.9</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>12.2</v>
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1118</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="L39" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr"/>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>92</v>
+        <v>1980.8</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.1</v>
+        <v>18.4</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>26.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="S39" s="3" t="n"/>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81556
-15252197
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2227
-191
-</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>1720</v>
+      </c>
+      <c r="U39" s="16" t="n">
+        <v>18</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 28
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>12.5</v>
+        <v>21.2</v>
+      </c>
+      <c r="W39" s="16" t="n">
+        <v>8151.7</v>
+      </c>
+      <c r="X39" s="16" t="n">
+        <v>119.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3863,77 +3685,67 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-4
-</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="F40" s="3" t="n">
+        <v>335.1</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F40" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>15.9</v>
+      <c r="G40" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>5.9</v>
+        <v>17.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>14.1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M40" s="16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>198</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>26.6</v>
+        <v>1</v>
+      </c>
+      <c r="Q40" s="16" t="n">
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>18.4</v>
+      <c r="S40" s="16" t="n">
+        <v>18.5</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>63.5</v>
+        <v>69.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="W40" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="16" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>88.3</v>
+      <c r="X40" s="16" t="n">
+        <v>199.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>76</v>
+        <v>983</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>7.2</v>
@@ -3952,80 +3764,66 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>5.2</v>
+        <v>245451.2</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="E41" s="8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>18.9</v>
+      <c r="E41" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>128.13</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>5.9</v>
+        <v>19.8</v>
+      </c>
+      <c r="H41" s="16" t="n">
+        <v>51</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J41" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>88.2</v>
+        <v>818.5</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>97.2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="P41" s="3" t="inlineStr"/>
       <c r="Q41" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S41" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2227
-191
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>22</v>
+        <v>23.9</v>
+      </c>
+      <c r="R41" s="16" t="n">
+        <v>717.9</v>
+      </c>
+      <c r="S41" s="16" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="16" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V41" s="16" t="n">
+        <v>222</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="3" t="inlineStr"/>
       <c r="Y41" s="3" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>214.2</v>
+        <v>121.2</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4041,87 +3839,67 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5724.4</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
-</t>
-        </is>
+        <v>524.4</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="11" t="n">
+        <v>60.1</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>12.8</v>
+        <v>19.3</v>
+      </c>
+      <c r="G42" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="J42" s="3" t="n">
-        <v>5.7</v>
-      </c>
+      <c r="J42" s="3" t="inlineStr"/>
       <c r="K42" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" s="16" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.3</v>
+        <v>2.2</v>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>13.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>23.9</v>
+        <v>26.6</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">432
-5
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>543.5</v>
+      </c>
+      <c r="U42" s="16" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="16" t="n">
         <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>161.3</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>7.2</v>
-      </c>
+      <c r="X42" s="3" t="inlineStr"/>
+      <c r="Y42" s="3" t="inlineStr"/>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4135,97 +3913,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n">
-        <v>6666844.6</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>242.2</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717774
-82
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24127
-8
-242257
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1859957
-5
-13 2
-529
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42529
-21222
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>2222.4</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W43" s="3" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y43" s="3" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="Z43" s="3" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="C43" s="3" t="inlineStr"/>
+      <c r="D43" s="3" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4239,89 +3950,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>5724.4</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-0
-2644
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-21
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424622
-2224
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>2169.4</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4336,75 +3988,71 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>10197.9</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>754.6</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>1911.2</v>
+      </c>
+      <c r="D45" s="15" t="inlineStr"/>
+      <c r="E45" s="15" t="inlineStr"/>
+      <c r="F45" s="17" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>56.8</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>14.9</v>
+        <v>454.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>101.9</v>
+        <v>121.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>11.1</v>
+        <v>51.2</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>38</v>
+        <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42529
-21222
-</t>
-        </is>
+        <v>198.6</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>166</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>54.7</v>
+        <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>22222.4</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.3</v>
+        <v>831.4</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X45" s="3" t="n"/>
+        <v>168.3</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+        <v>8263</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>331.8</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4418,23 +4066,21 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="D46" s="3" t="n">
+      <c r="C46" s="3" t="inlineStr"/>
+      <c r="D46" s="10" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F46" s="3" t="n">
+      <c r="E46" s="10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F46" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="3" t="n">
+      <c r="G46" s="10" t="n">
         <v>16.9</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>6.7</v>
+      <c r="H46" s="16" t="n">
+        <v>19.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>36.1</v>
@@ -4442,53 +4088,46 @@
       <c r="J46" s="3" t="n">
         <v>52.1</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="3" t="n">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="16" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M46" s="16" t="n">
         <v>10.7</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>12.8</v>
+        <v>4.8</v>
       </c>
       <c r="O46" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>24.2</v>
+        <v>6</v>
+      </c>
+      <c r="Q46" s="16" t="n">
+        <v>29.7</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>2169.4</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197 1
-</t>
-        </is>
-      </c>
+        <v>17.8</v>
+      </c>
+      <c r="S46" s="16" t="n">
+        <v>2261.5</v>
+      </c>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="W46" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>1680.1</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,18 +55,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,34 +146,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -793,22 +787,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="D4" s="10" t="n">
+        <v>3012.1</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>27.8</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="11" t="n">
-        <v>18.2</v>
+      <c r="G4" s="8" t="n">
+        <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.8</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -823,46 +817,46 @@
         <v>9.300000000000001</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N4" s="16" t="n">
-        <v>19.9</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q4" s="16" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="16" t="n">
-        <v>114.1</v>
+      <c r="S4" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>542.5</v>
+        <v>42.5</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="16" t="n">
-        <v>2219.1</v>
-      </c>
-      <c r="W4" s="16" t="n">
+      <c r="V4" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>41.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>0.1</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -880,68 +874,74 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="11" t="n">
         <v>26.9</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>44.5</v>
+        <v>11.5</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>15.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L5" s="16" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>19.4</v>
+      </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>190.8</v>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="16" t="n">
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="S5" s="16" t="n">
+      <c r="R5" s="8" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="16" t="n">
-        <v>189.5</v>
+      <c r="U5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v>199.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.2</v>
+        <v>19.2</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>2.1</v>
+        <v>18.3</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>180.5</v>
+        <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>6.6</v>
+        <v>66.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -959,68 +959,74 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>0.5</v>
+      <c r="G6" s="11" t="n">
+        <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>5.9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="K6" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" s="16" t="n">
-        <v>411</v>
-      </c>
-      <c r="N6" s="16" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>211</v>
+      </c>
+      <c r="N6" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R6" s="16" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S6" s="3" t="inlineStr"/>
+      <c r="Q6" s="8" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="R6" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="U6" s="3" t="inlineStr"/>
-      <c r="V6" s="16" t="n">
-        <v>715.8</v>
+      <c r="U6" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>114.3</v>
+        <v>18.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>0.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1036,76 +1042,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1275.8</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>22.2</v>
+        <v>275.8</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>98</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>444.4</v>
+        <v>17.3</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>112.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.4</v>
+        <v>12.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M7" s="16" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="N7" s="16" t="n">
-        <v>15</v>
+        <v>13.2</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="R7" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>43.3</v>
+      <c r="S7" s="8" t="n">
+        <v>77.5</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="U7" s="16" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>8.4</v>
+      <c r="U7" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>46.8</v>
+        <v>16.8</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>131.3</v>
+        <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>814.9</v>
+        <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>14.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1121,22 +1127,22 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>391.2</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>26.1</v>
+        <v>291.2</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>26.8</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>8.1</v>
+        <v>10.4</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>18.6</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1145,50 +1151,52 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>424.4</v>
-      </c>
-      <c r="N8" s="3" t="inlineStr"/>
+        <v>10.8</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>190.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O8" s="3" t="n">
-        <v>1718</v>
+        <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>0.8</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q8" s="8" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="R8" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>19.5</v>
+        <v>1.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>176</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W8" s="16" t="n">
-        <v>17.3</v>
+        <v>11.8</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>97.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>2.1</v>
+        <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>1.2</v>
+        <v>87</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>12.6</v>
+        <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1206,71 +1214,71 @@
       <c r="C9" s="3" t="n">
         <v>1749.7</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>128.6</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="F9" s="17" t="n">
-        <v>91.90000000000001</v>
+      <c r="D9" s="11" t="n">
+        <v>129</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>92</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1702.6</v>
+        <v>60.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13.3</v>
+        <v>19.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>17.7</v>
+        <v>7.8</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>56.4</v>
+        <v>56.7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>551.2</v>
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>55.1</v>
+        <v>25.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1484.8</v>
+        <v>484.8</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>101.5</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>185.9</v>
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>188.5</v>
+        <v>885.3</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>380.5</v>
+        <v>9501.5</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1233.3</v>
+        <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>184.9</v>
+        <v>8.9</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>911.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14154.5</v>
+        <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>119.8</v>
@@ -1289,44 +1297,46 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>849.9</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="J10" s="16" t="n">
-        <v>211.4</v>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>797.4</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>111</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>3</v>
+      <c r="M10" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="P10" s="16" t="n">
-        <v>1.5</v>
+        <v>96.8</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
@@ -1334,29 +1344,29 @@
       <c r="R10" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S10" s="16" t="n">
-        <v>12.7</v>
+      <c r="S10" s="8" t="n">
+        <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>14167.1</v>
+        <v>26.7</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="16" t="n">
+      <c r="X10" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>182.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1372,66 +1382,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1509.3</v>
-      </c>
-      <c r="D11" s="10" t="n">
+        <v>909.3</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>6.7</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>84.7</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>6.4</v>
+      </c>
       <c r="N11" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q11" s="16" t="n">
-        <v>226.3</v>
+        <v>119</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q11" s="8" t="n">
+        <v>66.5</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1.4</v>
+        <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>40.1</v>
+        <v>862</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="16" t="n">
+      <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>2.6</v>
+      <c r="W11" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1447,37 +1467,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1306.7</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E12" s="10" t="n">
+        <v>506.7</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>14.5</v>
+      <c r="F12" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>94.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>1.5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="16" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="16" t="n">
-        <v>21.9</v>
+        <v>17</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>22.1</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
@@ -1486,37 +1506,37 @@
         <v>195</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="S12" s="16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="S12" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>4.2</v>
+        <v>37</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>4.3</v>
+        <v>11.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.1</v>
+        <v>19.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1092</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1532,66 +1552,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1357.9</v>
-      </c>
-      <c r="D13" s="10" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
+        <v>3514.9</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>11.3</v>
+      </c>
       <c r="F13" s="11" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>4.4</v>
+        <v>18.2</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>14.7</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr"/>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="16" t="n">
-        <v>83.59999999999999</v>
+        <v>11.5</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="P13" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>180.9</v>
+      </c>
       <c r="R13" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="S13" s="16" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="16" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="X13" s="16" t="n">
+      <c r="W13" s="8" t="n">
+        <v>6816.4</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>9.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1607,70 +1637,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="G14" s="16" t="n">
+        <v>221</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="16" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="16" t="n">
-        <v>1182</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>3</v>
+      <c r="I14" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>18</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P14" s="16" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q14" s="16" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="R14" s="16" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S14" s="16" t="n">
-        <v>126.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="U14" s="3" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="W14" s="16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>6</v>
+        <v>19.5</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>81811</v>
+        <v>28.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1686,19 +1722,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1631</v>
-      </c>
-      <c r="D15" s="10" t="n">
+        <v>1638</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1011.08</v>
+        <v>11</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>118.15</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>15.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>15.6</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1707,53 +1743,55 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="16" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>21.3</v>
+      <c r="L15" s="8" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>711.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P15" s="16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q15" s="16" t="n">
+      <c r="P15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="T15" s="3" t="inlineStr"/>
+      <c r="R15" s="8" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>168</v>
+      </c>
       <c r="U15" s="3" t="n">
-        <v>17.9</v>
+        <v>15.8</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="W15" s="16" t="n">
-        <v>116.5</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>6.4</v>
+        <v>2</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>69.40000000000001</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>18.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1772,16 +1810,16 @@
         <v>2227.1</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>128</v>
+        <v>1298</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>256.8</v>
+        <v>56.8</v>
       </c>
       <c r="F16" s="17" t="n">
-        <v>92.3</v>
+        <v>9.5</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>79.2</v>
+        <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
@@ -1790,13 +1828,13 @@
         <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>121.8</v>
+        <v>51.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>59.1</v>
+        <v>591.7</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
@@ -1805,40 +1843,40 @@
         <v>67.90000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>439.8</v>
+        <v>39</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>11191</v>
+        <v>17119</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.1</v>
+        <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>721.1</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.1</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>160.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>921.2</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>801.9</v>
+        <v>801.7</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>182.2</v>
+        <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1364</v>
+        <v>2369.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.4</v>
+        <v>393.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1854,74 +1892,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>245.9</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>445.9</v>
+      </c>
+      <c r="D17" s="17" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>14.5</v>
+      <c r="E17" s="17" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>99.8</v>
+        <v>5.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="16" t="n">
+      <c r="N17" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>197.8</v>
-      </c>
-      <c r="P17" s="16" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P17" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="16" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S17" s="16" t="n">
+      <c r="R17" s="8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>162</v>
+        <v>72.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="V17" s="16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V17" s="8" t="n">
         <v>119.6</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="8" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>14.4</v>
+      <c r="X17" s="8" t="n">
+        <v>16.5</v>
       </c>
       <c r="Y17" s="3" t="n">
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1937,56 +1975,58 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1435.8</v>
-      </c>
-      <c r="D18" s="10" t="n">
+        <v>455.1</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="10" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="E18" s="15" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G18" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>61.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N18" s="16" t="n">
-        <v>61</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>1610.5</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="16" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="S18" s="16" t="n">
-        <v>115.4</v>
+      <c r="R18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>101.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1406</v>
+        <v>9</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>17.9</v>
@@ -1994,17 +2034,17 @@
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="X18" s="16" t="n">
-        <v>15.6</v>
+      <c r="W18" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>13791</v>
+        <v>510.1</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>110.9</v>
+        <v>11.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2020,69 +2060,73 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1531.1</v>
-      </c>
-      <c r="D19" s="10" t="n">
+        <v>95311.10000000001</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E19" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="G19" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>7.2</v>
+      </c>
       <c r="I19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L19" s="16" t="n">
-        <v>211</v>
-      </c>
-      <c r="M19" s="16" t="n">
-        <v>711</v>
-      </c>
-      <c r="N19" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>111</v>
+      </c>
+      <c r="N19" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>261.1</v>
-      </c>
-      <c r="R19" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>24.2</v>
+        <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>0.3</v>
+        <v>94.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>7.2</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="X19" s="16" t="n">
+      <c r="W19" s="8" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="X19" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>16.6</v>
@@ -2101,69 +2145,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>592.2</v>
-      </c>
-      <c r="D20" s="10" t="n">
+        <v>542.2</v>
+      </c>
+      <c r="D20" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="11" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="G20" s="16" t="n">
+      <c r="E20" s="15" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G20" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>733.5</v>
+        <v>6.9</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M20" s="16" t="n">
-        <v>8818.1</v>
-      </c>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>5.9</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>221.2</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>811</v>
+      </c>
       <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
+        <v>98.2</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="Q20" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="16" t="n">
-        <v>151.3</v>
+      <c r="R20" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>140.5</v>
+        <v>40.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>22.4</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X20" s="16" t="n">
-        <v>2298.2</v>
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="X20" s="8" t="n">
+        <v>29.9</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+        <v>721</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2180,59 +2232,61 @@
       <c r="C21" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="11" t="n">
         <v>24.8</v>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F21" s="10" t="n">
         <v>12.6</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="3" t="n">
-        <v>42.1</v>
+      <c r="H21" s="8" t="n">
+        <v>10.9</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.3</v>
+        <v>2.8</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N21" s="3" t="inlineStr"/>
+        <v>11.3</v>
+      </c>
+      <c r="M21" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>54.9</v>
+      </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>22.4</v>
+        <v>25.6</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S21" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="S21" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>1931</v>
+        <v>51</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V21" s="16" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2242,10 +2296,10 @@
         <v>20</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>187</v>
+        <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2261,72 +2315,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1429</v>
-      </c>
-      <c r="D22" s="10" t="n">
+        <v>194828.8</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="14" t="inlineStr"/>
+      <c r="E22" s="11" t="n">
+        <v>12.1</v>
+      </c>
       <c r="F22" s="11" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>13.1</v>
+        <v>18.6</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+        <v>85.90000000000001</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>20.7</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K22" s="16" t="n">
-        <v>8</v>
+        <v>19.8</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>9</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M22" s="16" t="n">
+      <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="16" t="n">
+      <c r="N22" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>99</v>
+        <v>992</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R22" s="16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="16" t="n">
-        <v>194.9</v>
+      <c r="S22" s="8" t="n">
+        <v>49.4</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>443454.4</v>
+        <v>49.5</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V22" s="16" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="16" t="n">
+      <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="16" t="n">
-        <v>13.9</v>
+      <c r="X22" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>50.5</v>
+        <v>505.9</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>113.4</v>
+        <v>1199.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2342,72 +2400,76 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>23203.1</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>12320.8</v>
+      </c>
+      <c r="D23" s="11" t="n">
         <v>132.1</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>551.4</v>
+        <v>201.5</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>75.09999999999999</v>
+        <v>94.40000000000001</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>75.7</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>141.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>101.3</v>
+        <v>5.9</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>61.8</v>
       </c>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="n">
+        <v>711.5</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
+        <v>293</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="Q23" s="3" t="n">
-        <v>1128.9</v>
+        <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>781.7</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>235.7</v>
+        <v>2351.7</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1106.7</v>
+        <v>106.7</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>185.5</v>
+        <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>26.3</v>
+        <v>86.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>1341.5</v>
+        <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>141</v>
+        <v>541</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2425,70 +2487,74 @@
       <c r="C24" s="3" t="n">
         <v>484.1</v>
       </c>
-      <c r="D24" s="10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="F24" s="10" t="n">
+      <c r="D24" s="11" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F24" s="17" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="11" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>7.1</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="16" t="n">
+      <c r="M24" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="16" t="n">
+      <c r="R24" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="16" t="n">
-        <v>15.6</v>
+      <c r="S24" s="3" t="n">
+        <v>129.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1247.9</v>
-      </c>
-      <c r="U24" s="16" t="n">
-        <v>197.5</v>
+        <v>22.9</v>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v>177.7</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>91.3</v>
+        <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>41.1</v>
-      </c>
-      <c r="X24" s="16" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.9</v>
+        <v>168.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2504,64 +2570,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1488.9</v>
-      </c>
-      <c r="D25" s="16" t="n">
+        <v>428.9</v>
+      </c>
+      <c r="D25" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E25" s="14" t="inlineStr"/>
-      <c r="F25" s="3" t="n">
+      <c r="E25" s="11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F25" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
+      <c r="G25" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="K25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="L25" s="16" t="n">
-        <v>107.9</v>
+        <v>6</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O25" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>18</v>
+      </c>
       <c r="P25" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q25" s="16" t="n">
-        <v>29.1</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>0.7</v>
+        <v>24.1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>549.3</v>
-      </c>
-      <c r="U25" s="16" t="n">
-        <v>151.8</v>
+        <v>6.9</v>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="16" t="n">
-        <v>16.9</v>
+      <c r="W25" s="8" t="n">
+        <v>116.9</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>16.8</v>
+        <v>116.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2577,52 +2655,58 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1349.9</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E26" s="3" t="n">
+        <v>349.9</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E26" s="11" t="n">
         <v>9.6</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G26" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="G26" s="11" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="I26" s="16" t="n">
-        <v>25.6</v>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>18.5</v>
+        <v>8.9</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="16" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M26" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="inlineStr"/>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="16" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S26" s="16" t="n">
-        <v>547.4</v>
+      <c r="R26" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>163.5</v>
+        <v>63.5</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2637,10 +2721,10 @@
         <v>14.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>512.1</v>
+        <v>194</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+        <v>211.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2659,65 +2743,73 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="F27" s="14" t="inlineStr"/>
-      <c r="G27" s="11" t="n">
-        <v>114.4</v>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
+        <v>24.5</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="16" t="n">
-        <v>15.1</v>
+      <c r="J27" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="M27" s="16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>44</v>
+      </c>
       <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="16" t="n">
-        <v>161.8</v>
+      <c r="R27" s="8" t="n">
+        <v>1618.1</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>11.7</v>
+        <v>11.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>186</v>
+        <v>56</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="W27" s="16" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="X27" s="16" t="n">
-        <v>187.5</v>
+        <v>87.40000000000001</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>15859.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>113</v>
+        <v>913</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2733,72 +2825,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>15139.5</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>27</v>
+        <v>313.3</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>23</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>11.15</v>
+        <v>15.6</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>15.4</v>
+        <v>19.3</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>15.1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="16" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="M28" s="16" t="n">
-        <v>113.3</v>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>13.2</v>
+      <c r="L28" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M28" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="N28" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q28" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q28" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="16" t="n">
+      <c r="R28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="16" t="n">
-        <v>99</v>
+      <c r="S28" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>168</v>
+        <v>68</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>11</v>
+      </c>
       <c r="Y28" s="3" t="n">
-        <v>121</v>
+        <v>1891</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>0.8</v>
+        <v>11.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2817,67 +2913,73 @@
         <v>523.3</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>48.28</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>12.1</v>
+        <v>28.3</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>10.7</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>48.4</v>
+        <v>19.5</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>18.1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3</v>
+        <v>7.2</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="J29" s="3" t="n">
-        <v>16.2</v>
+      <c r="J29" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M29" s="16" t="n">
-        <v>910.5</v>
-      </c>
-      <c r="N29" s="16" t="n">
-        <v>122.4</v>
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q29" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="R29" s="16" t="n">
-        <v>181.7</v>
-      </c>
-      <c r="S29" s="16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>217</v>
+      </c>
+      <c r="R29" s="8" t="n">
+        <v>517.1</v>
+      </c>
+      <c r="S29" s="3" t="n">
         <v>17</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr"/>
+        <v>57.8</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X29" s="8" t="n">
+        <v>12.7</v>
+      </c>
       <c r="Y29" s="3" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>111.2</v>
+        <v>111.9</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2893,73 +2995,73 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22848.1</v>
+        <v>22848.3</v>
       </c>
       <c r="D30" s="17" t="n">
         <v>131.2</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="F30" s="17" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G30" s="3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="G30" s="11" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>113.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1119.5</v>
+        <v>119.5</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>52.2</v>
+        <v>51.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>56.1</v>
+        <v>56.7</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1489</v>
+        <v>9489</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>113.2</v>
+        <v>1113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>86.7</v>
+        <v>851.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>184.4</v>
+        <v>844.7</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.9</v>
+        <v>35.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>181.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>83.2</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>1365</v>
+        <v>365</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>35</v>
@@ -2978,67 +3080,73 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1452</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>1532</v>
+      </c>
+      <c r="D31" s="17" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="17" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="10" t="n">
-        <v>15.8</v>
+      <c r="G31" s="8" t="n">
+        <v>58.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
+        <v>72.40000000000001</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J31" s="3" t="n">
         <v>39.1</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="16" t="n">
+      <c r="K31" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L31" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>14.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
+        <v>412.8</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
-      <c r="P31" s="16" t="n">
-        <v>40.4</v>
+      <c r="P31" s="3" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="16" t="n">
-        <v>179.3</v>
-      </c>
-      <c r="S31" s="16" t="n">
+      <c r="R31" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" s="16" t="n">
-        <v>11.1</v>
+        <v>13.1</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>211.1</v>
       </c>
       <c r="V31" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="16" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="16" t="n">
+      <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>730</v>
+        <v>13</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>7</v>
@@ -3057,71 +3165,77 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="D32" s="10" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="F32" s="10" t="n">
+        <v>528</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F32" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="G32" s="11" t="n">
-        <v>21.8</v>
+      <c r="G32" s="8" t="n">
+        <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.7</v>
+        <v>6.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>61.2</v>
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="L32" s="16" t="n">
-        <v>1090.5</v>
-      </c>
-      <c r="M32" s="3" t="n">
-        <v>103.3</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="O32" s="3" t="n">
-        <v>97.8</v>
+        <v>49</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>10.6</v>
+        <v>1</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R32" s="16" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R32" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="3" t="n">
+      <c r="S32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="V32" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X32" s="16" t="n">
-        <v>27.9</v>
+        <v>17.6</v>
+      </c>
+      <c r="X32" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3138,62 +3252,74 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>28.8</v>
+      <c r="D33" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>12.8</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>48.54</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>211.1</v>
+        <v>18.9</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>11.6</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
+        <v>1.9</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>95.90000000000001</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K33" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>6.8</v>
+      </c>
       <c r="L33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
+        <v>19.9</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="N33" s="8" t="n">
+        <v>18.6</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>98.8</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="3" t="n">
-        <v>204.3</v>
+      <c r="Q33" s="8" t="n">
+        <v>203.5</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="S33" s="16" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S33" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>79.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="3" t="inlineStr"/>
+      <c r="V33" s="8" t="n">
+        <v>19.9</v>
+      </c>
       <c r="W33" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3209,72 +3335,76 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.1</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>23.3</v>
+        <v>329.9</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>23.1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H34" s="16" t="n">
-        <v>14.1</v>
+        <v>14.7</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.9</v>
+        <v>18.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="L34" s="16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="16" t="n">
+      <c r="M34" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="8" t="n">
+        <v>7.8</v>
+      </c>
       <c r="O34" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q34" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S34" s="16" t="n">
-        <v>181.8</v>
+      <c r="R34" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="S34" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>72.8</v>
+        <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="V34" s="16" t="n">
-        <v>1287.1</v>
-      </c>
-      <c r="W34" s="16" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="inlineStr"/>
+      <c r="X34" s="8" t="n">
+        <v>81</v>
+      </c>
       <c r="Y34" s="3" t="n">
-        <v>893</v>
+        <v>82</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3290,19 +3420,19 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1506.7</v>
-      </c>
-      <c r="D35" s="3" t="n">
+        <v>5056.7</v>
+      </c>
+      <c r="D35" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>9.5</v>
@@ -3311,48 +3441,52 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>51.5</v>
+        <v>21.1</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="16" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>84.8</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R35" s="16" t="n">
-        <v>147.6</v>
+        <v>1891</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>572</v>
-      </c>
-      <c r="U35" s="16" t="n">
+        <v>252</v>
+      </c>
+      <c r="U35" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="16" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X35" s="16" t="n">
-        <v>4116.8</v>
+      <c r="W35" s="8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>68.5</v>
+        <v>168.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3374,15 +3508,15 @@
         <v>535.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>56.3</v>
+        <v>26.5</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>0.9</v>
+        <v>10.7</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>81.3</v>
-      </c>
-      <c r="G36" s="16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G36" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3395,51 +3529,51 @@
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="16" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="M36" s="16" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N36" s="8" t="n">
+        <v>12.6</v>
+      </c>
       <c r="O36" s="3" t="n">
         <v>199</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>18.1</v>
+        <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R36" s="16" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>14.8</v>
+      <c r="R36" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>65.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>685</v>
-      </c>
-      <c r="U36" s="16" t="n">
-        <v>27.9</v>
+        <v>115</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>17.9</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="16" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="X36" s="16" t="n">
-        <v>13.8</v>
+      <c r="W36" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>1.9</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>1110.8</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3454,72 +3588,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D37" s="17" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>160.9</v>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>991.7</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>1.6</v>
+        <v>2290.9</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>65.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>146</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>116.1</v>
+        <v>167.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>81.5</v>
+        <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>74.59999999999999</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>2492</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>115.5</v>
+        <v>115.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>811.9</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>116.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>54.5</v>
+        <v>554.5</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1100.9</v>
+        <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>183.1</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.8</v>
+        <v>89.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>394.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3535,18 +3673,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2448.1</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="E38" s="10" t="n">
+        <v>448.9</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="11" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3555,48 +3693,54 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="16" t="n">
-        <v>92.09999999999999</v>
+      <c r="J38" s="8" t="n">
+        <v>20.1</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="16" t="n">
+      <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="16" t="n">
+      <c r="M38" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>984.9</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>23.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S38" s="8" t="n">
+        <v>217.6</v>
+      </c>
       <c r="T38" s="3" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>424.3</v>
+        <v>83.5</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="16" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X38" s="16" t="n">
+      <c r="W38" s="8" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3612,64 +3756,74 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>3599.9</v>
-      </c>
-      <c r="D39" s="3" t="n">
+        <v>5372.9</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>26.9</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1118</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
+      <c r="G39" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="K39" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L39" s="16" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="N39" s="8" t="n">
+        <v>19.2</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>1980.8</v>
+        <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>18.4</v>
+        <v>4.9</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="8" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>1.6</v>
+        <v>10.2</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>1720</v>
-      </c>
-      <c r="U39" s="16" t="n">
+        <v>58146.9</v>
+      </c>
+      <c r="U39" s="8" t="n">
         <v>18</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="W39" s="16" t="n">
-        <v>8151.7</v>
-      </c>
-      <c r="X39" s="16" t="n">
-        <v>119.6</v>
+        <v>12.7</v>
+      </c>
+      <c r="W39" s="8" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>5</v>
+        <v>141.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3685,67 +3839,71 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.1</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F40" s="10" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F40" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G40" s="10" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>17.3</v>
+      <c r="G40" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12.4</v>
+        <v>21.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="16" t="n">
+      <c r="M40" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="N40" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="16" t="n">
-        <v>18.5</v>
+      <c r="S40" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V40" s="3" t="inlineStr"/>
-      <c r="W40" s="16" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X40" s="16" t="n">
-        <v>199.3</v>
+        <v>8</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>181.3</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>983</v>
+        <v>83</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>7.2</v>
@@ -3764,66 +3922,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>245451.2</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>128.13</v>
+        <v>458.2</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H41" s="16" t="n">
-        <v>51</v>
+        <v>1.9</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>51.9</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="K41" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>818.5</v>
+        <v>88.7</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P41" s="3" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R41" s="16" t="n">
-        <v>717.9</v>
-      </c>
-      <c r="S41" s="16" t="n">
-        <v>216.6</v>
-      </c>
-      <c r="T41" s="3" t="inlineStr"/>
-      <c r="U41" s="16" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V41" s="16" t="n">
-        <v>222</v>
+      <c r="R41" s="8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S41" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>4213.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>121.2</v>
+        <v>1112</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3839,39 +4007,43 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>524.4</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr"/>
+        <v>5254.4</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>27.2</v>
+      </c>
       <c r="E42" s="11" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="F42" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F42" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="11" t="n">
-        <v>25.2</v>
+      <c r="G42" s="15" t="n">
+        <v>15.2</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>5.6</v>
+      </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N42" s="16" t="n">
-        <v>13.2</v>
+        <v>0.2</v>
+      </c>
+      <c r="N42" s="8" t="n">
+        <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>0.8</v>
@@ -3879,25 +4051,27 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="S42" s="16" t="n">
-        <v>14.7</v>
+      <c r="R42" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>148.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>543.5</v>
-      </c>
-      <c r="U42" s="16" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="16" t="n">
-        <v>22</v>
+      <c r="V42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="X42" s="8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -3913,10 +4087,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="14" t="inlineStr"/>
+      <c r="C43" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
@@ -3950,10 +4126,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3990,68 +4168,72 @@
       <c r="C45" s="3" t="n">
         <v>1911.2</v>
       </c>
-      <c r="D45" s="15" t="inlineStr"/>
-      <c r="E45" s="15" t="inlineStr"/>
-      <c r="F45" s="17" t="n">
+      <c r="D45" s="17" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="F45" s="11" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="11" t="n">
-        <v>10.8</v>
+      <c r="G45" s="3" t="n">
+        <v>7.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>454.4</v>
+        <v>119.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>121.9</v>
+        <v>20.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>42.9</v>
+        <v>212.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>51.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>4.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>198.6</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>831.4</v>
+        <v>851.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>168.3</v>
+        <v>67.3</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>8263</v>
+        <v>1263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>331.8</v>
+        <v>331.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4066,64 +4248,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="10" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="C46" s="3" t="n">
+        <v>5417.8</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E46" s="17" t="n">
         <v>10.4</v>
       </c>
-      <c r="F46" s="10" t="n">
+      <c r="F46" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="10" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>19.7</v>
+      <c r="G46" s="8" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>52.1</v>
+        <v>3.6</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>52.4</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="16" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M46" s="16" t="n">
-        <v>10.7</v>
+      <c r="L46" s="8" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>4.8</v>
+        <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>97</v>
+        <v>197</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q46" s="16" t="n">
-        <v>29.7</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>247.1</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S46" s="16" t="n">
-        <v>2261.5</v>
-      </c>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>654.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="16" t="n">
+      <c r="W46" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="inlineStr"/>
       <c r="Y46" s="3" t="n">
-        <v>1680.1</v>
+        <v>1860.8</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,10 +164,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,7 +784,7 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3012.1</v>
+        <v>301.2</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>27.8</v>
@@ -802,7 +799,7 @@
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -823,24 +820,24 @@
         <v>11.9</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
+        <v>928</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="R4" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
-        <v>19.1</v>
+        <v>14.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="U4" s="3" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="U4" s="8" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="3" t="n">
@@ -856,7 +853,7 @@
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+        <v>73.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -883,8 +880,8 @@
       <c r="F5" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>15.9</v>
+      <c r="G5" s="8" t="n">
+        <v>59.4</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>7.9</v>
@@ -898,11 +895,11 @@
       <c r="K5" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <v>29.5</v>
+      <c r="L5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>19.4</v>
+        <v>8149.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -911,13 +908,13 @@
         <v>90</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>18.7</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="8" t="n">
-        <v>80.59999999999999</v>
+      <c r="R5" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>20.9</v>
@@ -925,14 +922,12 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="n">
-        <v>12</v>
-      </c>
+      <c r="U5" s="3" t="inlineStr"/>
       <c r="V5" s="8" t="n">
-        <v>199.5</v>
+        <v>19.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>19.2</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.3</v>
@@ -941,7 +936,7 @@
         <v>80.5</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>66.5</v>
+        <v>469.5</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -972,7 +967,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>5.9</v>
+        <v>7.9</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -981,13 +976,13 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>69.5</v>
+        <v>6.5</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>211</v>
+        <v>1.1</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>13.1</v>
@@ -999,10 +994,10 @@
         <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>158.4</v>
-      </c>
-      <c r="R6" s="8" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>11.6</v>
@@ -1011,22 +1006,22 @@
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>18.3</v>
+        <v>24.6</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1045,25 +1040,25 @@
         <v>275.8</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="E7" s="11" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G7" s="11" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>112.9</v>
+        <v>12.9</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0</v>
@@ -1078,27 +1073,27 @@
         <v>5</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>77.5</v>
+        <v>17.7</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="8" t="n">
+      <c r="V7" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1111,7 +1106,7 @@
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1127,16 +1122,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>291.2</v>
+        <v>391.2</v>
       </c>
       <c r="D8" s="11" t="n">
-        <v>26.8</v>
+        <v>27.3</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>15.8</v>
@@ -1151,27 +1146,27 @@
         <v>3.5</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>190.6</v>
+      <c r="M8" s="3" t="n">
+        <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="R8" s="8" t="n">
+        <v>2719.4</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1186,8 +1181,8 @@
       <c r="V8" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="W8" s="8" t="n">
-        <v>97.3</v>
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
       </c>
       <c r="X8" s="3" t="n">
         <v>18.9</v>
@@ -1212,31 +1207,31 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>129</v>
+        <v>43927.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>128.9</v>
       </c>
       <c r="E9" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="11" t="n">
-        <v>92</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="F9" s="10" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>60.6</v>
+        <v>12.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>9.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>56.7</v>
@@ -1245,10 +1240,10 @@
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>25.1</v>
+        <v>55.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>484.8</v>
+        <v>684.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.6</v>
@@ -1260,28 +1255,28 @@
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>885.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>9501.5</v>
+        <v>3801.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>911.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>9414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>119.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1297,7 +1292,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>849.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>25.8</v>
@@ -1318,11 +1313,9 @@
         <v>2</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>797.4</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>418.1</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
@@ -1336,7 +1329,7 @@
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.5</v>
+        <v>10.5</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>20.3</v>
@@ -1348,10 +1341,10 @@
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.7</v>
+        <v>26.1</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>7.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>19</v>
@@ -1366,7 +1359,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1382,25 +1375,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>909.3</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>509.3</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="G11" s="11" t="n">
+      <c r="E11" s="13" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
-      <c r="I11" s="8" t="n">
-        <v>84.7</v>
+      <c r="I11" s="3" t="n">
+        <v>4.7</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
@@ -1409,43 +1402,43 @@
         <v>0.2</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>21.1</v>
+        <v>17.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>51.8</v>
+        <v>2.9</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>66.5</v>
+        <v>26.3</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="3" t="n">
+      <c r="S11" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>862</v>
+        <v>512</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>11.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>66</v>
@@ -1467,49 +1460,49 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.7</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>29.9</v>
+        <v>506.1</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>5.9</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="13" t="n">
         <v>18.9</v>
       </c>
-      <c r="G12" s="8" t="n">
-        <v>13</v>
+      <c r="G12" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>9.4</v>
+        <v>7.1</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M12" s="3" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="M12" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>15.5</v>
@@ -1520,23 +1513,23 @@
       <c r="T12" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="U12" s="8" t="n">
-        <v>4.6</v>
+      <c r="U12" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>19.7</v>
+        <v>13.7</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1552,10 +1545,10 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3514.9</v>
+        <v>357.9</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="E13" s="11" t="n">
         <v>11.3</v>
@@ -1564,37 +1557,37 @@
         <v>18.2</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>13.6</v>
+        <v>23.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>9.699999999999999</v>
+      <c r="P13" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>180.9</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>17.3</v>
@@ -1603,7 +1596,7 @@
         <v>11.8</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>3</v>
@@ -1612,16 +1605,16 @@
         <v>19.6</v>
       </c>
       <c r="W13" s="8" t="n">
-        <v>6816.4</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>19.1</v>
+        <v>791.5</v>
+      </c>
+      <c r="X13" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>84</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1637,40 +1630,40 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>18.53</v>
-      </c>
-      <c r="G14" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>11.3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>19.8</v>
+      <c r="L14" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>98</v>
@@ -1678,23 +1671,21 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="3" t="n">
-        <v>15.9</v>
+      <c r="Q14" s="8" t="n">
+        <v>46.9</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="S14" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>14.9</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>19.5</v>
+        <v>0.6</v>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v>59.5</v>
       </c>
       <c r="W14" s="3" t="n">
         <v>6.2</v>
@@ -1703,10 +1694,10 @@
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>28.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1722,7 +1713,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1638</v>
+        <v>631</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>26</v>
@@ -1748,14 +1739,14 @@
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="8" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="M15" s="8" t="n">
-        <v>711.3</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1767,25 +1758,25 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="S15" s="8" t="n">
-        <v>57.9</v>
+        <v>72.59999999999999</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>15.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>15.8</v>
+        <v>48</v>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>69.40000000000001</v>
+        <v>16.3</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>16.4</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>67</v>
@@ -1809,16 +1800,16 @@
       <c r="C16" s="3" t="n">
         <v>2227.1</v>
       </c>
-      <c r="D16" s="17" t="n">
-        <v>1298</v>
-      </c>
-      <c r="E16" s="17" t="n">
+      <c r="D16" s="10" t="n">
+        <v>128</v>
+      </c>
+      <c r="E16" s="10" t="n">
         <v>56.8</v>
       </c>
-      <c r="F16" s="17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="10" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1828,43 +1819,43 @@
         <v>14.2</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>51.8</v>
+        <v>21.8</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>39.8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>591.7</v>
+        <v>5.9</v>
       </c>
       <c r="M16" s="3" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>17119</v>
+        <v>1111</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>77.7</v>
+        <v>78.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310.9</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>160.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>801.7</v>
@@ -1873,10 +1864,10 @@
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>2369.8</v>
+        <v>369</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>393.9</v>
+        <v>33.9</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1894,26 +1885,26 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="10" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="17" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F17" s="17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G17" s="3" t="n">
+      <c r="E17" s="10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G17" s="11" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="3" t="n">
-        <v>5.8</v>
+      <c r="J17" s="8" t="n">
+        <v>871.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
@@ -1929,7 +1920,7 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>22.2</v>
@@ -1937,20 +1928,20 @@
       <c r="R17" s="8" t="n">
         <v>16.9</v>
       </c>
-      <c r="S17" s="3" t="n">
+      <c r="S17" s="8" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>72.2</v>
+        <v>42</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V17" s="8" t="n">
-        <v>119.6</v>
+      <c r="V17" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W17" s="8" t="n">
-        <v>16.1</v>
+        <v>16.9</v>
       </c>
       <c r="X17" s="8" t="n">
         <v>16.5</v>
@@ -1975,40 +1966,40 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.1</v>
+        <v>455.5</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="15" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G18" s="15" t="n">
+      <c r="E18" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G18" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.9</v>
+        <v>2.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>61.5</v>
+        <v>1666.6</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>1610.5</v>
+        <v>16</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>19</v>
@@ -2020,31 +2011,31 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="S18" s="8" t="n">
-        <v>101.4</v>
+        <v>110.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U18" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="8" t="n">
+      <c r="W18" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>14.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>510.1</v>
+        <v>39</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>11.6</v>
+        <v>110.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2060,7 +2051,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>95311.10000000001</v>
+        <v>531.9</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>28</v>
@@ -2078,19 +2069,19 @@
         <v>7.2</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>11.2</v>
+        <v>111.2</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>111</v>
+        <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>13</v>
@@ -2098,11 +2089,11 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="3" t="n">
-        <v>0.4</v>
+      <c r="P19" s="8" t="n">
+        <v>9.4</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="R19" s="3" t="n">
         <v>18</v>
@@ -2111,7 +2102,7 @@
         <v>16.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>94.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="U19" s="8" t="n">
         <v>7.2</v>
@@ -2119,10 +2110,10 @@
       <c r="V19" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="W19" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2150,13 +2141,13 @@
       <c r="D20" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="15" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="G20" s="3" t="n">
+      <c r="E20" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G20" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2166,22 +2157,22 @@
         <v>33.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8" t="n">
-        <v>111.2</v>
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>221.2</v>
-      </c>
-      <c r="N20" s="8" t="n">
-        <v>811</v>
+        <v>211</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>98.2</v>
+        <v>198</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
@@ -2192,7 +2183,7 @@
       <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="S20" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T20" s="3" t="n">
@@ -2205,13 +2196,13 @@
         <v>22.2</v>
       </c>
       <c r="W20" s="8" t="n">
-        <v>89.5</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>29.9</v>
+        <v>299.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>721</v>
+        <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>2.6</v>
@@ -2233,25 +2224,25 @@
         <v>382.4</v>
       </c>
       <c r="D21" s="11" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="E21" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2263,7 +2254,7 @@
         <v>13</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>54.9</v>
+        <v>15.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>99</v>
@@ -2281,7 +2272,7 @@
         <v>16.8</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>16.2</v>
@@ -2299,7 +2290,7 @@
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2315,31 +2306,31 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>194828.8</v>
+        <v>9489</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G22" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>20.7</v>
+        <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>19.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>9</v>
+        <v>82.8</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>11.2</v>
@@ -2348,22 +2339,22 @@
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>14.1</v>
+        <v>1.4</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>992</v>
+        <v>99</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>2.3</v>
+        <v>23.6</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>49.5</v>
@@ -2378,13 +2369,13 @@
         <v>15.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>13.8</v>
+        <v>53.8</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>505.9</v>
+        <v>50.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1199.7</v>
+        <v>139.7</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2400,19 +2391,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.8</v>
-      </c>
-      <c r="D23" s="11" t="n">
+        <v>12320.3</v>
+      </c>
+      <c r="D23" s="10" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="17" t="n">
-        <v>201.5</v>
-      </c>
-      <c r="F23" s="17" t="n">
+      <c r="E23" s="11" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.7</v>
+      <c r="G23" s="11" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
@@ -2424,7 +2415,7 @@
         <v>20.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>5.9</v>
+        <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>2.5</v>
@@ -2433,7 +2424,7 @@
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>711.5</v>
+        <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>293</v>
@@ -2445,13 +2436,13 @@
         <v>128.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>86</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>781.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2351.7</v>
+        <v>235.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>88.5</v>
@@ -2469,7 +2460,7 @@
         <v>341.5</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>541</v>
+        <v>41</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2485,46 +2476,44 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>484.1</v>
+        <v>2464.1</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="E24" s="17" t="n">
+      <c r="E24" s="11" t="n">
         <v>11.4</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="11" t="n">
-        <v>15.1</v>
+      <c r="G24" s="8" t="n">
+        <v>57.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>29.4</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="8" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>25.8</v>
@@ -2533,25 +2522,25 @@
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>129.6</v>
+        <v>15.6</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>22.9</v>
+        <v>27.1</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>177.7</v>
+        <v>177.1</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>17.7</v>
+        <v>1.7</v>
       </c>
       <c r="X24" s="8" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>168.3</v>
+        <v>68.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2570,40 +2559,40 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>428.9</v>
+        <v>1488.9</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>9.699999999999999</v>
+        <v>32.7</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>3.2</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>16</v>
+      <c r="G25" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>15.4</v>
+        <v>2.2</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>49.7</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>5.4</v>
+        <v>19.4</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>18</v>
@@ -2611,35 +2600,35 @@
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>24.1</v>
+      <c r="Q25" s="8" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>37.6</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>13.8</v>
+        <v>113.2</v>
       </c>
       <c r="V25" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>116.8</v>
+        <v>216.9</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>66</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2670,40 +2659,40 @@
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>8.9</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>19.4</v>
+        <v>109.4</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S26" s="3" t="n">
-        <v>15.7</v>
+      <c r="R26" s="8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S26" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>63.5</v>
@@ -2715,16 +2704,16 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>16.2</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>211.8</v>
+        <v>111.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2743,19 +2732,19 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>24.5</v>
+        <v>19.1</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>11.7</v>
+        <v>17.1</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="3" t="n">
-        <v>14</v>
+      <c r="G27" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2</v>
@@ -2764,7 +2753,7 @@
         <v>2.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="L27" s="8" t="n">
         <v>12.4</v>
@@ -2773,40 +2762,40 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>8</v>
+        <v>88</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>1618.1</v>
+        <v>1618.2</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.1</v>
+        <v>0.7</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>15859.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>913</v>
+        <v>23</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.6</v>
@@ -2825,51 +2814,51 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>313.3</v>
+        <v>513.3</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>15.1</v>
+      <c r="G28" s="13" t="n">
+        <v>15.7</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <v>935.4</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="8" t="n">
-        <v>12.1</v>
+      <c r="N28" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="8" t="n">
+      <c r="Q28" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2881,17 +2870,17 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="8" t="n">
-        <v>645.4</v>
+      <c r="V28" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>11</v>
+        <v>817</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>1891</v>
+        <v>191</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>11.8</v>
@@ -2910,7 +2899,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>323.3</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>28.3</v>
@@ -2930,38 +2919,38 @@
       <c r="I29" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="J29" s="8" t="n">
-        <v>25.2</v>
+      <c r="J29" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="8" t="n">
-        <v>109.7</v>
+        <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>517.1</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>17</v>
+        <v>181.7</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>57.8</v>
+        <v>47.8</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>18.6</v>
@@ -2970,16 +2959,16 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>12.7</v>
+        <v>17.3</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>111.9</v>
+        <v>112.9</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2995,12 +2984,12 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>22848.3</v>
-      </c>
-      <c r="D30" s="17" t="n">
+        <v>2284.8</v>
+      </c>
+      <c r="D30" s="10" t="n">
         <v>131.2</v>
       </c>
-      <c r="E30" s="17" t="n">
+      <c r="E30" s="10" t="n">
         <v>52.2</v>
       </c>
       <c r="F30" s="11" t="n">
@@ -3010,7 +2999,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>216</v>
+        <v>16</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>113.8</v>
@@ -3022,34 +3011,32 @@
         <v>113.5</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>51.2</v>
+        <v>57.2</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="n">
-        <v>6.5</v>
-      </c>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>9489</v>
+        <v>489</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>1113.2</v>
+        <v>113.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>851.7</v>
+        <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>844.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.9</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>99.5</v>
@@ -3080,12 +3067,12 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1532</v>
-      </c>
-      <c r="D31" s="17" t="n">
+        <v>432</v>
+      </c>
+      <c r="D31" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="17" t="n">
+      <c r="E31" s="10" t="n">
         <v>10.4</v>
       </c>
       <c r="F31" s="11" t="n">
@@ -3095,7 +3082,7 @@
         <v>58.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
@@ -3103,50 +3090,48 @@
       <c r="J31" s="3" t="n">
         <v>39.1</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>11.1</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>412.8</v>
+        <v>11.2</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="R31" s="8" t="n">
-        <v>12.5</v>
+        <v>19.3</v>
       </c>
       <c r="S31" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>211.1</v>
-      </c>
-      <c r="V31" s="3" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="8" t="n">
-        <v>16.4</v>
+      <c r="W31" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>7</v>
@@ -3165,28 +3150,28 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>528</v>
+        <v>5280.8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>28.1</v>
+        <v>27.9</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="G32" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="G32" s="11" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>6.1</v>
+        <v>3.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
@@ -3195,33 +3180,33 @@
         <v>10.5</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>11.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="N32" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R32" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V32" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3231,10 +3216,10 @@
         <v>17.9</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3253,25 +3238,25 @@
         <v>349.1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>11.6</v>
+        <v>18.5</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>11.1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>95.90000000000001</v>
+        <v>8.9</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>6.8</v>
@@ -3280,46 +3265,46 @@
         <v>19.9</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>18.6</v>
+        <v>11.9</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
+        <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q33" s="8" t="n">
-        <v>203.5</v>
+      <c r="Q33" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9.9</v>
+        <v>29.9</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
       <c r="V33" s="8" t="n">
-        <v>19.9</v>
+        <v>19.4</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3338,40 +3323,40 @@
         <v>329.9</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>14.7</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="G34" s="11" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>19.7</v>
+      <c r="H34" s="8" t="n">
+        <v>49.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>71.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>18.9</v>
+        <v>1.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="M34" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="M34" s="8" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="8" t="n">
-        <v>7.8</v>
+      <c r="N34" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>99</v>
+        <v>991</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
@@ -3379,8 +3364,8 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>81.90000000000001</v>
+      <c r="R34" s="3" t="n">
+        <v>18.1</v>
       </c>
       <c r="S34" s="8" t="n">
         <v>18.7</v>
@@ -3389,22 +3374,22 @@
         <v>72</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="W34" s="8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="8" t="n">
-        <v>81</v>
+      <c r="X34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3420,7 +3405,7 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>5056.7</v>
+        <v>506.7</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>26.8</v>
@@ -3441,7 +3426,7 @@
         <v>3.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>21.1</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3452,17 +3437,17 @@
       <c r="M35" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>84.8</v>
+      <c r="N35" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1891</v>
+        <v>189</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>38.8</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="R35" s="3" t="n">
         <v>17.6</v>
@@ -3471,7 +3456,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>252</v>
+        <v>52</v>
       </c>
       <c r="U35" s="8" t="n">
         <v>12.8</v>
@@ -3480,13 +3465,13 @@
         <v>20.8</v>
       </c>
       <c r="W35" s="8" t="n">
-        <v>67.90000000000001</v>
+        <v>16.7</v>
       </c>
       <c r="X35" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>168.5</v>
+        <v>683.5</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3508,13 +3493,13 @@
         <v>535.5</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>10.7</v>
+        <v>10.54</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="G36" s="11" t="n">
         <v>15.9</v>
@@ -3537,11 +3522,11 @@
       <c r="M36" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="N36" s="8" t="n">
-        <v>12.6</v>
+      <c r="N36" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.1</v>
@@ -3552,11 +3537,11 @@
       <c r="R36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="8" t="n">
-        <v>65.8</v>
+      <c r="S36" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="U36" s="8" t="n">
         <v>17.9</v>
@@ -3564,14 +3549,14 @@
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="8" t="n">
-        <v>14.6</v>
+      <c r="W36" s="3" t="n">
+        <v>44.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.9</v>
+        <v>11.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="Z36" s="3" t="inlineStr"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3588,25 +3573,25 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2290.9</v>
+        <v>2140.4</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>129.5</v>
+        <v>128.5</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <v>65.7</v>
+        <v>60.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>67.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>167.9</v>
+        <v>141.7</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
@@ -3615,49 +3600,49 @@
         <v>8.5</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>64.5</v>
+        <v>6.4</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>74.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>115.9</v>
+        <v>185.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>811.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>116.9</v>
+        <v>216.9</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>554.5</v>
+        <v>54.5</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>837.1</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>89.8</v>
+        <v>84.8</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>3.9</v>
+        <v>39.4</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3673,13 +3658,13 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.9</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="F38" s="11" t="n">
         <v>18.9</v>
@@ -3693,24 +3678,24 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>20.1</v>
+      <c r="J38" s="3" t="n">
+        <v>90.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>2.8</v>
+        <v>14.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>984.9</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q38" s="3" t="n">
         <v>23.1</v>
@@ -3719,25 +3704,25 @@
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
-        <v>217.6</v>
+        <v>127.6</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>83.5</v>
+        <v>23.3</v>
       </c>
       <c r="U38" s="8" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="8" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>11.9</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3756,10 +3741,10 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5372.9</v>
+        <v>579.9</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>10.9</v>
@@ -3767,12 +3752,12 @@
       <c r="F39" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="3" t="n">
-        <v>12.9</v>
+      <c r="G39" s="11" t="n">
+        <v>15.9</v>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
       <c r="I39" s="3" t="n">
-        <v>6.5</v>
+        <v>5.1</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
@@ -3784,16 +3769,16 @@
         <v>12.7</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>19.2</v>
+        <v>2.5</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>4.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>26.6</v>
@@ -3802,10 +3787,10 @@
         <v>18</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>10.2</v>
+        <v>4.6</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>58146.9</v>
+        <v>92.5</v>
       </c>
       <c r="U39" s="8" t="n">
         <v>18</v>
@@ -3814,7 +3799,7 @@
         <v>12.7</v>
       </c>
       <c r="W39" s="8" t="n">
-        <v>157.5</v>
+        <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
         <v>12.3</v>
@@ -3823,7 +3808,7 @@
         <v>76</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>141.6</v>
+        <v>11.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3839,25 +3824,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>52.5</v>
+        <v>35.5</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>27.6</v>
+        <v>27.1</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="F40" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>12.9</v>
+        <v>11.6</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>21.4</v>
+        <v>29.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
       <c r="K40" s="3" t="n">
@@ -3876,19 +3861,19 @@
         <v>96</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3897,16 +3882,16 @@
         <v>12.7</v>
       </c>
       <c r="W40" s="8" t="n">
-        <v>181.3</v>
+        <v>181.5</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3922,25 +3907,23 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>458.2</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F41" s="15" t="n">
+        <v>451.2</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F41" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="H41" s="8" t="n">
-        <v>51.9</v>
-      </c>
+      <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
-        <v>3.6</v>
+        <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.7</v>
@@ -3949,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>88.7</v>
+        <v>88.3</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>8.6</v>
@@ -3967,13 +3950,13 @@
         <v>23.9</v>
       </c>
       <c r="R41" s="8" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="S41" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>4213.5</v>
+        <v>423.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3982,16 +3965,16 @@
         <v>22</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>1112</v>
+        <v>19.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4007,7 +3990,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>5254.4</v>
+        <v>529.4</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>27.2</v>
@@ -4018,14 +4001,14 @@
       <c r="F42" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="15" t="n">
-        <v>15.2</v>
+      <c r="G42" s="13" t="n">
+        <v>135.2</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>15.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
@@ -4033,13 +4016,13 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="8" t="n">
+      <c r="L42" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4052,24 +4035,24 @@
         <v>26.6</v>
       </c>
       <c r="R42" s="8" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>148.7</v>
+        <v>12.7</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>153.2</v>
+        <v>43.5</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
-        <v>2</v>
+      <c r="V42" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X42" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="X42" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="Y42" s="3" t="inlineStr"/>
@@ -4090,8 +4073,8 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="12" t="inlineStr"/>
+      <c r="D43" s="11" t="inlineStr"/>
+      <c r="E43" s="11" t="inlineStr"/>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
@@ -4129,8 +4112,8 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="12" t="inlineStr"/>
-      <c r="E44" s="12" t="inlineStr"/>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
       <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
@@ -4168,23 +4151,23 @@
       <c r="C45" s="3" t="n">
         <v>1911.2</v>
       </c>
-      <c r="D45" s="17" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>41.8</v>
+      <c r="D45" s="11" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>41.6</v>
       </c>
       <c r="F45" s="11" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7.9</v>
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.4</v>
+        <v>119.9</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
@@ -4193,19 +4176,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>212.9</v>
+        <v>22.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>31.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>98.59999999999999</v>
@@ -4220,20 +4203,22 @@
         <v>216.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>851.9</v>
+        <v>831.9</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>67.5</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>200.8</v>
+      </c>
       <c r="Y45" s="3" t="n">
         <v>1263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>331.9</v>
+        <v>2331.8</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4249,12 +4234,12 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>5417.8</v>
-      </c>
-      <c r="D46" s="17" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="D46" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="E46" s="17" t="n">
+      <c r="E46" s="11" t="n">
         <v>10.4</v>
       </c>
       <c r="F46" s="11" t="n">
@@ -4269,15 +4254,15 @@
       <c r="I46" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="J46" s="8" t="n">
-        <v>52.4</v>
+      <c r="J46" s="3" t="n">
+        <v>62.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="8" t="n">
-        <v>41.1</v>
+        <v>11181.9</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>12.8</v>
@@ -4289,29 +4274,29 @@
         <v>6.4</v>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>247.1</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>24.7</v>
+      </c>
+      <c r="R46" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>654.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
-      </c>
+        <v>54.1</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Y46" s="3" t="n">
-        <v>1860.8</v>
+        <v>1862.4</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -170,7 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -898,8 +898,8 @@
       <c r="L5" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="8" t="n">
-        <v>8149.4</v>
+      <c r="M5" s="13" t="n">
+        <v>81.494</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -978,7 +978,7 @@
       <c r="K6" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="13" t="n">
         <v>1.1</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -1163,8 +1163,8 @@
       <c r="P8" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q8" s="8" t="n">
-        <v>2719.4</v>
+      <c r="Q8" s="13" t="n">
+        <v>27.194</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>18.9</v>
@@ -1230,13 +1230,13 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="10" t="n">
         <v>56.7</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="10" t="n">
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1248,10 +1248,10 @@
       <c r="P9" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="10" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="10" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1263,10 +1263,10 @@
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="10" t="n">
         <v>8.4</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1316,10 +1316,10 @@
         <v>418.1</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="8" t="n">
+      <c r="L10" s="10" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="M10" s="10" t="n">
         <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
@@ -1331,10 +1331,10 @@
       <c r="P10" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="10" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="S10" s="8" t="n">
@@ -1346,10 +1346,10 @@
       <c r="U10" s="3" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="10" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1404,7 +1404,7 @@
       <c r="L11" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="13" t="n">
         <v>1.2</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1486,8 +1486,8 @@
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="8" t="n">
-        <v>191.7</v>
+      <c r="L12" s="13" t="n">
+        <v>19.17</v>
       </c>
       <c r="M12" s="8" t="n">
         <v>22.1</v>
@@ -1586,7 +1586,7 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="8" t="n">
+      <c r="Q13" s="13" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1604,8 +1604,8 @@
       <c r="V13" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>791.5</v>
+      <c r="W13" s="13" t="n">
+        <v>79.15000000000001</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>29.1</v>
@@ -1659,7 +1659,7 @@
       <c r="L14" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="13" t="n">
         <v>83</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1671,7 +1671,7 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="13" t="n">
         <v>46.9</v>
       </c>
       <c r="R14" s="8" t="n">
@@ -1684,7 +1684,7 @@
       <c r="U14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="V14" s="8" t="n">
+      <c r="V14" s="13" t="n">
         <v>59.5</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1757,7 +1757,7 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="8" t="n">
+      <c r="R15" s="13" t="n">
         <v>72.59999999999999</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1769,7 +1769,7 @@
       <c r="U15" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="13" t="n">
         <v>2</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1821,13 +1821,13 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="10" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="10" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1839,10 +1839,10 @@
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="10" t="n">
         <v>1111</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="10" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1854,10 +1854,10 @@
       <c r="U16" s="3" t="n">
         <v>60.9</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="10" t="n">
         <v>9.5</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="10" t="n">
         <v>801.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1907,10 +1907,10 @@
         <v>871.8</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="10" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="8" t="n">
@@ -1922,10 +1922,10 @@
       <c r="P17" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="10" t="n">
         <v>16.9</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1937,10 +1937,10 @@
       <c r="U17" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="10" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.9</v>
       </c>
       <c r="X17" s="8" t="n">
@@ -1992,10 +1992,10 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>1666.6</v>
-      </c>
-      <c r="M18" s="3" t="n">
+      <c r="L18" s="13" t="n">
+        <v>16.666</v>
+      </c>
+      <c r="M18" s="13" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="N18" s="8" t="n">
@@ -2007,10 +2007,10 @@
       <c r="P18" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="3" t="n">
+      <c r="Q18" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="11" t="n">
         <v>17.3</v>
       </c>
       <c r="S18" s="8" t="n">
@@ -2022,7 +2022,7 @@
       <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="11" t="n">
         <v>21</v>
       </c>
       <c r="W18" s="3" t="n">
@@ -2077,8 +2077,8 @@
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="8" t="n">
-        <v>111.2</v>
+      <c r="L19" s="13" t="n">
+        <v>11.12</v>
       </c>
       <c r="M19" s="8" t="n">
         <v>11</v>
@@ -2092,10 +2092,10 @@
       <c r="P19" s="8" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="11" t="n">
         <v>18</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2107,7 +2107,7 @@
       <c r="U19" s="8" t="n">
         <v>7.2</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="11" t="n">
         <v>21.2</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2165,8 +2165,8 @@
       <c r="L20" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>211</v>
+      <c r="M20" s="13" t="n">
+        <v>21.1</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>13</v>
@@ -2177,10 +2177,10 @@
       <c r="P20" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2192,10 +2192,10 @@
       <c r="U20" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="13" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="X20" s="8" t="n">
@@ -2262,10 +2262,10 @@
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
+      <c r="Q21" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2277,7 +2277,7 @@
       <c r="U21" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
@@ -2347,10 +2347,10 @@
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
@@ -2362,7 +2362,7 @@
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="11" t="n">
         <v>22.5</v>
       </c>
       <c r="W22" s="8" t="n">
@@ -2414,13 +2414,13 @@
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="10" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2432,11 +2432,11 @@
       <c r="P23" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="11" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="R23" s="11" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>78.09999999999999</v>
@@ -2447,10 +2447,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="11" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="10" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2500,10 +2500,10 @@
         <v>16.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2515,10 +2515,10 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2530,10 +2530,10 @@
       <c r="U24" s="8" t="n">
         <v>177.1</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="10" t="n">
         <v>1.7</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2588,7 +2588,7 @@
       <c r="L25" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="13" t="n">
         <v>2.9</v>
       </c>
       <c r="N25" s="8" t="n">
@@ -2600,7 +2600,7 @@
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q25" s="13" t="n">
         <v>41.5</v>
       </c>
       <c r="R25" s="8" t="n">
@@ -2615,11 +2615,11 @@
       <c r="U25" s="8" t="n">
         <v>113.2</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>216.9</v>
+      <c r="W25" s="13" t="n">
+        <v>21.69</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>16.8</v>
@@ -2670,8 +2670,8 @@
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="8" t="n">
-        <v>109.4</v>
+      <c r="L26" s="13" t="n">
+        <v>10.94</v>
       </c>
       <c r="M26" s="8" t="n">
         <v>10.2</v>
@@ -2700,7 +2700,7 @@
       <c r="U26" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="11" t="n">
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2773,8 +2773,8 @@
       <c r="Q27" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="8" t="n">
-        <v>1618.2</v>
+      <c r="R27" s="13" t="n">
+        <v>16.182</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>11.2</v>
@@ -2785,10 +2785,10 @@
       <c r="U27" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="13" t="n">
         <v>0.7</v>
       </c>
       <c r="X27" s="8" t="n">
@@ -2840,8 +2840,8 @@
       <c r="K28" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L28" s="8" t="n">
-        <v>935.4</v>
+      <c r="L28" s="13" t="n">
+        <v>93.53999999999999</v>
       </c>
       <c r="M28" s="8" t="n">
         <v>13.3</v>
@@ -2870,7 +2870,7 @@
       <c r="U28" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2943,8 +2943,8 @@
       <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="8" t="n">
-        <v>181.7</v>
+      <c r="R29" s="13" t="n">
+        <v>18.17</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>12</v>
@@ -2955,7 +2955,7 @@
       <c r="U29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="11" t="n">
         <v>22.8</v>
       </c>
       <c r="W29" s="3" t="n">
@@ -3007,13 +3007,13 @@
       <c r="J30" s="3" t="n">
         <v>119.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>113.5</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="10" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="10" t="n">
         <v>56.7</v>
       </c>
       <c r="N30" s="3" t="inlineStr"/>
@@ -3023,10 +3023,10 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="10" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="10" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3038,10 +3038,10 @@
       <c r="U30" s="3" t="n">
         <v>55.9</v>
       </c>
-      <c r="V30" s="3" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="W30" s="3" t="n">
+      <c r="V30" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="W30" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3091,10 +3091,10 @@
         <v>39.1</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="10" t="n">
         <v>11.5</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="10" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3106,10 +3106,10 @@
       <c r="P31" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="10" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="8" t="n">
+      <c r="R31" s="10" t="n">
         <v>19.3</v>
       </c>
       <c r="S31" s="8" t="n">
@@ -3121,10 +3121,10 @@
       <c r="U31" s="3" t="n">
         <v>111.1</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="10" t="n">
         <v>16.9</v>
       </c>
       <c r="X31" s="8" t="n">
@@ -3176,7 +3176,7 @@
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="8" t="n">
+      <c r="L32" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="M32" s="8" t="n">
@@ -3194,7 +3194,7 @@
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3261,7 +3261,7 @@
       <c r="K33" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="11" t="n">
         <v>19.9</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3279,7 +3279,7 @@
       <c r="Q33" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3346,7 +3346,7 @@
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="11" t="n">
         <v>12</v>
       </c>
       <c r="M34" s="8" t="n">
@@ -3364,7 +3364,7 @@
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="11" t="n">
         <v>18.1</v>
       </c>
       <c r="S34" s="8" t="n">
@@ -3376,7 +3376,7 @@
       <c r="U34" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W34" s="3" t="n">
@@ -3431,7 +3431,7 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="11" t="n">
         <v>13</v>
       </c>
       <c r="M35" s="3" t="n">
@@ -3449,7 +3449,7 @@
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3516,7 +3516,7 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3534,7 +3534,7 @@
       <c r="Q36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="11" t="n">
         <v>17.1</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3549,7 +3549,7 @@
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="13" t="n">
         <v>44.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3596,13 +3596,13 @@
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>8.5</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>65</v>
-      </c>
-      <c r="M37" s="3" t="n">
+      <c r="L37" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="M37" s="10" t="n">
         <v>6.4</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3614,11 +3614,11 @@
       <c r="P37" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="10" t="n">
         <v>185.9</v>
       </c>
-      <c r="R37" s="3" t="n">
-        <v>82.90000000000001</v>
+      <c r="R37" s="11" t="n">
+        <v>88.8</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
@@ -3629,10 +3629,10 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="10" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="10" t="n">
         <v>837.1</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3682,10 +3682,10 @@
         <v>90.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="8" t="n">
+      <c r="L38" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="10" t="n">
         <v>12.8</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3697,10 +3697,10 @@
       <c r="P38" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3712,10 +3712,10 @@
       <c r="U38" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="8" t="n">
+      <c r="W38" s="10" t="n">
         <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
@@ -3762,13 +3762,13 @@
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="8" t="n">
+      <c r="M39" s="13" t="n">
         <v>2.5</v>
       </c>
       <c r="N39" s="3" t="n">
@@ -3798,7 +3798,7 @@
       <c r="V39" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
@@ -3845,7 +3845,7 @@
         <v>29.4</v>
       </c>
       <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="8" t="n">
@@ -3863,7 +3863,7 @@
       <c r="P40" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="13" t="n">
         <v>82</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3881,8 +3881,8 @@
       <c r="V40" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>181.5</v>
+      <c r="W40" s="11" t="n">
+        <v>18.15</v>
       </c>
       <c r="X40" s="3" t="n">
         <v>29.3</v>
@@ -3928,10 +3928,10 @@
       <c r="J41" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K41" s="3" t="n">
+      <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="13" t="n">
         <v>88.3</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3964,7 +3964,7 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4013,13 +4013,13 @@
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4034,7 +4034,7 @@
       <c r="Q42" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="13" t="n">
         <v>87.59999999999999</v>
       </c>
       <c r="S42" s="8" t="n">
@@ -4049,7 +4049,7 @@
       <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4080,19 +4080,19 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="16" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
+      <c r="Q43" s="16" t="inlineStr"/>
+      <c r="R43" s="16" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="V43" s="16" t="inlineStr"/>
+      <c r="W43" s="11" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4119,19 +4119,19 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="16" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="16" t="inlineStr"/>
+      <c r="R44" s="16" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="16" t="inlineStr"/>
+      <c r="W44" s="11" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4172,13 +4172,13 @@
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="10" t="n">
         <v>22.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4190,10 +4190,10 @@
       <c r="P45" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="10" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="10" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4205,11 +4205,11 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="10" t="n">
         <v>831.9</v>
       </c>
-      <c r="W45" s="3" t="n">
-        <v>67.5</v>
+      <c r="W45" s="11" t="n">
+        <v>66.5</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>200.8</v>
@@ -4258,10 +4258,10 @@
         <v>62.1</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="8" t="n">
+      <c r="L46" s="10" t="n">
         <v>11181.9</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="10" t="n">
         <v>1</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4273,10 +4273,10 @@
       <c r="P46" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="10" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="8" t="n">
+      <c r="R46" s="10" t="n">
         <v>88.59999999999999</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4286,10 +4286,10 @@
         <v>54.1</v>
       </c>
       <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -2013,14 +2013,14 @@
       <c r="R18" s="11" t="n">
         <v>17.3</v>
       </c>
-      <c r="S18" s="8" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v>17.9</v>
+      <c r="S18" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T18" s="11" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="U18" s="11" t="n">
+        <v>13.5</v>
       </c>
       <c r="V18" s="11" t="n">
         <v>21</v>
@@ -2098,14 +2098,14 @@
       <c r="R19" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v>7.2</v>
+      <c r="S19" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="U19" s="11" t="n">
+        <v>12.8</v>
       </c>
       <c r="V19" s="11" t="n">
         <v>21.2</v>
@@ -2183,14 +2183,14 @@
       <c r="R20" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T20" s="3" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="U20" s="3" t="n">
-        <v>22.4</v>
+      <c r="S20" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="T20" s="11" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="U20" s="11" t="n">
+        <v>16</v>
       </c>
       <c r="V20" s="11" t="n">
         <v>22.2</v>
@@ -2268,14 +2268,14 @@
       <c r="R21" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="S21" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>16.2</v>
+      <c r="S21" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="U21" s="11" t="n">
+        <v>11.9</v>
       </c>
       <c r="V21" s="11" t="n">
         <v>19.8</v>
@@ -2353,14 +2353,14 @@
       <c r="R22" s="11" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="8" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>14.8</v>
+      <c r="S22" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T22" s="11" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="U22" s="11" t="n">
+        <v>10.7</v>
       </c>
       <c r="V22" s="11" t="n">
         <v>22.5</v>
@@ -2521,14 +2521,14 @@
       <c r="R24" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v>177.1</v>
+      <c r="S24" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T24" s="11" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U24" s="11" t="n">
+        <v>13.1</v>
       </c>
       <c r="V24" s="11" t="n">
         <v>21.3</v>
@@ -2618,16 +2618,16 @@
       <c r="V25" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="13" t="n">
-        <v>21.69</v>
-      </c>
-      <c r="X25" s="8" t="n">
+      <c r="W25" s="11" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X25" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y25" s="3" t="n">
+      <c r="Y25" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="Z25" s="3" t="n">
+      <c r="Z25" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -3517,18 +3517,18 @@
         <v>0</v>
       </c>
       <c r="L36" s="11" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N36" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="M36" s="11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N36" s="11" t="n">
         <v>12.4</v>
       </c>
-      <c r="O36" s="3" t="n">
+      <c r="O36" s="11" t="n">
         <v>99</v>
       </c>
-      <c r="P36" s="3" t="n">
+      <c r="P36" s="11" t="n">
         <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
@@ -3600,7 +3600,7 @@
         <v>8.5</v>
       </c>
       <c r="L37" s="11" t="n">
-        <v>66</v>
+        <v>65.7</v>
       </c>
       <c r="M37" s="10" t="n">
         <v>6.4</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,19 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,10 +155,28 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,22 +790,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>301.2</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="E4" s="11" t="n">
+        <v>391.2</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="8" t="n">
+      <c r="G4" s="12" t="n">
         <v>81.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -808,52 +814,52 @@
         <v>4.9</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>9.9</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>11.9</v>
+      <c r="N4" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>928</v>
+        <v>98</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>14.1</v>
+      <c r="S4" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>462.5</v>
-      </c>
-      <c r="U4" s="8" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="U4" s="12" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>73.8</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -871,20 +877,20 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="8" t="n">
-        <v>59.4</v>
+      <c r="G5" s="9" t="n">
+        <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -893,13 +899,13 @@
         <v>2.6</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="13" t="n">
-        <v>81.494</v>
+      <c r="M5" s="17" t="n">
+        <v>11.94</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>12.9</v>
@@ -910,7 +916,7 @@
       <c r="P5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q5" s="8" t="n">
+      <c r="Q5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="R5" s="3" t="n">
@@ -922,21 +928,23 @@
       <c r="T5" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="U5" s="3" t="inlineStr"/>
-      <c r="V5" s="8" t="n">
+      <c r="U5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X5" s="3" t="n">
+      <c r="W5" s="9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X5" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="Y5" s="3" t="n">
+      <c r="Y5" s="9" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z5" s="3" t="n">
-        <v>469.5</v>
+      <c r="Z5" s="9" t="n">
+        <v>4.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -954,20 +962,20 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F6" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G6" s="11" t="n">
+      <c r="E6" s="9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -976,46 +984,46 @@
         <v>1.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M6" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="M6" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P6" s="3" t="n">
+      <c r="N6" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="O6" s="9" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="P6" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="Q6" s="12" t="n">
         <v>15.4</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>92</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V6" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>24.6</v>
+      <c r="W6" s="12" t="n">
+        <v>15.3</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>95</v>
@@ -1039,74 +1047,74 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>12.9</v>
+      <c r="H7" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>11.9</v>
+        <v>1.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>5</v>
+      <c r="M7" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N7" s="12" t="n">
+        <v>15</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="8" t="n">
+      <c r="R7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="8" t="n">
-        <v>17.7</v>
+      <c r="S7" s="3" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
+      <c r="X7" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1124,20 +1132,20 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="11" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="D8" s="9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>7.2</v>
+        <v>17.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1148,43 +1156,43 @@
       <c r="K8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="M8" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1.2</v>
+        <v>12.7</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q8" s="13" t="n">
-        <v>27.194</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q8" s="12" t="n">
+        <v>27.4</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>18.9</v>
+        <v>18.4</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1.9</v>
+        <v>19.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
+      <c r="V8" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W8" s="17" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="X8" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1207,73 +1215,71 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>43927.4</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>1749.7</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="10" t="n">
         <v>55</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>73.90000000000001</v>
+      <c r="G9" s="3" t="n">
+        <v>13.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12.6</v>
+        <v>140.6</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="K9" s="10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>56.7</v>
+        <v>7.7</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>57.3</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>55.2</v>
+        <v>551.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>55.1</v>
+        <v>766.1</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>684.8</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>9.6</v>
-      </c>
+        <v>484.9</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="10" t="n">
         <v>101.5</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>85.3</v>
+        <v>185.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>3801.5</v>
+        <v>380.5</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="10" t="n">
+      <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
       <c r="W9" s="10" t="n">
-        <v>8.4</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9414.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1292,18 +1298,18 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>349.9</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>8349.9</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="10" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1312,41 +1318,41 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>418.1</v>
+      <c r="J10" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="N10" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>96.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.5</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" s="10" t="n">
         <v>20.3</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S10" s="8" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="S10" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>26.1</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="V10" s="10" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
       <c r="W10" s="10" t="n">
@@ -1358,9 +1364,7 @@
       <c r="Y10" s="3" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="Z10" s="3" t="n">
-        <v>6</v>
-      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1377,17 +1381,17 @@
       <c r="C11" s="3" t="n">
         <v>509.3</v>
       </c>
-      <c r="D11" s="8" t="n">
+      <c r="D11" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>16.6</v>
+      <c r="E11" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>18.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
@@ -1399,49 +1403,49 @@
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.2</v>
+        <v>26</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>1.2</v>
+        <v>11.4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q11" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q11" s="12" t="n">
         <v>26.3</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S11" s="8" t="n">
-        <v>17.9</v>
+      <c r="S11" s="12" t="n">
+        <v>14.4</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>512</v>
-      </c>
-      <c r="U11" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="U11" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="8" t="n">
+      <c r="W11" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="3" t="n">
-        <v>19.6</v>
+      <c r="X11" s="12" t="n">
+        <v>17.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>9</v>
@@ -1460,37 +1464,37 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>506.1</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E12" s="3" t="n">
+        <v>508.7</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="13" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="F12" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G12" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="L12" s="13" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>22.1</v>
+      <c r="L12" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>13.2</v>
@@ -1504,10 +1508,10 @@
       <c r="Q12" s="3" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="8" t="n">
+      <c r="S12" s="12" t="n">
         <v>12.9</v>
       </c>
       <c r="T12" s="3" t="n">
@@ -1516,17 +1520,17 @@
       <c r="U12" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>12.2</v>
@@ -1547,38 +1551,38 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>99.40000000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>8.5</v>
+        <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>23.6</v>
+        <v>21.6</v>
+      </c>
+      <c r="N13" s="12" t="n">
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>98</v>
@@ -1586,34 +1590,34 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="13" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="R13" s="3" t="n">
+      <c r="Q13" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R13" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>11.8</v>
+        <v>18.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>85.5</v>
+        <v>185.4</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="13" t="n">
-        <v>79.15000000000001</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y13" s="3" t="n">
+      <c r="W13" s="9" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X13" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y13" s="9" t="n">
         <v>84</v>
       </c>
-      <c r="Z13" s="3" t="n">
+      <c r="Z13" s="9" t="n">
         <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1632,35 +1636,35 @@
       <c r="C14" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E14" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="G14" s="8" t="n">
+      <c r="D14" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="K14" s="8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>83</v>
+      <c r="I14" s="12" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>14.8</v>
@@ -1669,35 +1673,37 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q14" s="13" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S14" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>197</v>
+      </c>
       <c r="U14" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="V14" s="13" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="X14" s="8" t="n">
+      <c r="V14" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W14" s="12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X14" s="12" t="n">
         <v>16</v>
       </c>
       <c r="Y14" s="3" t="n">
         <v>95</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1715,17 +1721,17 @@
       <c r="C15" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>15.6</v>
+      <c r="E15" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>50.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1739,8 +1745,8 @@
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="3" t="n">
-        <v>27.4</v>
+      <c r="L15" s="17" t="n">
+        <v>77.40000000000001</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
@@ -1757,32 +1763,32 @@
       <c r="Q15" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="13" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>15.9</v>
+      <c r="R15" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <v>15.7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="V15" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X15" s="3" t="n">
+      <c r="U15" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="X15" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Y15" s="3" t="n">
+      <c r="Y15" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="Z15" s="3" t="n">
-        <v>8.699999999999999</v>
+      <c r="Z15" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1797,26 +1803,24 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>2227.1</v>
-      </c>
+      <c r="C16" s="3" t="inlineStr"/>
       <c r="D16" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="G16" s="11" t="n">
+      <c r="E16" s="9" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>39.5</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>21.8</v>
@@ -1831,10 +1835,10 @@
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>57.1</v>
+        <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>399</v>
+        <v>489.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
@@ -1842,32 +1846,32 @@
       <c r="Q16" s="10" t="n">
         <v>1111</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="9" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>78.7</v>
+        <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.9</v>
+        <v>310.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="V16" s="10" t="n">
-        <v>9.5</v>
+        <v>603.9</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>98.2</v>
       </c>
       <c r="W16" s="10" t="n">
-        <v>801.7</v>
+        <v>801.9</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>33.9</v>
+        <v>33.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1885,16 +1889,16 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="10" t="n">
+      <c r="E17" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1903,8 +1907,8 @@
       <c r="I17" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>871.8</v>
+      <c r="J17" s="3" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="10" t="n">
@@ -1913,44 +1917,44 @@
       <c r="M17" s="10" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="8" t="n">
+      <c r="N17" s="12" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.8</v>
+        <v>7.4</v>
       </c>
       <c r="Q17" s="10" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="10" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S17" s="8" t="n">
+      <c r="R17" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>15.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>42</v>
+        <v>362</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="V17" s="10" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
       <c r="W17" s="10" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X17" s="8" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X17" s="12" t="n">
         <v>16.5</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>72.8</v>
+        <v>872.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1966,25 +1970,25 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
+        <v>845.5</v>
+      </c>
+      <c r="D18" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <v>13.8</v>
+      <c r="G18" s="12" t="n">
+        <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>6.7</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -1992,50 +1996,50 @@
       <c r="K18" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="13" t="n">
-        <v>16.666</v>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="P18" s="3" t="n">
+      <c r="L18" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="P18" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="11" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="S18" s="11" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="T18" s="11" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="U18" s="11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="V18" s="11" t="n">
+      <c r="R18" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="S18" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U18" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="3" t="n">
+      <c r="X18" s="12" t="n">
         <v>19.6</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>110.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2051,19 +2055,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>531.9</v>
-      </c>
-      <c r="D19" s="11" t="n">
+        <v>531.1</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>17.4</v>
+      <c r="G19" s="3" t="n">
+        <v>17.9</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2077,10 +2081,10 @@
       <c r="K19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="13" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="M19" s="8" t="n">
+      <c r="L19" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2089,38 +2093,38 @@
       <c r="O19" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q19" s="11" t="n">
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S19" s="11" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="T19" s="11" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="U19" s="11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V19" s="11" t="n">
+      <c r="S19" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="U19" s="12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V19" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="X19" s="3" t="n">
+      <c r="W19" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X19" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y19" s="3" t="n">
+      <c r="Y19" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="Z19" s="3" t="n">
-        <v>16.6</v>
+      <c r="Z19" s="9" t="n">
+        <v>6.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2138,74 +2142,74 @@
       <c r="C20" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="9" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="9" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="8" t="n">
-        <v>33.5</v>
+      <c r="I20" s="12" t="n">
+        <v>33.3</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L20" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="13" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="N20" s="3" t="n">
+      <c r="M20" s="17" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N20" s="12" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>198</v>
+        <v>28</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="11" t="n">
+      <c r="R20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="S20" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="T20" s="11" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="U20" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="V20" s="11" t="n">
+      <c r="S20" s="3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="U20" s="12" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="13" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="X20" s="8" t="n">
-        <v>299.7</v>
+      <c r="W20" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X20" s="12" t="n">
+        <v>19.1</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>71</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2223,74 +2227,74 @@
       <c r="C21" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D21" s="11" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G21" s="11" t="n">
+      <c r="D21" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M21" s="8" t="n">
+      <c r="L21" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>15.9</v>
+      <c r="N21" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="11" t="n">
+      <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="11" t="n">
+      <c r="R21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="S21" s="11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T21" s="11" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="U21" s="11" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="V21" s="11" t="n">
+      <c r="S21" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
       <c r="W21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="X21" s="3" t="n">
-        <v>20</v>
+      <c r="X21" s="12" t="n">
+        <v>0.9</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>87</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2306,40 +2310,40 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9489</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>989</v>
+      </c>
+      <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>18.7</v>
+      <c r="E22" s="17" t="n">
+        <v>-7.8</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>13.9</v>
+        <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>11.2</v>
+        <v>8</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>12.3</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>14.9</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>99</v>
@@ -2347,29 +2351,29 @@
       <c r="P22" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="11" t="n">
+      <c r="R22" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="S22" s="11" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="T22" s="11" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="U22" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="V22" s="11" t="n">
+      <c r="S22" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="3" t="n">
-        <v>53.8</v>
+      <c r="X22" s="12" t="n">
+        <v>13.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>50.5</v>
@@ -2391,55 +2395,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>12320.3</v>
-      </c>
-      <c r="D23" s="10" t="n">
+        <v>2322.3</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="E23" s="10" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F23" s="10" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>75.40000000000001</v>
+      <c r="G23" s="3" t="n">
+        <v>75.90000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.4</v>
+        <v>14.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>20.8</v>
+        <v>28.8</v>
       </c>
       <c r="K23" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="10" t="n">
-        <v>2.5</v>
+      <c r="L23" s="9" t="n">
+        <v>62.5</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>61.8</v>
+        <v>161.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>293</v>
+        <v>2493</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q23" s="11" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="11" t="n">
-        <v>88.59999999999999</v>
+      <c r="R23" s="10" t="n">
+        <v>85</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2447,7 +2451,7 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="11" t="n">
+      <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
       <c r="W23" s="10" t="n">
@@ -2476,38 +2480,40 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2464.1</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F24" s="11" t="n">
+        <v>464.1</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="8" t="n">
-        <v>57.1</v>
+      <c r="G24" s="9" t="n">
+        <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
       <c r="M24" s="10" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.4</v>
+        <v>11.9</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2515,32 +2521,32 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="10" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="11" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T24" s="11" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U24" s="11" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="V24" s="11" t="n">
+      <c r="S24" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="W24" s="10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X24" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X24" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>68.3</v>
+        <v>58.3</v>
       </c>
       <c r="Z24" s="3" t="n">
         <v>8.199999999999999</v>
@@ -2559,75 +2565,75 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1488.9</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F25" s="11" t="n">
+        <v>488.9</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>13.6</v>
+      <c r="G25" s="12" t="n">
+        <v>10.9</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>49.7</v>
+        <v>4.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L25" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="M25" s="13" t="n">
+      <c r="M25" s="17" t="n">
         <v>2.9</v>
       </c>
-      <c r="N25" s="8" t="n">
-        <v>19.4</v>
+      <c r="N25" s="3" t="n">
+        <v>14</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>18</v>
+        <v>0.4</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q25" s="13" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v>113.2</v>
-      </c>
-      <c r="V25" s="11" t="n">
+      <c r="Q25" s="9" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S25" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="T25" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="11" t="n">
+      <c r="W25" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="X25" s="11" t="n">
+      <c r="X25" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y25" s="11" t="n">
+      <c r="Y25" s="9" t="n">
         <v>66</v>
       </c>
-      <c r="Z25" s="11" t="n">
+      <c r="Z25" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -2646,23 +2652,23 @@
       <c r="C26" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="9" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.3</v>
+        <v>6.6</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>23.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
@@ -2670,50 +2676,50 @@
       <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="13" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="M26" s="8" t="n">
+      <c r="L26" s="9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q26" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="8" t="n">
+      <c r="R26" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T26" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="V26" s="11" t="n">
+      <c r="S26" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T26" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="U26" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="3" t="n">
+      <c r="W26" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X26" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>111.8</v>
+      <c r="X26" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y26" s="9" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="Z26" s="9" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2731,16 +2737,16 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F27" s="11" t="n">
+      <c r="D27" s="9" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G27" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2750,55 +2756,55 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L27" s="8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14</v>
+        <v>1.4</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q27" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q27" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="13" t="n">
-        <v>16.182</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V27" s="11" t="n">
+      <c r="R27" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="S27" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="T27" s="9" t="n">
+        <v>90.3</v>
+      </c>
+      <c r="U27" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="X27" s="8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>1.6</v>
+      <c r="W27" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X27" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y27" s="9" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="Z27" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2816,74 +2822,74 @@
       <c r="C28" s="3" t="n">
         <v>513.3</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F28" s="11" t="n">
+      <c r="E28" s="9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="13" t="n">
-        <v>15.7</v>
+      <c r="G28" s="12" t="n">
+        <v>15.9</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L28" s="13" t="n">
-        <v>93.53999999999999</v>
-      </c>
-      <c r="M28" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M28" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="O28" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P28" s="3" t="n">
+      <c r="N28" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P28" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q28" s="3" t="n">
+      <c r="Q28" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="T28" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V28" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="W28" s="3" t="n">
+      <c r="S28" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T28" s="9" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="U28" s="9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="V28" s="9" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W28" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>817</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>11.8</v>
+      <c r="X28" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y28" s="9" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Z28" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2899,19 +2905,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>323.3</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>523.3</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <v>18.1</v>
+      <c r="G29" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2925,50 +2931,50 @@
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>196</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q29" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q29" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="13" t="n">
-        <v>18.17</v>
-      </c>
-      <c r="S29" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="T29" s="3" t="n">
+      <c r="R29" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" s="9" t="n">
         <v>47.8</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="V29" s="11" t="n">
+      <c r="V29" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="3" t="n">
+      <c r="W29" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Y29" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z29" s="3" t="n">
-        <v>112.9</v>
+      <c r="X29" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y29" s="9" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="Z29" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2984,46 +2990,48 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>131.2</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="F30" s="11" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="11" t="n">
+      <c r="G30" s="3" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>113.8</v>
+        <v>13.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119.5</v>
+        <v>19.5</v>
       </c>
       <c r="K30" s="10" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="L30" s="10" t="n">
-        <v>57.2</v>
+        <v>13.5</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>57.9</v>
       </c>
       <c r="M30" s="10" t="n">
         <v>56.7</v>
       </c>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
       <c r="O30" s="3" t="n">
         <v>489</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="Q30" s="9" t="n">
         <v>113.2</v>
       </c>
       <c r="R30" s="10" t="n">
@@ -3036,22 +3044,22 @@
         <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>55.9</v>
-      </c>
-      <c r="V30" s="11" t="n">
-        <v>100</v>
+        <v>35.4</v>
+      </c>
+      <c r="V30" s="9" t="n">
+        <v>99.5</v>
       </c>
       <c r="W30" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="X30" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="Z30" s="3" t="n">
-        <v>35</v>
+      <c r="X30" s="9" t="n">
+        <v>522</v>
+      </c>
+      <c r="Y30" s="9" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="Z30" s="9" t="n">
+        <v>506.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3067,74 +3075,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>432</v>
-      </c>
-      <c r="D31" s="11" t="n">
+        <v>452</v>
+      </c>
+      <c r="D31" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="10" t="n">
+      <c r="E31" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="8" t="n">
-        <v>58.4</v>
+      <c r="G31" s="9" t="n">
+        <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>39.1</v>
+        <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="10" t="n">
+      <c r="L31" s="9" t="n">
         <v>11.5</v>
       </c>
       <c r="M31" s="10" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>97.8</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q31" s="10" t="n">
+      <c r="N31" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="R31" s="10" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S31" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S31" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U31" s="3" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="V31" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="U31" s="12" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="W31" s="10" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>7</v>
+        <v>16.4</v>
+      </c>
+      <c r="X31" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y31" s="9" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z31" s="9" t="n">
+        <v>4.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3150,76 +3158,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>5280.8</v>
-      </c>
-      <c r="D32" s="11" t="n">
+        <v>520</v>
+      </c>
+      <c r="D32" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" s="9" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L32" s="11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>12.1</v>
+      <c r="L32" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="M32" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>12.4</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R32" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>26.46</v>
+      </c>
+      <c r="R32" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>9.699999999999999</v>
+      <c r="S32" s="9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="T32" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>13.7</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>170</v>
-      </c>
+      <c r="X32" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
       <c r="Z32" s="3" t="n">
-        <v>4</v>
+        <v>171.8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3237,23 +3243,23 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="13" t="n">
-        <v>11.1</v>
+      <c r="G33" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>8.9</v>
+        <v>2.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>16.5</v>
+        <v>1.9</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
@@ -3261,50 +3267,50 @@
       <c r="K33" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="N33" s="3" t="n">
-        <v>16.5</v>
+      <c r="L33" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N33" s="12" t="n">
+        <v>18.5</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R33" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="R33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.8</v>
+      <c r="S33" s="9" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T33" s="9" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W33" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="X33" s="12" t="n">
+        <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>83</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3322,71 +3328,71 @@
       <c r="C34" s="3" t="n">
         <v>329.9</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>49.7</v>
+      <c r="H34" s="12" t="n">
+        <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>71.5</v>
+        <v>11.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>1.9</v>
+        <v>8.9</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="M34" s="8" t="n">
+      <c r="L34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="3" t="n">
-        <v>1.7</v>
+      <c r="N34" s="12" t="n">
+        <v>7.8</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>991</v>
+        <v>99</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="11" t="n">
+      <c r="R34" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="T34" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V34" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="3" t="n">
+      <c r="S34" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T34" s="9" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="U34" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="3" t="n">
+      <c r="X34" s="12" t="n">
         <v>18</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3407,16 +3413,16 @@
       <c r="C35" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="9" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3431,47 +3437,47 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N35" s="3" t="n">
+      <c r="M35" s="9" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N35" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="O35" s="3" t="n">
-        <v>189</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3" t="n">
+      <c r="O35" s="9" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q35" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="11" t="n">
+      <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T35" s="9" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="U35" s="9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W35" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="X35" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="T35" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W35" s="8" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>16.8</v>
-      </c>
       <c r="Y35" s="3" t="n">
-        <v>683.5</v>
+        <v>68.3</v>
       </c>
       <c r="Z35" s="3" t="n">
         <v>8</v>
@@ -3492,73 +3498,75 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="11" t="n">
-        <v>10.54</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G36" s="11" t="n">
+      <c r="E36" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G36" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K36" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="P36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="11" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M36" s="11" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="N36" s="11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O36" s="11" t="n">
-        <v>99</v>
-      </c>
-      <c r="P36" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="R36" s="11" t="n">
+      <c r="Q36" s="9" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="T36" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>17.9</v>
+      <c r="S36" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T36" s="9" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="U36" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="V36" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="13" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="X36" s="3" t="n">
-        <v>11.3</v>
+      <c r="W36" s="9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="X36" s="12" t="n">
+        <v>3.3</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Z36" s="3" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3573,37 +3581,37 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2140.4</v>
-      </c>
-      <c r="D37" s="11" t="n">
+        <v>2240.4</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="10" t="n">
         <v>60.9</v>
       </c>
       <c r="F37" s="10" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="13" t="n">
-        <v>67.3</v>
+      <c r="G37" s="3" t="n">
+        <v>62.6</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>141.7</v>
+        <v>14.9</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="K37" s="10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L37" s="11" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>6.4</v>
+        <v>18.5</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>63.7</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
@@ -3611,13 +3619,11 @@
       <c r="O37" s="3" t="n">
         <v>492</v>
       </c>
-      <c r="P37" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q37" s="10" t="n">
-        <v>185.9</v>
-      </c>
-      <c r="R37" s="11" t="n">
+      <c r="P37" s="3" t="inlineStr"/>
+      <c r="Q37" s="9" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="R37" s="9" t="n">
         <v>88.8</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3632,17 +3638,17 @@
       <c r="V37" s="10" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="10" t="n">
-        <v>837.1</v>
+      <c r="W37" s="9" t="n">
+        <v>83.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.5</v>
+        <v>359.3</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>39.4</v>
+        <v>34.6</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3658,18 +3664,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>448.1</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3678,51 +3684,51 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>90.09999999999999</v>
+      <c r="J38" s="12" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="11" t="n">
+      <c r="L38" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="10" t="n">
+      <c r="M38" s="9" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="3" t="n">
+      <c r="N38" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="O38" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P38" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Q38" s="10" t="n">
+      <c r="O38" s="9" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q38" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="11" t="n">
+      <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>127.6</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>19.9</v>
+      <c r="S38" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="U38" s="9" t="n">
+        <v>7.8</v>
       </c>
       <c r="V38" s="10" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="10" t="n">
+      <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>21.9</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>6.9</v>
@@ -3743,36 +3749,38 @@
       <c r="C39" s="3" t="n">
         <v>579.9</v>
       </c>
-      <c r="D39" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F39" s="11" t="n">
+      <c r="D39" s="9" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F39" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I39" s="3" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="11" t="n">
+      <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M39" s="13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>1.7</v>
+      <c r="L39" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="M39" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N39" s="12" t="n">
+        <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
@@ -3780,35 +3788,33 @@
       <c r="P39" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="8" t="n">
+      <c r="R39" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="n">
-        <v>4.6</v>
-      </c>
+      <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W39" s="11" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>12.3</v>
+        <v>45.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="W39" s="17" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>14.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>11.6</v>
+        <v>176</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3824,56 +3830,58 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E40" s="11" t="n">
+        <v>335.9</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>96</v>
+        <v>196</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>82</v>
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="9" t="n">
+        <v>22</v>
       </c>
       <c r="R40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="S40" s="3" t="n">
-        <v>18.5</v>
+      <c r="S40" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>69.5</v>
+        <v>169.5</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>8</v>
@@ -3881,17 +3889,17 @@
       <c r="V40" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="W40" s="11" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="X40" s="3" t="n">
+      <c r="W40" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y40" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="Y40" s="3" t="n">
-        <v>89</v>
-      </c>
       <c r="Z40" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>83</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3909,54 +3917,56 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>18.5</v>
+      <c r="D41" s="9" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>18.3</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>51</v>
+      </c>
       <c r="I41" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="K41" s="11" t="n">
+      <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="13" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="M41" s="3" t="n">
+      <c r="L41" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>0</v>
+      <c r="N41" s="9" t="n">
+        <v>11.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Q41" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="R41" s="8" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S41" s="3" t="n">
+      <c r="R41" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="S41" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>423.5</v>
+        <v>57.9</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12.9</v>
@@ -3964,17 +3974,17 @@
       <c r="V41" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="11" t="n">
+      <c r="W41" s="17" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>16.3</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>14.8</v>
       </c>
       <c r="Y41" s="3" t="n">
         <v>58</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>19.8</v>
+        <v>15.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3990,39 +4000,39 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>529.4</v>
-      </c>
-      <c r="D42" s="11" t="n">
+        <v>524.4</v>
+      </c>
+      <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="F42" s="11" t="n">
+      <c r="E42" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="13" t="n">
-        <v>135.2</v>
+      <c r="G42" s="17" t="n">
+        <v>12.6</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>3.9</v>
+        <v>13.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="11" t="n">
+      <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N42" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M42" s="9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N42" s="9" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4031,30 +4041,26 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="13" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="S42" s="8" t="n">
-        <v>12.7</v>
+      <c r="R42" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="S42" s="12" t="n">
+        <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="U42" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="U42" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="8" t="n">
+      <c r="V42" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>14.8</v>
-      </c>
+      <c r="W42" s="16" t="inlineStr"/>
+      <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -4073,26 +4079,26 @@
       <c r="C43" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D43" s="11" t="inlineStr"/>
-      <c r="E43" s="11" t="inlineStr"/>
-      <c r="F43" s="11" t="inlineStr"/>
+      <c r="D43" s="9" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="11" t="inlineStr"/>
+      <c r="K43" s="16" t="inlineStr"/>
       <c r="L43" s="16" t="inlineStr"/>
-      <c r="M43" s="16" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="16" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr"/>
       <c r="R43" s="16" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
       <c r="V43" s="16" t="inlineStr"/>
-      <c r="W43" s="11" t="inlineStr"/>
+      <c r="W43" s="16" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4112,26 +4118,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="11" t="inlineStr"/>
+      <c r="K44" s="16" t="inlineStr"/>
       <c r="L44" s="16" t="inlineStr"/>
-      <c r="M44" s="16" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="16" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
       <c r="R44" s="16" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
       <c r="V44" s="16" t="inlineStr"/>
-      <c r="W44" s="11" t="inlineStr"/>
+      <c r="W44" s="16" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4149,49 +4155,49 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="F45" s="11" t="n">
+        <v>1981.2</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="3" t="n">
-        <v>27.9</v>
+      <c r="G45" s="17" t="n">
+        <v>10.8</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>119.9</v>
+        <v>16.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="11" t="n">
-        <v>0</v>
+      <c r="K45" s="10" t="n">
+        <v>10</v>
       </c>
       <c r="L45" s="10" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="10" t="n">
-        <v>22.9</v>
+      <c r="M45" s="9" t="n">
+        <v>42.5</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>31.6</v>
+        <v>5.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" s="10" t="n">
-        <v>98.59999999999999</v>
+        <v>12.3</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="R45" s="10" t="n">
         <v>71</v>
@@ -4200,7 +4206,7 @@
         <v>66</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>216.9</v>
+        <v>216.4</v>
       </c>
       <c r="U45" s="3" t="n">
         <v>59</v>
@@ -4208,17 +4214,17 @@
       <c r="V45" s="10" t="n">
         <v>831.9</v>
       </c>
-      <c r="W45" s="11" t="n">
-        <v>66.5</v>
+      <c r="W45" s="10" t="n">
+        <v>67.3</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>200.8</v>
+        <v>62.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1263</v>
+        <v>263</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>2331.8</v>
+        <v>35.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4234,37 +4240,39 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>417.8</v>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F46" s="11" t="n">
+        <v>477.8</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F46" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>69.40000000000001</v>
+      <c r="G46" s="9" t="n">
+        <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.6</v>
+        <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="K46" s="3" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="L46" s="10" t="n">
-        <v>11181.9</v>
-      </c>
-      <c r="M46" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N46" s="3" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N46" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4273,30 +4281,32 @@
       <c r="P46" s="3" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q46" s="10" t="n">
+      <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
       <c r="R46" s="10" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>11.6</v>
+        <v>17.7</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>54.1</v>
       </c>
-      <c r="U46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="V46" s="10" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="11" t="n">
+      <c r="W46" s="10" t="n">
         <v>16.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>1.4</v>
+        <v>15.7</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1862.4</v>
+        <v>265.7</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>81.90000000000001</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,18 +146,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -170,13 +158,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -801,11 +795,11 @@
       <c r="F4" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>81.7</v>
+      <c r="G4" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
+        <v>5.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.5</v>
@@ -813,37 +807,37 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>8</v>
+      <c r="K4" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="N4" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="O4" s="9" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="P4" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q4" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="S4" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T4" s="3" t="n">
+      <c r="R4" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="S4" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="T4" s="9" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="12" t="n">
+      <c r="U4" s="9" t="n">
         <v>19.1</v>
       </c>
       <c r="V4" s="9" t="n">
@@ -852,7 +846,7 @@
       <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -890,7 +884,7 @@
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.8</v>
@@ -898,53 +892,53 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.2</v>
       </c>
       <c r="L5" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+      <c r="M5" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q5" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>18.6</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>2</v>
+      <c r="S5" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>1.4</v>
       </c>
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="X5" s="9" t="n">
+      <c r="W5" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="Y5" s="9" t="n">
+      <c r="Y5" s="3" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>4.4</v>
+      <c r="Z5" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -966,12 +960,12 @@
         <v>25.9</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>7.9</v>
+        <v>10.9</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="G6" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G6" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -981,10 +975,10 @@
         <v>1.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>16.5</v>
+        <v>1.1</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>11.1</v>
@@ -993,43 +987,43 @@
         <v>11</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>98.5</v>
+        <v>99.3</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q6" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="S6" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>11.9</v>
+      <c r="S6" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>0.8</v>
       </c>
       <c r="V6" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y6" s="3" t="n">
+      <c r="W6" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X6" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y6" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="Z6" s="3" t="n">
-        <v>2.9</v>
+      <c r="Z6" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1066,40 +1060,40 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>21.1</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N7" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
+      <c r="M7" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="T7" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>4.8</v>
+      <c r="S7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="V7" s="9" t="n">
         <v>18.9</v>
@@ -1107,14 +1101,14 @@
       <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1136,16 +1130,16 @@
         <v>26.3</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>17.7</v>
+        <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>2.2</v>
@@ -1153,46 +1147,46 @@
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="N8" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q8" s="12" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="R8" s="3" t="n">
+      <c r="N8" s="9" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="R8" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>6</v>
+      <c r="S8" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="17" t="n">
-        <v>97.3</v>
-      </c>
-      <c r="X8" s="12" t="n">
+      <c r="W8" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1215,22 +1209,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1749.7</v>
+        <v>174.7</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>13.9</v>
+      <c r="G9" s="9" t="n">
+        <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>140.6</v>
+        <v>40.6</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>9.9</v>
@@ -1238,14 +1232,14 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>551.2</v>
+        <v>57.2</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>766.1</v>
@@ -1254,14 +1248,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="9" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="10" t="n">
-        <v>185.3</v>
+      <c r="R9" s="15" t="n">
+        <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1272,14 +1266,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="15" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>414.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1298,15 +1292,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8349.9</v>
+        <v>349.9</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>18.4</v>
       </c>
       <c r="G10" s="9" t="n">
@@ -1318,44 +1312,44 @@
       <c r="I10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>9.4</v>
+      <c r="J10" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>96.8</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q10" s="10" t="n">
+      <c r="N10" s="9" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="10" t="n">
-        <v>117.7</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.7</v>
+      <c r="R10" s="15" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S10" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="10" t="n">
+      <c r="W10" s="15" t="n">
         <v>17</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1379,7 +1373,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
+        <v>509.5</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1390,26 +1384,26 @@
       <c r="F11" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="12" t="n">
-        <v>18.6</v>
+      <c r="G11" s="9" t="n">
+        <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>6.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1420,35 +1414,35 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S11" s="12" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S11" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="T11" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U11" s="12" t="n">
+      <c r="T11" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="9" t="n">
         <v>19.9</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z11" s="3" t="n">
-        <v>9</v>
+      <c r="X11" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="Z11" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1464,7 +1458,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>508.7</v>
+        <v>506.7</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>25.9</v>
@@ -1482,18 +1476,18 @@
         <v>7.1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="M12" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="M12" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1505,35 +1499,35 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>25.4</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>20.4</v>
+      <c r="S12" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>14.8</v>
       </c>
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>12.2</v>
+      <c r="W12" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X12" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1552,25 +1546,25 @@
         <v>357.9</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I13" s="12" t="n">
-        <v>99.40000000000001</v>
+        <v>7.5</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0.5</v>
@@ -1579,9 +1573,9 @@
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N13" s="12" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N13" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1590,20 +1584,20 @@
       <c r="P13" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="R13" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>185.4</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>13</v>
+      <c r="S13" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="V13" s="9" t="n">
         <v>19.6</v>
@@ -1637,13 +1631,13 @@
         <v>227</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>10.5</v>
@@ -1651,19 +1645,19 @@
       <c r="H14" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>28.5</v>
+      <c r="I14" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>29.5</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L14" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M14" s="12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="M14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1673,37 +1667,37 @@
         <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q14" s="17" t="n">
-        <v>84.90000000000001</v>
+        <v>0.9</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>14.9</v>
       </c>
       <c r="R14" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S14" s="9" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>0.6</v>
+        <v>16.7</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X14" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z14" s="3" t="n">
-        <v>1</v>
+      <c r="W14" s="9" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="X14" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>-0.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1719,19 +1713,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>631</v>
+        <v>31</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>50.8</v>
+        <v>18.5</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>7.9</v>
@@ -1740,19 +1734,19 @@
         <v>3.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="L15" s="17" t="n">
-        <v>77.40000000000001</v>
+      <c r="L15" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="M15" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>99</v>
@@ -1760,20 +1754,20 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="R15" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S15" s="12" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="S15" s="9" t="n">
         <v>15.7</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="9" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="12" t="n">
-        <v>17.8</v>
+      <c r="U15" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>20.7</v>
@@ -1804,16 +1798,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
       <c r="E16" s="9" t="n">
-        <v>56.3</v>
+        <v>56.8</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="G16" s="3" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="G16" s="9" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1825,44 +1819,44 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="10" t="n">
+      <c r="K16" s="15" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M16" s="10" t="n">
+      <c r="L16" s="15" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="M16" s="15" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>489.8</v>
+        <v>89</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="10" t="n">
-        <v>1111</v>
-      </c>
-      <c r="R16" s="9" t="n">
+      <c r="Q16" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="R16" s="15" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>77.7</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>310.8</v>
+        <v>310</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>603.9</v>
+        <v>60.9</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="10" t="n">
-        <v>801.9</v>
+      <c r="W16" s="9" t="n">
+        <v>78.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1905,56 +1899,56 @@
         <v>7.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>97.40000000000001</v>
+        <v>27.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="15" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="15" t="n">
         <v>11.6</v>
       </c>
-      <c r="N17" s="12" t="n">
+      <c r="N17" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Q17" s="10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q17" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="15" t="n">
         <v>16.4</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>362</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>18.2</v>
+      <c r="S17" s="9" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>872.8</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>1.8</v>
+      <c r="X17" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>4.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1970,7 +1964,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>845.5</v>
+        <v>45.5</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>25.9</v>
@@ -1979,21 +1973,21 @@
         <v>10.9</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>13</v>
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L18" s="9" t="n">
@@ -2014,32 +2008,32 @@
       <c r="Q18" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="S18" s="12" t="n">
+      <c r="R18" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="S18" s="9" t="n">
         <v>15.4</v>
       </c>
-      <c r="T18" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U18" s="12" t="n">
+      <c r="T18" s="9" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U18" s="9" t="n">
         <v>17.9</v>
       </c>
       <c r="V18" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="12" t="n">
+      <c r="W18" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="12" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>10.4</v>
+      <c r="X18" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z18" s="9" t="n">
+        <v>7.3</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2066,8 +2060,8 @@
       <c r="F19" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>17.9</v>
+      <c r="G19" s="9" t="n">
+        <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>7.2</v>
@@ -2078,13 +2072,13 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="9" t="n">
         <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2099,17 +2093,17 @@
       <c r="Q19" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S19" s="3" t="n">
+      <c r="R19" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S19" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="T19" s="3" t="n">
+      <c r="T19" s="9" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="12" t="n">
-        <v>7.2</v>
+      <c r="U19" s="9" t="n">
+        <v>17.2</v>
       </c>
       <c r="V19" s="9" t="n">
         <v>21.2</v>
@@ -2157,59 +2151,59 @@
       <c r="H20" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="I20" s="12" t="n">
-        <v>33.3</v>
+      <c r="I20" s="3" t="n">
+        <v>23.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N20" s="12" t="n">
+      <c r="M20" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>13</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="R20" s="9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="S20" s="9" t="n">
         <v>15.3</v>
       </c>
-      <c r="T20" s="3" t="n">
+      <c r="T20" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="12" t="n">
-        <v>222.4</v>
+      <c r="U20" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="V20" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X20" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y20" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z20" s="3" t="n">
-        <v>7.6</v>
+      <c r="W20" s="9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X20" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="Z20" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2230,13 +2224,13 @@
       <c r="D21" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2248,52 +2242,52 @@
       <c r="J21" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="N21" s="3" t="n">
+      <c r="N21" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="O21" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P21" s="3" t="n">
+      <c r="O21" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P21" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q21" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S21" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>1.6</v>
+      <c r="U21" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="V21" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="X21" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Y21" s="3" t="n">
+      <c r="W21" s="9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="X21" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="9" t="n">
         <v>87</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Z21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2310,22 +2304,22 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>989</v>
+        <v>9</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="17" t="n">
-        <v>-7.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="9" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>83.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.7</v>
@@ -2333,53 +2327,53 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>8</v>
+      <c r="K22" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P22" s="3" t="n">
+      <c r="N22" s="9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="P22" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="S22" s="3" t="n">
+      <c r="R22" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S22" s="9" t="n">
         <v>14.4</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>149.5</v>
-      </c>
-      <c r="U22" s="3" t="n">
+      <c r="T22" s="9" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="U22" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="V22" s="9" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="9" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>139.7</v>
+      <c r="X22" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z22" s="9" t="n">
+        <v>9.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2395,55 +2389,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2322.3</v>
+        <v>2320.3</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="F23" s="10" t="n">
+      <c r="E23" s="9" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="F23" s="15" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="3" t="n">
-        <v>75.90000000000001</v>
+      <c r="G23" s="9" t="n">
+        <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="K23" s="10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>62.5</v>
       </c>
-      <c r="M23" s="10" t="n">
-        <v>161.8</v>
+      <c r="M23" s="9" t="n">
+        <v>61.7</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>2493</v>
+        <v>93</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="10" t="n">
-        <v>85</v>
+      <c r="R23" s="15" t="n">
+        <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>7.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>235.7</v>
@@ -2454,7 +2448,7 @@
       <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="10" t="n">
+      <c r="W23" s="15" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2485,10 +2479,10 @@
       <c r="D24" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="10" t="n">
+      <c r="E24" s="9" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="10" t="n">
+      <c r="F24" s="9" t="n">
         <v>18.9</v>
       </c>
       <c r="G24" s="9" t="n">
@@ -2501,7 +2495,7 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>1.4</v>
@@ -2509,11 +2503,11 @@
       <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="10" t="n">
-        <v>12.4</v>
+      <c r="M24" s="9" t="n">
+        <v>12.3</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2524,32 +2518,32 @@
       <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="R24" s="15" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>47.9</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>17.8</v>
+      <c r="S24" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T24" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>13.1</v>
       </c>
       <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="10" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="W24" s="15" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X24" s="9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Y24" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z24" s="9" t="n">
+        <v>5.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2576,8 +2570,8 @@
       <c r="F25" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>10.9</v>
+      <c r="G25" s="9" t="n">
+        <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>5.7</v>
@@ -2588,23 +2582,23 @@
       <c r="J25" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K25" s="3" t="n">
-        <v>6.4</v>
+      <c r="K25" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M25" s="17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>0.9</v>
+        <v>10.1</v>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q25" s="9" t="n">
         <v>24.7</v>
@@ -2650,7 +2644,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>349.9</v>
+        <v>349.1</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>24.4</v>
@@ -2667,29 +2661,29 @@
       <c r="H26" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>23.4</v>
+      <c r="I26" s="3" t="n">
+        <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="K26" s="3" t="n">
+      <c r="K26" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>0.9</v>
+      <c r="N26" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q26" s="9" t="n">
         <v>21</v>
@@ -2709,17 +2703,17 @@
       <c r="V26" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="X26" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y26" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="Z26" s="9" t="n">
-        <v>8.199999999999999</v>
+      <c r="W26" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>11.8</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2738,16 +2732,16 @@
         <v>340.2</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>24</v>
+      <c r="G27" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>8.4</v>
@@ -2756,25 +2750,25 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>7.1</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O27" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.4</v>
+      <c r="N27" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>17.6</v>
@@ -2794,17 +2788,17 @@
       <c r="V27" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y27" s="9" t="n">
-        <v>95.7</v>
-      </c>
-      <c r="Z27" s="9" t="n">
-        <v>0.9</v>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2831,11 +2825,11 @@
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>15.9</v>
+      <c r="G28" s="9" t="n">
+        <v>15.5</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>2.4</v>
@@ -2843,11 +2837,11 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="9" t="n">
         <v>5.5</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>13.3</v>
@@ -2856,10 +2850,10 @@
         <v>15.3</v>
       </c>
       <c r="O28" s="9" t="n">
-        <v>98.7</v>
+        <v>99.3</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>22.9</v>
@@ -2879,17 +2873,17 @@
       <c r="V28" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="3" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="Y28" s="9" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="Z28" s="9" t="n">
-        <v>1</v>
+      <c r="X28" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,7 +2899,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>523.3</v>
+        <v>593.3</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>28.8</v>
@@ -2916,8 +2910,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>1.8</v>
+      <c r="G29" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2928,23 +2922,23 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>2.6</v>
+      <c r="N29" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>27</v>
@@ -2965,16 +2959,16 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>17.3</v>
+        <v>14.7</v>
       </c>
       <c r="X29" s="9" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="Y29" s="9" t="n">
-        <v>71.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="Z29" s="9" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2993,15 +2987,15 @@
         <v>228.4</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>131.8</v>
+        <v>131.2</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>51.4</v>
+        <v>52.1</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="9" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
@@ -3013,14 +3007,14 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="10" t="n">
+      <c r="K30" s="9" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v>56.7</v>
+        <v>57.2</v>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>65.90000000000001</v>
@@ -3034,32 +3028,32 @@
       <c r="Q30" s="9" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="R30" s="15" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>314.8</v>
+        <v>14.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>35.4</v>
+        <v>55.4</v>
       </c>
       <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="15" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="X30" s="9" t="n">
-        <v>522</v>
-      </c>
-      <c r="Y30" s="9" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="Z30" s="9" t="n">
-        <v>506.8</v>
+      <c r="X30" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>35</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3075,7 +3069,7 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>26.2</v>
@@ -3100,49 +3094,49 @@
       </c>
       <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="M31" s="10" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="P31" s="9" t="n">
+      <c r="N31" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="10" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="S31" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>63</v>
-      </c>
-      <c r="U31" s="12" t="n">
-        <v>111.4</v>
+      <c r="R31" s="15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S31" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="T31" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="U31" s="9" t="n">
+        <v>7.7</v>
       </c>
       <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="15" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="Y31" s="9" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="Z31" s="9" t="n">
-        <v>4.6</v>
+      <c r="X31" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>730.2</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3167,7 +3161,7 @@
         <v>10.2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>17.7</v>
@@ -3181,11 +3175,11 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>20.5</v>
+      <c r="K32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>10.2</v>
@@ -3193,39 +3187,39 @@
       <c r="N32" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O32" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>26.46</v>
+      <c r="O32" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="S32" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="T32" s="9" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="V32" s="3" t="n">
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="n">
-        <v>171.8</v>
+      <c r="X32" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="Y32" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="Z32" s="9" t="n">
+        <v>5.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3256,61 +3250,61 @@
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.4</v>
+        <v>9.4</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="3" t="n">
+      <c r="K33" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>14.9</v>
       </c>
       <c r="M33" s="9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N33" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q33" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>17.8</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="T33" s="9" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>19.9</v>
+      <c r="S33" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="9" t="n">
+        <v>19.4</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>14</v>
+      <c r="X33" s="9" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Y33" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z33" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3326,7 +3320,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>329.9</v>
+        <v>329.1</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>23.3</v>
@@ -3340,62 +3334,62 @@
       <c r="G34" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="H34" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>15.9</v>
       </c>
-      <c r="N34" s="12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="O34" s="3" t="n">
+      <c r="N34" s="9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O34" s="9" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="P34" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="R34" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="S34" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T34" s="9" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="U34" s="9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V34" s="12" t="n">
-        <v>28.7</v>
+      <c r="S34" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="V34" s="9" t="n">
+        <v>18.7</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y34" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>3.8</v>
+      <c r="X34" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y34" s="9" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="Z34" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3434,7 +3428,7 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
@@ -3444,43 +3438,43 @@
         <v>12.9</v>
       </c>
       <c r="N35" s="9" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q35" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R35" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S35" s="9" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="T35" s="9" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="V35" s="12" t="n">
+      <c r="S35" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V35" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Y35" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>8</v>
+      <c r="X35" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="Z35" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3502,70 +3496,70 @@
         <v>26.3</v>
       </c>
       <c r="E36" s="9" t="n">
-        <v>10.9</v>
+        <v>10.4</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G36" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G36" s="9" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>8.6</v>
+      <c r="K36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>10.6</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N36" s="9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O36" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="R36" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="S36" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T36" s="9" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="V36" s="3" t="n">
+      <c r="S36" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="V36" s="9" t="n">
         <v>20.6</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>11</v>
+      <c r="X36" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Z36" s="9" t="n">
+        <v>7.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3581,47 +3575,47 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2240.4</v>
+        <v>224.4</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="9" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="3" t="n">
-        <v>62.6</v>
+      <c r="G37" s="9" t="n">
+        <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>14.9</v>
+        <v>14.1</v>
       </c>
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="L37" s="10" t="n">
-        <v>63</v>
+      <c r="K37" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>65</v>
       </c>
       <c r="M37" s="9" t="n">
-        <v>63.7</v>
+        <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>492</v>
+        <v>92</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="9" t="n">
-        <v>115.9</v>
+      <c r="Q37" s="15" t="n">
+        <v>115.5</v>
       </c>
       <c r="R37" s="9" t="n">
         <v>88.8</v>
@@ -3630,12 +3624,12 @@
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>216.9</v>
+        <v>16.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="10" t="n">
+      <c r="V37" s="9" t="n">
         <v>100.9</v>
       </c>
       <c r="W37" s="9" t="n">
@@ -3645,7 +3639,7 @@
         <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>359.3</v>
+        <v>359.5</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>34.6</v>
@@ -3664,7 +3658,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>44.8</v>
+        <v>448.1</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>25.7</v>
@@ -3684,11 +3678,13 @@
       <c r="I38" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="10" t="n">
+      <c r="J38" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="9" t="n">
         <v>13</v>
       </c>
       <c r="M38" s="9" t="n">
@@ -3698,40 +3694,40 @@
         <v>14.8</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q38" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="15" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="S38" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="T38" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="V38" s="10" t="n">
+      <c r="S38" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V38" s="9" t="n">
         <v>20.2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="12" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Y38" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>6.9</v>
+      <c r="X38" s="9" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y38" s="9" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="Z38" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3762,59 +3758,59 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M39" s="9" t="n">
+      <c r="L39" s="9" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="12" t="n">
+      <c r="N39" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Q39" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
       <c r="T39" s="3" t="n">
-        <v>45.5</v>
+        <v>45.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="V39" s="17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="W39" s="17" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="Y39" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="Z39" s="3" t="n">
-        <v>176</v>
+      <c r="V39" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W39" s="9" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="X39" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="Y39" s="9" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="Z39" s="9" t="n">
+        <v>8.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3830,7 +3826,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>335.9</v>
+        <v>355.7</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>27.2</v>
@@ -3853,53 +3849,53 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>10.2</v>
+      <c r="N40" s="9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" s="12" t="n">
+      <c r="R40" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S40" s="9" t="n">
         <v>18.4</v>
       </c>
-      <c r="T40" s="3" t="n">
-        <v>169.5</v>
-      </c>
-      <c r="U40" s="3" t="n">
+      <c r="T40" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U40" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="W40" s="12" t="n">
+      <c r="V40" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="W40" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y40" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="Z40" s="3" t="n">
-        <v>83</v>
+      <c r="X40" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y40" s="9" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="Z40" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3918,51 +3914,51 @@
         <v>451.2</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>28.94</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G41" s="3" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G41" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>51</v>
+      <c r="H41" s="3" t="n">
+        <v>22</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.3</v>
+        <v>3.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="9" t="n">
-        <v>11.1</v>
+      <c r="N41" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q41" s="9" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="R41" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="12" t="n">
+      <c r="S41" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="T41" s="3" t="n">
@@ -3971,20 +3967,20 @@
       <c r="U41" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="17" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Y41" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>15.7</v>
+      <c r="W41" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X41" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Y41" s="9" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z41" s="9" t="n">
+        <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4005,34 +4001,34 @@
       <c r="D42" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="17" t="n">
-        <v>1.1</v>
+      <c r="E42" s="9" t="n">
+        <v>11.4</v>
       </c>
       <c r="F42" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="17" t="n">
-        <v>12.6</v>
+      <c r="G42" s="9" t="n">
+        <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>7.8</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="M42" s="9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N42" s="9" t="n">
+      <c r="L42" s="9" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N42" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4041,25 +4037,25 @@
       <c r="P42" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q42" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R42" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S42" s="12" t="n">
+      <c r="Q42" s="14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R42" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S42" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="U42" s="12" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="16" t="inlineStr"/>
+      <c r="W42" s="9" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4086,19 +4082,19 @@
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="16" t="inlineStr"/>
-      <c r="L43" s="16" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="9" t="inlineStr"/>
+      <c r="L43" s="9" t="inlineStr"/>
+      <c r="M43" s="16" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
+      <c r="Q43" s="16" t="inlineStr"/>
       <c r="R43" s="16" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="16" t="inlineStr"/>
-      <c r="W43" s="16" t="inlineStr"/>
+      <c r="V43" s="9" t="inlineStr"/>
+      <c r="W43" s="9" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4125,19 +4121,19 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="16" t="inlineStr"/>
-      <c r="L44" s="16" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="9" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
+      <c r="M44" s="16" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="Q44" s="16" t="inlineStr"/>
       <c r="R44" s="16" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="16" t="inlineStr"/>
-      <c r="W44" s="16" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4155,37 +4151,37 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1981.2</v>
+        <v>1911.2</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>41.4</v>
+        <v>109.7</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>41.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="G45" s="17" t="n">
-        <v>10.8</v>
+      <c r="G45" s="3" t="n">
+        <v>27.9</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>16.4</v>
+        <v>14.4</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="L45" s="10" t="n">
+      <c r="K45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="9" t="n">
-        <v>42.5</v>
+      <c r="M45" s="15" t="n">
+        <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>5.1</v>
@@ -4194,12 +4190,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="R45" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="15" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="R45" s="15" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4211,14 +4207,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="10" t="n">
-        <v>831.9</v>
-      </c>
-      <c r="W45" s="10" t="n">
-        <v>67.3</v>
+      <c r="V45" s="9" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="W45" s="9" t="n">
+        <v>51</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>62.8</v>
+        <v>66.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4245,7 +4241,7 @@
       <c r="D46" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="10" t="n">
+      <c r="E46" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="F46" s="9" t="n">
@@ -4261,33 +4257,33 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L46" s="10" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="M46" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>111100</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M46" s="15" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q46" s="15" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="15" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="12" t="n">
+      <c r="S46" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="T46" s="3" t="n">
@@ -4296,20 +4292,20 @@
       <c r="U46" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V46" s="10" t="n">
+      <c r="V46" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="10" t="n">
+      <c r="W46" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>265.7</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>81.90000000000001</v>
+      <c r="X46" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y46" s="9" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Z46" s="9" t="n">
+        <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,6 +152,21 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -164,10 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -811,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M4" s="9" t="n">
         <v>9.1</v>
@@ -820,10 +832,10 @@
         <v>11.6</v>
       </c>
       <c r="O4" s="9" t="n">
-        <v>95.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="P4" s="9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" s="9" t="n">
         <v>25.8</v>
@@ -843,17 +855,17 @@
       <c r="V4" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>7.8</v>
+      <c r="X4" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y4" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="Z4" s="9" t="n">
+        <v>5.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -928,17 +940,17 @@
       <c r="V5" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v>2.9</v>
+      <c r="W5" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X5" s="9" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="Z5" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -969,7 +981,7 @@
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>1.2</v>
@@ -1060,7 +1072,7 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.1</v>
+        <v>1.9</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0</v>
@@ -1098,17 +1110,17 @@
       <c r="V7" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>4.1</v>
+      <c r="X7" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>2.7</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1142,7 +1154,7 @@
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
@@ -1183,17 +1195,17 @@
       <c r="V8" s="9" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>2.6</v>
+      <c r="X8" s="9" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1209,7 +1221,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.7</v>
+        <v>174.9</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>128.9</v>
@@ -1236,7 +1248,7 @@
         <v>7.7</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>57.2</v>
+        <v>56.7</v>
       </c>
       <c r="M9" s="9" t="n">
         <v>55.2</v>
@@ -1251,11 +1263,11 @@
       <c r="Q9" s="9" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="15" t="n">
+      <c r="R9" s="10" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.5</v>
+        <v>88.3</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1266,14 +1278,14 @@
       <c r="V9" s="9" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="15" t="n">
+      <c r="W9" s="10" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>14.5</v>
+        <v>414.5</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>19.8</v>
@@ -1334,31 +1346,33 @@
       <c r="Q10" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="15" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T10" s="9" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v>4.3</v>
+      <c r="R10" s="10" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>6.7</v>
       </c>
       <c r="V10" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="15" t="n">
+      <c r="W10" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Z10" s="3" t="inlineStr"/>
+      <c r="X10" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1373,7 +1387,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.5</v>
+        <v>509.3</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>27.3</v>
@@ -1396,7 +1410,7 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1418,31 +1432,31 @@
         <v>26.3</v>
       </c>
       <c r="R11" s="9" t="n">
-        <v>12.4</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>14.4</v>
+        <v>19.5</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>42</v>
+        <v>56.9</v>
       </c>
       <c r="U11" s="9" t="n">
-        <v>19.9</v>
+        <v>14.7</v>
       </c>
       <c r="V11" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="W11" s="9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X11" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="X11" s="9" t="n">
-        <v>20.1</v>
-      </c>
       <c r="Y11" s="9" t="n">
-        <v>75.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="Z11" s="9" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1481,7 +1495,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1517,17 +1531,17 @@
       <c r="V12" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X12" s="9" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="Y12" s="9" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z12" s="9" t="n">
-        <v>8.6</v>
+      <c r="W12" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1561,12 +1575,12 @@
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1582,7 +1596,7 @@
         <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="Q13" s="9" t="n">
         <v>18.9</v>
@@ -1649,13 +1663,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>6.7</v>
+        <v>11.5</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>16.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1687,17 +1701,17 @@
       <c r="V14" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="X14" s="9" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="Y14" s="9" t="n">
-        <v>104.6</v>
-      </c>
-      <c r="Z14" s="9" t="n">
-        <v>-0.8</v>
+      <c r="W14" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1713,7 +1727,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>31</v>
+        <v>631</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>26</v>
@@ -1736,7 +1750,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1801,13 +1815,13 @@
       <c r="D16" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>56.8</v>
+      <c r="E16" s="10" t="n">
+        <v>57</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>92.5</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="3" t="n">
         <v>71.2</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1819,20 +1833,20 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="15" t="n">
+      <c r="K16" s="9" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="15" t="n">
+      <c r="L16" s="10" t="n">
         <v>59.1</v>
       </c>
-      <c r="M16" s="15" t="n">
+      <c r="M16" s="10" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>89</v>
+        <v>289</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>2</v>
@@ -1840,7 +1854,7 @@
       <c r="Q16" s="9" t="n">
         <v>111</v>
       </c>
-      <c r="R16" s="15" t="n">
+      <c r="R16" s="10" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1855,8 +1869,8 @@
       <c r="V16" s="9" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>78.7</v>
+      <c r="W16" s="10" t="n">
+        <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>82.2</v>
@@ -1902,13 +1916,13 @@
         <v>2.9</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>27.4</v>
+        <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="15" t="n">
+      <c r="L17" s="10" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="15" t="n">
+      <c r="M17" s="10" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1918,12 +1932,12 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="15" t="n">
+      <c r="R17" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="S17" s="9" t="n">
@@ -1938,17 +1952,17 @@
       <c r="V17" s="9" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="9" t="n">
+      <c r="W17" s="10" t="n">
         <v>16.1</v>
       </c>
-      <c r="X17" s="9" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Y17" s="9" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="Z17" s="9" t="n">
-        <v>4.5</v>
+      <c r="X17" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1982,7 +1996,7 @@
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
@@ -2078,7 +2092,7 @@
       <c r="L19" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2163,7 +2177,7 @@
       <c r="L20" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="3" t="n">
         <v>11</v>
       </c>
       <c r="N20" s="3" t="n">
@@ -2173,7 +2187,7 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q20" s="9" t="n">
         <v>28</v>
@@ -2240,22 +2254,22 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>13.1</v>
+        <v>17.6</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>13</v>
+        <v>17.4</v>
       </c>
       <c r="N21" s="9" t="n">
-        <v>14.9</v>
+        <v>19.9</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="P21" s="9" t="n">
         <v>0.2</v>
@@ -2304,13 +2318,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>9</v>
+        <v>429</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>25.2</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>12.1</v>
+        <v>12.9</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>18.7</v>
@@ -2394,10 +2408,10 @@
       <c r="D23" s="9" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="10" t="n">
         <v>56.7</v>
       </c>
-      <c r="F23" s="15" t="n">
+      <c r="F23" s="10" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="G23" s="9" t="n">
@@ -2407,7 +2421,7 @@
         <v>40.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>20.8</v>
@@ -2416,24 +2430,24 @@
         <v>0.3</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="M23" s="9" t="n">
-        <v>61.7</v>
+        <v>67</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>71.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>93</v>
+        <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.4</v>
+        <v>11.4</v>
       </c>
       <c r="Q23" s="9" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="15" t="n">
+      <c r="R23" s="10" t="n">
         <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2448,7 +2462,7 @@
       <c r="V23" s="9" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="15" t="n">
+      <c r="W23" s="10" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2495,19 +2509,19 @@
         <v>2.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>22.1</v>
+        <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="9" t="n">
-        <v>12.3</v>
+      <c r="M24" s="10" t="n">
+        <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2518,7 +2532,7 @@
       <c r="Q24" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="15" t="n">
+      <c r="R24" s="10" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="9" t="n">
@@ -2533,7 +2547,7 @@
       <c r="V24" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="15" t="n">
+      <c r="W24" s="10" t="n">
         <v>17.1</v>
       </c>
       <c r="X24" s="9" t="n">
@@ -2577,10 +2591,10 @@
         <v>5.7</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
@@ -2665,7 +2679,7 @@
         <v>2.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0.9</v>
@@ -2704,10 +2718,10 @@
         <v>21.6</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>25.5</v>
+        <v>13.5</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>14.2</v>
+        <v>142.2</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>55</v>
@@ -2750,7 +2764,7 @@
         <v>2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>7.1</v>
@@ -2820,13 +2834,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>19.3</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>8.1</v>
@@ -2910,8 +2924,8 @@
       <c r="F29" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>18.7</v>
+      <c r="G29" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2944,16 +2958,16 @@
         <v>27</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="S29" s="9" t="n">
-        <v>17</v>
+        <v>21.6</v>
       </c>
       <c r="T29" s="9" t="n">
-        <v>47.8</v>
+        <v>60.4</v>
       </c>
       <c r="U29" s="9" t="n">
-        <v>18.6</v>
+        <v>14.1</v>
       </c>
       <c r="V29" s="9" t="n">
         <v>22.8</v>
@@ -2984,7 +2998,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>228.4</v>
+        <v>2284.8</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>131.2</v>
@@ -2999,7 +3013,7 @@
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3028,14 +3042,14 @@
       <c r="Q30" s="9" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="15" t="n">
+      <c r="R30" s="9" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>84.40000000000001</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>14.8</v>
+        <v>314.8</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>55.4</v>
@@ -3043,7 +3057,7 @@
       <c r="V30" s="9" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="15" t="n">
+      <c r="W30" s="10" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3099,8 +3113,8 @@
       <c r="M31" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="3" t="n">
-        <v>12.4</v>
+      <c r="N31" s="9" t="n">
+        <v>13.2</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3111,7 +3125,7 @@
       <c r="Q31" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="15" t="n">
+      <c r="R31" s="9" t="n">
         <v>17.3</v>
       </c>
       <c r="S31" s="9" t="n">
@@ -3126,7 +3140,7 @@
       <c r="V31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="15" t="n">
+      <c r="W31" s="10" t="n">
         <v>16.4</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3136,7 +3150,7 @@
         <v>730.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>25.8</v>
+        <v>165.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3197,7 +3211,7 @@
         <v>21.1</v>
       </c>
       <c r="R32" s="9" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
@@ -3335,7 +3349,7 @@
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.5</v>
@@ -3350,10 +3364,10 @@
         <v>16</v>
       </c>
       <c r="M34" s="9" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="N34" s="9" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="O34" s="9" t="n">
         <v>99</v>
@@ -3456,7 +3470,7 @@
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
@@ -3544,7 +3558,7 @@
         <v>45</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="V36" s="9" t="n">
         <v>20.6</v>
@@ -3575,7 +3589,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>224.4</v>
+        <v>224</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>128.5</v>
@@ -3590,7 +3604,7 @@
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>14.1</v>
@@ -3604,27 +3618,27 @@
       <c r="L37" s="9" t="n">
         <v>65</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="10" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>74.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>92</v>
+        <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="15" t="n">
+      <c r="Q37" s="10" t="n">
         <v>115.5</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>88.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>88</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>16.4</v>
+        <v>316.4</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>54.5</v>
@@ -3636,7 +3650,7 @@
         <v>83.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>84.7</v>
+        <v>82.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3679,7 +3693,7 @@
         <v>28.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>42.1</v>
+        <v>22.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
@@ -3699,7 +3713,7 @@
       <c r="P38" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="15" t="n">
+      <c r="Q38" s="10" t="n">
         <v>23.1</v>
       </c>
       <c r="R38" s="9" t="n">
@@ -3712,7 +3726,7 @@
         <v>63.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="V38" s="9" t="n">
         <v>20.2</v>
@@ -3746,7 +3760,7 @@
         <v>579.9</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>26.9</v>
+        <v>26.92</v>
       </c>
       <c r="E39" s="9" t="n">
         <v>11</v>
@@ -3758,7 +3772,7 @@
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>4.5</v>
@@ -3772,30 +3786,32 @@
       <c r="L39" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="3" t="n">
+      <c r="M39" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q39" s="3" t="n">
+      <c r="N39" s="9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P39" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q39" s="9" t="n">
         <v>26.6</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>19</v>
+      <c r="S39" s="9" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T39" s="9" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="U39" s="9" t="n">
+        <v>14.2</v>
       </c>
       <c r="V39" s="9" t="n">
         <v>21.7</v>
@@ -3859,13 +3875,13 @@
         <v>10.3</v>
       </c>
       <c r="N40" s="9" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>98.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>22</v>
@@ -3926,7 +3942,7 @@
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>3.6</v>
@@ -3940,32 +3956,32 @@
       <c r="L41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+      <c r="N41" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="O41" s="9" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P41" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q41" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="R41" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="T41" s="3" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>12.9</v>
+      <c r="S41" s="9" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="U41" s="9" t="n">
+        <v>8.9</v>
       </c>
       <c r="V41" s="9" t="n">
         <v>22</v>
@@ -4025,32 +4041,32 @@
       <c r="L42" s="9" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q42" s="14" t="n">
-        <v>2.6</v>
+      <c r="M42" s="9" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="P42" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q42" s="9" t="n">
+        <v>26.6</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>17.6</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>19.6</v>
+      <c r="S42" s="9" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="T42" s="9" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="U42" s="9" t="n">
+        <v>14.7</v>
       </c>
       <c r="V42" s="9" t="n">
         <v>22</v>
@@ -4084,12 +4100,12 @@
       <c r="J43" s="3" t="inlineStr"/>
       <c r="K43" s="9" t="inlineStr"/>
       <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="16" t="inlineStr"/>
+      <c r="M43" s="9" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="16" t="inlineStr"/>
-      <c r="R43" s="16" t="inlineStr"/>
+      <c r="Q43" s="9" t="inlineStr"/>
+      <c r="R43" s="20" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
@@ -4123,12 +4139,12 @@
       <c r="J44" s="3" t="inlineStr"/>
       <c r="K44" s="9" t="inlineStr"/>
       <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="16" t="inlineStr"/>
+      <c r="M44" s="9" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="16" t="inlineStr"/>
-      <c r="R44" s="16" t="inlineStr"/>
+      <c r="Q44" s="9" t="inlineStr"/>
+      <c r="R44" s="20" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
@@ -4156,17 +4172,17 @@
       <c r="D45" s="9" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="E45" s="10" t="n">
         <v>41.5</v>
       </c>
       <c r="F45" s="9" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>27.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4180,22 +4196,22 @@
       <c r="L45" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="15" t="n">
+      <c r="M45" s="9" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>5.1</v>
+        <v>51.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q45" s="15" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q45" s="9" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="15" t="n">
+      <c r="R45" s="10" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4257,18 +4273,18 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>5.2</v>
+        <v>52.1</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>111100</v>
+        <v>101.1</v>
       </c>
       <c r="L46" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="M46" s="15" t="n">
+      <c r="M46" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="3" t="n">
+      <c r="N46" s="9" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4277,20 +4293,20 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="15" t="n">
+      <c r="Q46" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="15" t="n">
+      <c r="R46" s="10" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="T46" s="3" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>14.7</v>
+      <c r="S46" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="T46" s="9" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="U46" s="9" t="n">
+        <v>10.9</v>
       </c>
       <c r="V46" s="9" t="n">
         <v>21.3</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,40 +143,37 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -798,16 +789,16 @@
       <c r="C4" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>18.7</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -819,53 +810,53 @@
       <c r="J4" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="M4" s="9" t="n">
+      <c r="L4" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="M4" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="N4" s="9" t="n">
+      <c r="N4" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="O4" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P4" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q4" s="9" t="n">
+      <c r="O4" s="8" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q4" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="S4" s="9" t="n">
+      <c r="S4" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="T4" s="9" t="n">
+      <c r="T4" s="8" t="n">
         <v>42.5</v>
       </c>
-      <c r="U4" s="9" t="n">
+      <c r="U4" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="X4" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y4" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="Z4" s="9" t="n">
-        <v>5.6</v>
+      <c r="X4" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -883,16 +874,16 @@
       <c r="C5" s="3" t="n">
         <v>382.4</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -904,53 +895,53 @@
       <c r="J5" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="K5" s="9" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="N5" s="9" t="n">
+      <c r="N5" s="8" t="n">
         <v>13.5</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" s="8" t="n">
         <v>94.2</v>
       </c>
-      <c r="P5" s="9" t="n">
+      <c r="P5" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="S5" s="9" t="n">
+      <c r="S5" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="T5" s="9" t="n">
+      <c r="T5" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="U5" s="9" t="n">
+      <c r="U5" s="8" t="n">
         <v>1.4</v>
       </c>
-      <c r="V5" s="9" t="n">
+      <c r="V5" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="W5" s="9" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="X5" s="9" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Y5" s="9" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="Z5" s="9" t="n">
-        <v>3</v>
+      <c r="W5" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -968,16 +959,16 @@
       <c r="C6" s="3" t="n">
         <v>309.1</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -989,52 +980,52 @@
       <c r="J6" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S6" s="9" t="n">
+      <c r="S6" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T6" s="9" t="n">
+      <c r="T6" s="8" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="U6" s="9" t="n">
+      <c r="U6" s="8" t="n">
         <v>0.8</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="X6" s="9" t="n">
+      <c r="X6" s="8" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y6" s="9" t="n">
+      <c r="Y6" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="Z6" s="9" t="n">
+      <c r="Z6" s="8" t="n">
         <v>0.9</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1053,16 +1044,16 @@
       <c r="C7" s="3" t="n">
         <v>275.8</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>9</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1072,55 +1063,55 @@
         <v>1.2</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K7" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="n">
+      <c r="L7" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="N7" s="9" t="n">
+      <c r="N7" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P7" s="9" t="n">
+      <c r="P7" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="S7" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="T7" s="9" t="n">
+      <c r="T7" s="8" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="U7" s="9" t="n">
+      <c r="U7" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="9" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y7" s="9" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="Z7" s="9" t="n">
-        <v>2.7</v>
+      <c r="X7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1138,74 +1129,74 @@
       <c r="C8" s="3" t="n">
         <v>391.2</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E8" s="9" t="n">
+      <c r="E8" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>7.7</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K8" s="9" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N8" s="9" t="n">
+      <c r="N8" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P8" s="9" t="n">
+      <c r="P8" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="S8" s="9" t="n">
+      <c r="S8" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="T8" s="9" t="n">
+      <c r="T8" s="8" t="n">
         <v>83</v>
       </c>
-      <c r="U8" s="9" t="n">
+      <c r="U8" s="8" t="n">
         <v>4.3</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="3" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="Y8" s="9" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="Z8" s="9" t="n">
-        <v>1.8</v>
+      <c r="X8" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1221,18 +1212,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>174.9</v>
-      </c>
-      <c r="D9" s="9" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>55</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>73.90000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1244,13 +1235,13 @@
       <c r="J9" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="K9" s="9" t="n">
+      <c r="K9" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="L9" s="9" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="M9" s="9" t="n">
+      <c r="L9" s="8" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>55.2</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1260,14 +1251,14 @@
         <v>484.9</v>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="10" t="n">
+      <c r="R9" s="13" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>88.3</v>
+        <v>88.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>380.5</v>
@@ -1275,10 +1266,10 @@
       <c r="U9" s="3" t="n">
         <v>33.3</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>95</v>
       </c>
-      <c r="W9" s="10" t="n">
+      <c r="W9" s="13" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1306,16 +1297,16 @@
       <c r="C10" s="3" t="n">
         <v>349.9</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H10" s="3" t="n">
@@ -1328,51 +1319,49 @@
         <v>27.4</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N10" s="9" t="n">
+      <c r="N10" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P10" s="9" t="n">
+      <c r="P10" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="Q10" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="10" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="V10" s="9" t="n">
+      <c r="R10" s="13" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="V10" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="X10" s="9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Y10" s="9" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Z10" s="9" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="X10" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="Z10" s="3" t="inlineStr"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1387,18 +1376,18 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>509.3</v>
-      </c>
-      <c r="D11" s="9" t="n">
+        <v>504.5</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1410,14 +1399,14 @@
       <c r="J11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>11</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>11.9</v>
+        <v>19.9</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>13</v>
@@ -1428,34 +1417,34 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="R11" s="9" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S11" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T11" s="9" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="U11" s="9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V11" s="9" t="n">
+      <c r="R11" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="9" t="n">
+      <c r="W11" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X11" s="9" t="n">
+      <c r="X11" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y11" s="9" t="n">
+      <c r="Y11" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="Z11" s="9" t="n">
+      <c r="Z11" s="8" t="n">
         <v>9</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1474,16 +1463,16 @@
       <c r="C12" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1495,7 +1484,7 @@
       <c r="J12" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1513,26 +1502,26 @@
       <c r="P12" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="R12" s="9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S12" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T12" s="9" t="n">
-        <v>54.2</v>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V12" s="9" t="n">
+      <c r="R12" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="V12" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>19.7</v>
+        <v>14.7</v>
       </c>
       <c r="X12" s="3" t="n">
         <v>13.1</v>
@@ -1559,35 +1548,35 @@
       <c r="C13" s="3" t="n">
         <v>357.9</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>14.1</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="3" t="n">
         <v>0.5</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>11.6</v>
+        <v>18.6</v>
       </c>
       <c r="N13" s="3" t="n">
         <v>13.6</v>
@@ -1598,34 +1587,34 @@
       <c r="P13" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="S13" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T13" s="9" t="n">
+      <c r="T13" s="8" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="U13" s="9" t="n">
+      <c r="U13" s="8" t="n">
         <v>2.1</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="9" t="n">
+      <c r="W13" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X13" s="9" t="n">
+      <c r="X13" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y13" s="9" t="n">
+      <c r="Y13" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="Z13" s="9" t="n">
+      <c r="Z13" s="8" t="n">
         <v>3.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -1644,16 +1633,16 @@
       <c r="C14" s="3" t="n">
         <v>227</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1663,13 +1652,13 @@
         <v>1.3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>16.7</v>
+        <v>8.5</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>26.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>23.2</v>
+        <v>13.3</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13</v>
@@ -1683,22 +1672,22 @@
       <c r="P14" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="S14" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="T14" s="9" t="n">
+      <c r="T14" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="U14" s="9" t="n">
+      <c r="U14" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>14.5</v>
       </c>
       <c r="W14" s="3" t="n">
@@ -1729,16 +1718,16 @@
       <c r="C15" s="3" t="n">
         <v>631</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1750,7 +1739,7 @@
       <c r="J15" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1768,34 +1757,34 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="S15" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="T15" s="9" t="n">
+      <c r="T15" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="U15" s="9" t="n">
+      <c r="U15" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="9" t="n">
+      <c r="W15" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="X15" s="9" t="n">
+      <c r="X15" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="Y15" s="9" t="n">
+      <c r="Y15" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="Z15" s="9" t="n">
+      <c r="Z15" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -1812,13 +1801,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E16" s="13" t="n">
         <v>57</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="8" t="n">
         <v>92.5</v>
       </c>
       <c r="G16" s="3" t="n">
@@ -1833,13 +1822,13 @@
       <c r="J16" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="13" t="n">
         <v>39.8</v>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="L16" s="13" t="n">
         <v>59.1</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="M16" s="13" t="n">
         <v>58.2</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1851,10 +1840,10 @@
       <c r="P16" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="R16" s="13" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1866,10 +1855,10 @@
       <c r="U16" s="3" t="n">
         <v>60.9</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>98.2</v>
       </c>
-      <c r="W16" s="10" t="n">
+      <c r="W16" s="13" t="n">
         <v>80.7</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1897,16 +1886,16 @@
       <c r="C17" s="3" t="n">
         <v>445.9</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D17" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1919,10 +1908,10 @@
         <v>29.4</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="10" t="n">
+      <c r="L17" s="13" t="n">
         <v>11.8</v>
       </c>
-      <c r="M17" s="10" t="n">
+      <c r="M17" s="13" t="n">
         <v>11.6</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1932,27 +1921,27 @@
         <v>97.8</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="10" t="n">
+      <c r="R17" s="13" t="n">
         <v>16.4</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="S17" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="T17" s="9" t="n">
+      <c r="T17" s="8" t="n">
         <v>69.7</v>
       </c>
-      <c r="U17" s="9" t="n">
+      <c r="U17" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W17" s="10" t="n">
+      <c r="W17" s="13" t="n">
         <v>16.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1962,7 +1951,7 @@
         <v>72.8</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1980,73 +1969,73 @@
       <c r="C18" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D18" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>15</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="N18" s="9" t="n">
+      <c r="N18" s="8" t="n">
         <v>16.5</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P18" s="9" t="n">
+      <c r="P18" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q18" s="9" t="n">
+      <c r="Q18" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="S18" s="8" t="n">
         <v>15.4</v>
       </c>
-      <c r="T18" s="9" t="n">
+      <c r="T18" s="8" t="n">
         <v>46.2</v>
       </c>
-      <c r="U18" s="9" t="n">
+      <c r="U18" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X18" s="9" t="n">
+      <c r="X18" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="Y18" s="9" t="n">
+      <c r="Y18" s="8" t="n">
         <v>70.8</v>
       </c>
-      <c r="Z18" s="9" t="n">
+      <c r="Z18" s="8" t="n">
         <v>7.3</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2065,16 +2054,16 @@
       <c r="C19" s="3" t="n">
         <v>531.1</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>17.4</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2086,10 +2075,10 @@
       <c r="J19" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M19" s="3" t="n">
@@ -2104,34 +2093,34 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="S19" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="T19" s="9" t="n">
+      <c r="T19" s="8" t="n">
         <v>48.5</v>
       </c>
-      <c r="U19" s="9" t="n">
+      <c r="U19" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="X19" s="9" t="n">
+      <c r="X19" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y19" s="9" t="n">
+      <c r="Y19" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="Z19" s="9" t="n">
+      <c r="Z19" s="8" t="n">
         <v>6.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2150,16 +2139,16 @@
       <c r="C20" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>28.2</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2171,10 +2160,10 @@
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2187,36 +2176,36 @@
         <v>98</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q20" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="S20" s="9" t="n">
+      <c r="S20" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="T20" s="9" t="n">
+      <c r="T20" s="8" t="n">
         <v>40.5</v>
       </c>
-      <c r="U20" s="9" t="n">
+      <c r="U20" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="X20" s="9" t="n">
+      <c r="X20" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="Y20" s="9" t="n">
+      <c r="Y20" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="Z20" s="9" t="n">
+      <c r="Z20" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2233,18 +2222,18 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>382.4</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H21" s="3" t="n">
@@ -2254,54 +2243,54 @@
         <v>2.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K21" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="9" t="n">
+      <c r="N21" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P21" s="9" t="n">
+      <c r="P21" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="S21" s="9" t="n">
+      <c r="S21" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="T21" s="9" t="n">
+      <c r="T21" s="8" t="n">
         <v>51</v>
       </c>
-      <c r="U21" s="9" t="n">
+      <c r="U21" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>17.5</v>
       </c>
-      <c r="X21" s="9" t="n">
+      <c r="X21" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="Y21" s="9" t="n">
+      <c r="Y21" s="8" t="n">
         <v>87</v>
       </c>
-      <c r="Z21" s="9" t="n">
+      <c r="Z21" s="8" t="n">
         <v>3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2318,18 +2307,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>429</v>
-      </c>
-      <c r="D22" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>13.1</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2341,52 +2330,52 @@
       <c r="J22" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>12.3</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="N22" s="9" t="n">
+      <c r="N22" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="P22" s="9" t="n">
+      <c r="P22" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>23.6</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="S22" s="9" t="n">
+      <c r="S22" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="T22" s="9" t="n">
+      <c r="T22" s="8" t="n">
         <v>49.5</v>
       </c>
-      <c r="U22" s="9" t="n">
+      <c r="U22" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>15.6</v>
       </c>
-      <c r="X22" s="9" t="n">
+      <c r="X22" s="8" t="n">
         <v>17.7</v>
       </c>
-      <c r="Y22" s="9" t="n">
+      <c r="Y22" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="Z22" s="9" t="n">
+      <c r="Z22" s="8" t="n">
         <v>9.5</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -2403,18 +2392,18 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2320.3</v>
-      </c>
-      <c r="D23" s="9" t="n">
+        <v>232</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <v>132.1</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="E23" s="13" t="n">
         <v>56.7</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="13" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2426,13 +2415,13 @@
       <c r="J23" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>67</v>
       </c>
-      <c r="M23" s="10" t="n">
+      <c r="M23" s="13" t="n">
         <v>61.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2442,12 +2431,12 @@
         <v>293</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q23" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q23" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="10" t="n">
+      <c r="R23" s="13" t="n">
         <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2459,10 +2448,10 @@
       <c r="U23" s="3" t="n">
         <v>88.5</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="10" t="n">
+      <c r="W23" s="13" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2490,16 +2479,16 @@
       <c r="C24" s="3" t="n">
         <v>464.1</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>15.1</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2512,16 +2501,16 @@
         <v>42.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="M24" s="10" t="n">
+      <c r="M24" s="13" t="n">
         <v>12.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>11.8</v>
+        <v>10.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>98.59999999999999</v>
@@ -2529,34 +2518,34 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="10" t="n">
+      <c r="R24" s="13" t="n">
         <v>17.6</v>
       </c>
-      <c r="S24" s="9" t="n">
+      <c r="S24" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T24" s="9" t="n">
+      <c r="T24" s="8" t="n">
         <v>60.5</v>
       </c>
-      <c r="U24" s="9" t="n">
+      <c r="U24" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="10" t="n">
+      <c r="W24" s="13" t="n">
         <v>17.1</v>
       </c>
-      <c r="X24" s="9" t="n">
+      <c r="X24" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="Y24" s="9" t="n">
+      <c r="Y24" s="8" t="n">
         <v>77</v>
       </c>
-      <c r="Z24" s="9" t="n">
+      <c r="Z24" s="8" t="n">
         <v>5.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2575,16 +2564,16 @@
       <c r="C25" s="3" t="n">
         <v>488.9</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2596,52 +2585,52 @@
       <c r="J25" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="9" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="M25" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N25" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="O25" s="9" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="P25" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q25" s="9" t="n">
+      <c r="K25" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N25" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O25" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="S25" s="9" t="n">
+      <c r="S25" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="T25" s="9" t="n">
+      <c r="T25" s="8" t="n">
         <v>63</v>
       </c>
-      <c r="U25" s="9" t="n">
+      <c r="U25" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="X25" s="9" t="n">
+      <c r="X25" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="Y25" s="9" t="n">
+      <c r="Y25" s="8" t="n">
         <v>66</v>
       </c>
-      <c r="Z25" s="9" t="n">
+      <c r="Z25" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -2660,16 +2649,16 @@
       <c r="C26" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>14.8</v>
       </c>
       <c r="H26" s="3" t="n">
@@ -2681,53 +2670,53 @@
       <c r="J26" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L26" s="9" t="n">
+      <c r="L26" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N26" s="9" t="n">
+      <c r="N26" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P26" s="9" t="n">
+      <c r="P26" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S26" s="9" t="n">
+      <c r="S26" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="T26" s="9" t="n">
+      <c r="T26" s="8" t="n">
         <v>74</v>
       </c>
-      <c r="U26" s="9" t="n">
+      <c r="U26" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>142.2</v>
-      </c>
-      <c r="Y26" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v>11.8</v>
+      <c r="W26" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y26" s="8" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="Z26" s="8" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2745,16 +2734,16 @@
       <c r="C27" s="3" t="n">
         <v>340.2</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D27" s="8" t="n">
         <v>25.1</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>11.1</v>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="8" t="n">
         <v>18.1</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2766,53 +2755,53 @@
       <c r="J27" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="L27" s="9" t="n">
+      <c r="L27" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="N27" s="9" t="n">
+      <c r="N27" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P27" s="9" t="n">
+      <c r="P27" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="S27" s="9" t="n">
+      <c r="S27" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="T27" s="9" t="n">
+      <c r="T27" s="8" t="n">
         <v>90.3</v>
       </c>
-      <c r="U27" s="9" t="n">
+      <c r="U27" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>1.6</v>
+      <c r="X27" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y27" s="8" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="Z27" s="8" t="n">
+        <v>0.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2830,16 +2819,16 @@
       <c r="C28" s="3" t="n">
         <v>513.3</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D28" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>15.4</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2851,53 +2840,53 @@
       <c r="J28" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="8" t="n">
         <v>13.3</v>
       </c>
-      <c r="N28" s="9" t="n">
+      <c r="N28" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="O28" s="9" t="n">
+      <c r="O28" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P28" s="9" t="n">
+      <c r="P28" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="S28" s="9" t="n">
+      <c r="S28" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="T28" s="9" t="n">
+      <c r="T28" s="8" t="n">
         <v>76.7</v>
       </c>
-      <c r="U28" s="9" t="n">
+      <c r="U28" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="W28" s="3" t="n">
+      <c r="W28" s="8" t="n">
         <v>15.5</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y28" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>1.8</v>
+      <c r="X28" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="Y28" s="8" t="n">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="Z28" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2915,17 +2904,17 @@
       <c r="C29" s="3" t="n">
         <v>593.3</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>28.8</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.2</v>
@@ -2936,52 +2925,52 @@
       <c r="J29" s="3" t="n">
         <v>6.2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L29" s="9" t="n">
+      <c r="L29" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N29" s="9" t="n">
+      <c r="N29" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="8" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="P29" s="9" t="n">
+      <c r="P29" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="R29" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S29" s="9" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="T29" s="9" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="U29" s="9" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="V29" s="9" t="n">
+      <c r="R29" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="V29" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="X29" s="9" t="n">
+      <c r="X29" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="Y29" s="9" t="n">
+      <c r="Y29" s="8" t="n">
         <v>60</v>
       </c>
-      <c r="Z29" s="9" t="n">
+      <c r="Z29" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2998,22 +2987,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2284.8</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>228.4</v>
+      </c>
+      <c r="D30" s="8" t="n">
         <v>131.2</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E30" s="8" t="n">
         <v>52.1</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="8" t="n">
         <v>91.7</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="8" t="n">
         <v>79.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>13.8</v>
@@ -3021,13 +3010,13 @@
       <c r="J30" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="K30" s="9" t="n">
+      <c r="K30" s="13" t="n">
         <v>13.5</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" s="13" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="13" t="n">
         <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3039,10 +3028,10 @@
       <c r="P30" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="13" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3054,10 +3043,10 @@
       <c r="U30" s="3" t="n">
         <v>55.4</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="10" t="n">
+      <c r="W30" s="13" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3085,16 +3074,16 @@
       <c r="C31" s="3" t="n">
         <v>457</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3107,14 +3096,14 @@
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="9" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="M31" s="9" t="n">
+      <c r="L31" s="13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M31" s="13" t="n">
         <v>11.2</v>
       </c>
-      <c r="N31" s="9" t="n">
-        <v>13.2</v>
+      <c r="N31" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>97.8</v>
@@ -3122,35 +3111,35 @@
       <c r="P31" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="13" t="n">
         <v>17.3</v>
       </c>
-      <c r="S31" s="9" t="n">
+      <c r="S31" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="T31" s="9" t="n">
+      <c r="T31" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="U31" s="9" t="n">
+      <c r="U31" s="8" t="n">
         <v>7.7</v>
       </c>
-      <c r="V31" s="9" t="n">
+      <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="10" t="n">
+      <c r="W31" s="13" t="n">
         <v>16.4</v>
       </c>
-      <c r="X31" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>730.2</v>
-      </c>
-      <c r="Z31" s="3" t="n">
-        <v>165.8</v>
+      <c r="X31" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y31" s="8" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z31" s="8" t="n">
+        <v>4.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3168,16 +3157,16 @@
       <c r="C32" s="3" t="n">
         <v>520</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3189,50 +3178,50 @@
       <c r="J32" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="9" t="n">
+      <c r="K32" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>10.2</v>
       </c>
-      <c r="N32" s="9" t="n">
+      <c r="N32" s="8" t="n">
         <v>12.4</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P32" s="9" t="n">
+      <c r="P32" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="S32" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>62.2</v>
+        <v>62.5</v>
       </c>
       <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W32" s="9" t="n">
+      <c r="W32" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="X32" s="9" t="n">
+      <c r="X32" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="Y32" s="9" t="n">
+      <c r="Y32" s="8" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="Z32" s="9" t="n">
+      <c r="Z32" s="8" t="n">
         <v>5.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -3251,16 +3240,16 @@
       <c r="C33" s="3" t="n">
         <v>349.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3272,28 +3261,28 @@
       <c r="J33" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="K33" s="9" t="n">
+      <c r="K33" s="8" t="n">
         <v>6.8</v>
       </c>
-      <c r="L33" s="9" t="n">
+      <c r="L33" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="N33" s="9" t="n">
+      <c r="N33" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P33" s="9" t="n">
+      <c r="P33" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3305,19 +3294,19 @@
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="X33" s="9" t="n">
+      <c r="X33" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="Y33" s="9" t="n">
+      <c r="Y33" s="8" t="n">
         <v>91</v>
       </c>
-      <c r="Z33" s="9" t="n">
+      <c r="Z33" s="8" t="n">
         <v>2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -3336,16 +3325,16 @@
       <c r="C34" s="3" t="n">
         <v>329.1</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>23.3</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3357,28 +3346,28 @@
       <c r="J34" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K34" s="9" t="n">
+      <c r="K34" s="8" t="n">
         <v>1.7</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="N34" s="9" t="n">
+      <c r="N34" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" s="8" t="n">
         <v>99</v>
       </c>
-      <c r="P34" s="9" t="n">
+      <c r="P34" s="8" t="n">
         <v>0.2</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3390,19 +3379,19 @@
       <c r="U34" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X34" s="9" t="n">
+      <c r="X34" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="8" t="n">
         <v>88.7</v>
       </c>
-      <c r="Z34" s="9" t="n">
+      <c r="Z34" s="8" t="n">
         <v>2.4</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -3421,16 +3410,16 @@
       <c r="C35" s="3" t="n">
         <v>506.7</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>14</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3442,52 +3431,52 @@
       <c r="J35" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K35" s="9" t="n">
+      <c r="K35" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="N35" s="9" t="n">
+      <c r="N35" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="O35" s="9" t="n">
+      <c r="O35" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P35" s="9" t="n">
+      <c r="P35" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="X35" s="9" t="n">
+      <c r="X35" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="Y35" s="9" t="n">
+      <c r="Y35" s="8" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="Z35" s="9" t="n">
+      <c r="Z35" s="8" t="n">
         <v>5.6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -3506,16 +3495,16 @@
       <c r="C36" s="3" t="n">
         <v>535.5</v>
       </c>
-      <c r="D36" s="9" t="n">
+      <c r="D36" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3527,52 +3516,52 @@
       <c r="J36" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K36" s="9" t="n">
+      <c r="K36" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N36" s="9" t="n">
+      <c r="N36" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" s="8" t="n">
         <v>99.3</v>
       </c>
-      <c r="P36" s="9" t="n">
+      <c r="P36" s="8" t="n">
         <v>0.1</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>14.6</v>
       </c>
-      <c r="X36" s="9" t="n">
+      <c r="X36" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="Y36" s="9" t="n">
+      <c r="Y36" s="8" t="n">
         <v>68.5</v>
       </c>
-      <c r="Z36" s="9" t="n">
+      <c r="Z36" s="8" t="n">
         <v>7.6</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -3591,16 +3580,16 @@
       <c r="C37" s="3" t="n">
         <v>224</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>128.5</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>60.9</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>94.7</v>
       </c>
-      <c r="G37" s="9" t="n">
+      <c r="G37" s="8" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3612,13 +3601,13 @@
       <c r="J37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="K37" s="9" t="n">
+      <c r="K37" s="8" t="n">
         <v>8.5</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="M37" s="10" t="n">
+      <c r="M37" s="13" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3628,10 +3617,10 @@
         <v>492</v>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="10" t="n">
+      <c r="Q37" s="13" t="n">
         <v>115.5</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3643,14 +3632,14 @@
       <c r="U37" s="3" t="n">
         <v>54.5</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>100.9</v>
       </c>
-      <c r="W37" s="9" t="n">
+      <c r="W37" s="8" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>82.7</v>
+        <v>84.7</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>359.5</v>
@@ -3674,23 +3663,23 @@
       <c r="C38" s="3" t="n">
         <v>448.1</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>13.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>28.1</v>
+        <v>2.8</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>22.1</v>
@@ -3698,25 +3687,25 @@
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="9" t="n">
+      <c r="L38" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="N38" s="9" t="n">
+      <c r="N38" s="8" t="n">
         <v>14.8</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P38" s="9" t="n">
+      <c r="P38" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="10" t="n">
+      <c r="Q38" s="13" t="n">
         <v>23.1</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>17.9</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3728,19 +3717,19 @@
       <c r="U38" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X38" s="9" t="n">
+      <c r="X38" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="Y38" s="9" t="n">
+      <c r="Y38" s="8" t="n">
         <v>79.8</v>
       </c>
-      <c r="Z38" s="9" t="n">
+      <c r="Z38" s="8" t="n">
         <v>4.8</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -3759,16 +3748,16 @@
       <c r="C39" s="3" t="n">
         <v>579.9</v>
       </c>
-      <c r="D39" s="9" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="8" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="H39" s="3" t="n">
@@ -3780,52 +3769,52 @@
       <c r="J39" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="9" t="n">
+      <c r="K39" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>12.7</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="N39" s="9" t="n">
+      <c r="N39" s="8" t="n">
         <v>14.5</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="O39" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P39" s="9" t="n">
+      <c r="P39" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="S39" s="9" t="n">
+      <c r="S39" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="T39" s="9" t="n">
+      <c r="T39" s="8" t="n">
         <v>59.2</v>
       </c>
-      <c r="U39" s="9" t="n">
+      <c r="U39" s="8" t="n">
         <v>14.2</v>
       </c>
-      <c r="V39" s="9" t="n">
+      <c r="V39" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="X39" s="9" t="n">
+      <c r="X39" s="8" t="n">
         <v>17.8</v>
       </c>
-      <c r="Y39" s="9" t="n">
+      <c r="Y39" s="8" t="n">
         <v>68.7</v>
       </c>
-      <c r="Z39" s="9" t="n">
+      <c r="Z39" s="8" t="n">
         <v>8.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -3844,13 +3833,13 @@
       <c r="C40" s="3" t="n">
         <v>355.7</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E40" s="9" t="n">
+      <c r="E40" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F40" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="G40" s="3" t="n">
@@ -3865,52 +3854,52 @@
       <c r="J40" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K40" s="9" t="n">
+      <c r="K40" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="N40" s="9" t="n">
+      <c r="N40" s="8" t="n">
         <v>12.5</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="O40" s="8" t="n">
         <v>98</v>
       </c>
-      <c r="P40" s="9" t="n">
+      <c r="P40" s="8" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="S40" s="9" t="n">
+      <c r="S40" s="8" t="n">
         <v>18.4</v>
       </c>
-      <c r="T40" s="9" t="n">
+      <c r="T40" s="8" t="n">
         <v>69.5</v>
       </c>
-      <c r="U40" s="9" t="n">
+      <c r="U40" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X40" s="9" t="n">
+      <c r="X40" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y40" s="9" t="n">
+      <c r="Y40" s="8" t="n">
         <v>83.3</v>
       </c>
-      <c r="Z40" s="9" t="n">
+      <c r="Z40" s="8" t="n">
         <v>3.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -3929,16 +3918,16 @@
       <c r="C41" s="3" t="n">
         <v>451.2</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>28.4</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3950,52 +3939,52 @@
       <c r="J41" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="K41" s="9" t="n">
+      <c r="K41" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="9" t="n">
+      <c r="L41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="N41" s="9" t="n">
+      <c r="N41" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="8" t="n">
         <v>98.7</v>
       </c>
-      <c r="P41" s="9" t="n">
+      <c r="P41" s="8" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>23.4</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="S41" s="9" t="n">
+      <c r="S41" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="T41" s="9" t="n">
+      <c r="T41" s="8" t="n">
         <v>69</v>
       </c>
-      <c r="U41" s="9" t="n">
+      <c r="U41" s="8" t="n">
         <v>8.9</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>18.5</v>
       </c>
-      <c r="X41" s="9" t="n">
+      <c r="X41" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="Y41" s="9" t="n">
+      <c r="Y41" s="8" t="n">
         <v>80.5</v>
       </c>
-      <c r="Z41" s="9" t="n">
+      <c r="Z41" s="8" t="n">
         <v>5.1</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -4014,16 +4003,16 @@
       <c r="C42" s="3" t="n">
         <v>524.4</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>11.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -4035,43 +4024,43 @@
       <c r="J42" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="K42" s="9" t="n">
+      <c r="K42" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="N42" s="9" t="n">
+      <c r="N42" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="8" t="n">
         <v>96.09999999999999</v>
       </c>
-      <c r="P42" s="9" t="n">
+      <c r="P42" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="S42" s="9" t="n">
+      <c r="S42" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="T42" s="9" t="n">
+      <c r="T42" s="8" t="n">
         <v>57.7</v>
       </c>
-      <c r="U42" s="9" t="n">
+      <c r="U42" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W42" s="9" t="inlineStr"/>
+      <c r="W42" s="8" t="inlineStr"/>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="inlineStr"/>
       <c r="Z42" s="3" t="inlineStr"/>
@@ -4089,28 +4078,28 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr"/>
-      <c r="F43" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr"/>
+      <c r="K43" s="8" t="inlineStr"/>
+      <c r="L43" s="8" t="inlineStr"/>
+      <c r="M43" s="8" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="9" t="inlineStr"/>
-      <c r="R43" s="20" t="inlineStr"/>
+      <c r="Q43" s="8" t="inlineStr"/>
+      <c r="R43" s="19" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="9" t="inlineStr"/>
-      <c r="W43" s="9" t="inlineStr"/>
+      <c r="V43" s="8" t="inlineStr"/>
+      <c r="W43" s="8" t="inlineStr"/>
       <c r="X43" s="3" t="inlineStr"/>
       <c r="Y43" s="3" t="inlineStr"/>
       <c r="Z43" s="3" t="inlineStr"/>
@@ -4128,28 +4117,28 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="9" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="8" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="20" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="19" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4167,22 +4156,22 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1911.2</v>
-      </c>
-      <c r="D45" s="9" t="n">
+        <v>191.1</v>
+      </c>
+      <c r="D45" s="8" t="n">
         <v>109.7</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="13" t="n">
         <v>41.5</v>
       </c>
-      <c r="F45" s="9" t="n">
+      <c r="F45" s="8" t="n">
         <v>75.59999999999999</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>67.90000000000001</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>14.4</v>
@@ -4190,13 +4179,13 @@
       <c r="J45" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>44</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="8" t="n">
         <v>42.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4206,12 +4195,12 @@
         <v>388</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="10" t="n">
+      <c r="R45" s="13" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4223,14 +4212,14 @@
       <c r="U45" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="V45" s="9" t="n">
+      <c r="V45" s="8" t="n">
         <v>85.40000000000001</v>
       </c>
-      <c r="W45" s="9" t="n">
+      <c r="W45" s="8" t="n">
         <v>51</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>66.8</v>
+        <v>60.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>263</v>
@@ -4254,16 +4243,16 @@
       <c r="C46" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>27.4</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>16.9</v>
       </c>
       <c r="H46" s="3" t="n">
@@ -4273,18 +4262,18 @@
         <v>36.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="K46" s="8" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="9" t="n">
+      <c r="N46" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4293,34 +4282,34 @@
       <c r="P46" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="10" t="n">
+      <c r="R46" s="13" t="n">
         <v>17.7</v>
       </c>
-      <c r="S46" s="9" t="n">
+      <c r="S46" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="T46" s="9" t="n">
+      <c r="T46" s="8" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="U46" s="9" t="n">
+      <c r="U46" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X46" s="9" t="n">
+      <c r="X46" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="Y46" s="9" t="n">
+      <c r="Y46" s="8" t="n">
         <v>75.5</v>
       </c>
-      <c r="Z46" s="9" t="n">
+      <c r="Z46" s="8" t="n">
         <v>6.2</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -173,7 +173,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -820,19 +826,19 @@
         <v>9.1</v>
       </c>
       <c r="N4" s="8" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="O4" s="8" t="n">
-        <v>95.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="P4" s="8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="R4" s="8" t="n">
-        <v>12.1</v>
+        <v>16.8</v>
       </c>
       <c r="S4" s="8" t="n">
         <v>14.1</v>
@@ -905,13 +911,13 @@
         <v>11.4</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>94.2</v>
+        <v>90</v>
       </c>
       <c r="P5" s="8" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="8" t="n">
         <v>19.6</v>
@@ -920,13 +926,13 @@
         <v>18.6</v>
       </c>
       <c r="S5" s="8" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="T5" s="8" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="V5" s="8" t="n">
         <v>19.5</v>
@@ -993,10 +999,10 @@
         <v>13.1</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
         <v>15.4</v>
@@ -1005,22 +1011,22 @@
         <v>14.7</v>
       </c>
       <c r="S6" s="8" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="T6" s="8" t="n">
-        <v>95.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="V6" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="W6" s="8" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="Y6" s="8" t="n">
         <v>95</v>
@@ -1075,13 +1081,13 @@
         <v>13.1</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>19.3</v>
@@ -1090,27 +1096,27 @@
         <v>16.8</v>
       </c>
       <c r="S7" s="8" t="n">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="8" t="n">
-        <v>85.40000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="V7" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z7" s="3" t="n">
+      <c r="X7" s="8" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y7" s="8" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="Z7" s="8" t="n">
         <v>4.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1160,13 +1166,13 @@
         <v>10.6</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>98.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q8" s="8" t="n">
         <v>21.4</v>
@@ -1175,27 +1181,27 @@
         <v>18.4</v>
       </c>
       <c r="S8" s="8" t="n">
-        <v>21.2</v>
+        <v>19.1</v>
       </c>
       <c r="T8" s="8" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="V8" s="8" t="n">
         <v>18.7</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="X8" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Y8" s="3" t="n">
-        <v>87</v>
-      </c>
-      <c r="Z8" s="3" t="n">
+      <c r="X8" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y8" s="8" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="Z8" s="8" t="n">
         <v>2.6</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1254,7 +1260,7 @@
       <c r="Q9" s="8" t="n">
         <v>101.5</v>
       </c>
-      <c r="R9" s="13" t="n">
+      <c r="R9" s="8" t="n">
         <v>85.3</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1326,28 +1332,28 @@
         <v>11</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>98</v>
+        <v>96.5</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="R10" s="13" t="n">
+      <c r="R10" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="S10" s="8" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="T10" s="8" t="n">
-        <v>81.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>19</v>
@@ -1421,7 +1427,7 @@
         <v>26.3</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>12.4</v>
+        <v>17.1</v>
       </c>
       <c r="S11" s="8" t="n">
         <v>14.4</v>
@@ -1435,8 +1441,8 @@
       <c r="V11" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>15.5</v>
+      <c r="W11" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="X11" s="8" t="n">
         <v>17.6</v>
@@ -1506,7 +1512,7 @@
         <v>25.4</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>9.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="S12" s="8" t="n">
         <v>12.1</v>
@@ -1594,19 +1600,19 @@
         <v>17.3</v>
       </c>
       <c r="S13" s="8" t="n">
-        <v>19.7</v>
+        <v>18.6</v>
       </c>
       <c r="T13" s="8" t="n">
-        <v>90.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="V13" s="8" t="n">
         <v>19.6</v>
       </c>
-      <c r="W13" s="8" t="n">
-        <v>16.8</v>
+      <c r="W13" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="X13" s="8" t="n">
         <v>19.1</v>
@@ -1679,13 +1685,13 @@
         <v>14.7</v>
       </c>
       <c r="S14" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="T14" s="8" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="V14" s="8" t="n">
         <v>14.5</v>
@@ -1761,7 +1767,7 @@
         <v>25.5</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>13.7</v>
+        <v>17.6</v>
       </c>
       <c r="S15" s="8" t="n">
         <v>15.7</v>
@@ -1775,8 +1781,8 @@
       <c r="V15" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="W15" s="8" t="n">
-        <v>14.4</v>
+      <c r="W15" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="X15" s="8" t="n">
         <v>16.4</v>
@@ -1843,7 +1849,7 @@
       <c r="Q16" s="8" t="n">
         <v>111</v>
       </c>
-      <c r="R16" s="13" t="n">
+      <c r="R16" s="8" t="n">
         <v>82.2</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1926,17 +1932,17 @@
       <c r="Q17" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="R17" s="13" t="n">
+      <c r="R17" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="S17" s="8" t="n">
-        <v>18.6</v>
+        <v>14.7</v>
       </c>
       <c r="T17" s="8" t="n">
-        <v>69.7</v>
+        <v>54.9</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>8.1</v>
+        <v>12.1</v>
       </c>
       <c r="V17" s="8" t="n">
         <v>19.6</v>
@@ -1996,8 +2002,8 @@
       <c r="L18" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>14.5</v>
+      <c r="M18" s="10" t="n">
+        <v>1.6</v>
       </c>
       <c r="N18" s="8" t="n">
         <v>16.5</v>
@@ -2012,7 +2018,7 @@
         <v>25.8</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>13.4</v>
+        <v>17.5</v>
       </c>
       <c r="S18" s="8" t="n">
         <v>15.4</v>
@@ -2030,13 +2036,13 @@
         <v>15.5</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>17.6</v>
+        <v>13.9</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>70.8</v>
+        <v>55.7</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2081,23 +2087,23 @@
       <c r="L19" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="N19" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P19" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q19" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>14.2</v>
+        <v>18</v>
       </c>
       <c r="S19" s="8" t="n">
         <v>16.2</v>
@@ -2112,7 +2118,7 @@
         <v>21.2</v>
       </c>
       <c r="W19" s="8" t="n">
-        <v>16.4</v>
+        <v>17.8</v>
       </c>
       <c r="X19" s="8" t="n">
         <v>18.6</v>
@@ -2166,23 +2172,23 @@
       <c r="L20" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P20" s="3" t="n">
+      <c r="N20" s="8" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P20" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="Q20" s="8" t="n">
         <v>28</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>13.3</v>
+        <v>18.1</v>
       </c>
       <c r="S20" s="8" t="n">
         <v>15.3</v>
@@ -2200,13 +2206,13 @@
         <v>18.4</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>21.2</v>
+        <v>18.6</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>79.09999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2251,8 +2257,8 @@
       <c r="L21" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>17.4</v>
+      <c r="M21" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="N21" s="8" t="n">
         <v>19.9</v>
@@ -2267,7 +2273,7 @@
         <v>25.6</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>14.8</v>
+        <v>18.2</v>
       </c>
       <c r="S21" s="8" t="n">
         <v>16.8</v>
@@ -2282,7 +2288,7 @@
         <v>19.8</v>
       </c>
       <c r="W21" s="8" t="n">
-        <v>17.5</v>
+        <v>18.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>20</v>
@@ -2352,7 +2358,7 @@
         <v>23.6</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>12.4</v>
+        <v>16.2</v>
       </c>
       <c r="S22" s="8" t="n">
         <v>14.4</v>
@@ -2370,13 +2376,13 @@
         <v>15.6</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>17.7</v>
+        <v>13</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>65</v>
+        <v>47.8</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>9.5</v>
+        <v>14.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2436,7 +2442,7 @@
       <c r="Q23" s="8" t="n">
         <v>128.9</v>
       </c>
-      <c r="R23" s="13" t="n">
+      <c r="R23" s="8" t="n">
         <v>88</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2451,7 +2457,7 @@
       <c r="V23" s="8" t="n">
         <v>106.7</v>
       </c>
-      <c r="W23" s="13" t="n">
+      <c r="W23" s="8" t="n">
         <v>85.5</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2509,44 +2515,44 @@
       <c r="M24" s="13" t="n">
         <v>12.4</v>
       </c>
-      <c r="N24" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="P24" s="3" t="n">
+      <c r="N24" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="P24" s="8" t="n">
         <v>0.3</v>
       </c>
       <c r="Q24" s="8" t="n">
         <v>25.8</v>
       </c>
-      <c r="R24" s="13" t="n">
+      <c r="R24" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="S24" s="8" t="n">
-        <v>20.1</v>
+        <v>14.5</v>
       </c>
       <c r="T24" s="8" t="n">
-        <v>60.5</v>
+        <v>43.7</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>13.1</v>
+        <v>18.7</v>
       </c>
       <c r="V24" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="W24" s="13" t="n">
+      <c r="W24" s="8" t="n">
         <v>17.1</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>19.5</v>
+        <v>16.6</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>77</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>5.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2592,7 +2598,7 @@
         <v>17</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>16.7</v>
+        <v>9.9</v>
       </c>
       <c r="N25" s="8" t="n">
         <v>19</v>
@@ -2610,19 +2616,19 @@
         <v>17.2</v>
       </c>
       <c r="S25" s="8" t="n">
-        <v>19.6</v>
+        <v>14.5</v>
       </c>
       <c r="T25" s="8" t="n">
-        <v>63</v>
+        <v>46.6</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>11.5</v>
+        <v>16.6</v>
       </c>
       <c r="V25" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="W25" s="8" t="n">
-        <v>14.8</v>
+        <v>16.9</v>
       </c>
       <c r="X25" s="8" t="n">
         <v>16.8</v>
@@ -2680,13 +2686,13 @@
         <v>10.2</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>98.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="P26" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q26" s="8" t="n">
         <v>21</v>
@@ -2695,13 +2701,13 @@
         <v>16.2</v>
       </c>
       <c r="S26" s="8" t="n">
-        <v>18.4</v>
+        <v>15.1</v>
       </c>
       <c r="T26" s="8" t="n">
-        <v>74</v>
+        <v>60.9</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>6.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="V26" s="8" t="n">
         <v>21.6</v>
@@ -2710,13 +2716,13 @@
         <v>15.5</v>
       </c>
       <c r="X26" s="8" t="n">
-        <v>17.6</v>
+        <v>13.4</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>68.2</v>
+        <v>52.1</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>8.199999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2765,13 +2771,13 @@
         <v>12.2</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P27" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q27" s="8" t="n">
         <v>17.6</v>
@@ -2780,13 +2786,13 @@
         <v>16</v>
       </c>
       <c r="S27" s="8" t="n">
-        <v>18.2</v>
+        <v>17.1</v>
       </c>
       <c r="T27" s="8" t="n">
-        <v>90.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="V27" s="8" t="n">
         <v>17.4</v>
@@ -2795,13 +2801,13 @@
         <v>16.7</v>
       </c>
       <c r="X27" s="8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>95.7</v>
+        <v>93.3</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2850,13 +2856,13 @@
         <v>13.3</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P28" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q28" s="8" t="n">
         <v>22.9</v>
@@ -2865,13 +2871,13 @@
         <v>18.6</v>
       </c>
       <c r="S28" s="8" t="n">
-        <v>21.4</v>
+        <v>18.5</v>
       </c>
       <c r="T28" s="8" t="n">
-        <v>76.7</v>
+        <v>66.2</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>6.5</v>
+        <v>9.4</v>
       </c>
       <c r="V28" s="8" t="n">
         <v>16.4</v>
@@ -2880,13 +2886,13 @@
         <v>15.5</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>17.6</v>
+        <v>17</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>94.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z28" s="8" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2935,19 +2941,19 @@
         <v>10.5</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>97.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="P29" s="8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q29" s="8" t="n">
         <v>27</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>15</v>
+        <v>18.7</v>
       </c>
       <c r="S29" s="8" t="n">
         <v>17</v>
@@ -2962,7 +2968,7 @@
         <v>22.8</v>
       </c>
       <c r="W29" s="8" t="n">
-        <v>14.7</v>
+        <v>17.3</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>16.7</v>
@@ -3016,7 +3022,7 @@
       <c r="L30" s="13" t="n">
         <v>57.2</v>
       </c>
-      <c r="M30" s="13" t="n">
+      <c r="M30" s="8" t="n">
         <v>56.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3031,7 +3037,7 @@
       <c r="Q30" s="8" t="n">
         <v>113.2</v>
       </c>
-      <c r="R30" s="13" t="n">
+      <c r="R30" s="8" t="n">
         <v>86.7</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3046,7 +3052,7 @@
       <c r="V30" s="8" t="n">
         <v>99.5</v>
       </c>
-      <c r="W30" s="13" t="n">
+      <c r="W30" s="8" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3099,7 +3105,7 @@
       <c r="L31" s="13" t="n">
         <v>12.8</v>
       </c>
-      <c r="M31" s="13" t="n">
+      <c r="M31" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3114,32 +3120,32 @@
       <c r="Q31" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="R31" s="13" t="n">
+      <c r="R31" s="8" t="n">
         <v>17.3</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>19.7</v>
+        <v>16.1</v>
       </c>
       <c r="T31" s="8" t="n">
-        <v>72</v>
+        <v>58.8</v>
       </c>
       <c r="U31" s="8" t="n">
-        <v>7.7</v>
+        <v>11.3</v>
       </c>
       <c r="V31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="W31" s="13" t="n">
+      <c r="W31" s="8" t="n">
         <v>16.4</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>18.6</v>
+        <v>16.3</v>
       </c>
       <c r="Y31" s="8" t="n">
-        <v>80.3</v>
+        <v>70</v>
       </c>
       <c r="Z31" s="8" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3188,13 +3194,13 @@
         <v>10.2</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="O32" s="8" t="n">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P32" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>21.1</v>
@@ -3216,13 +3222,13 @@
         <v>17.6</v>
       </c>
       <c r="X32" s="8" t="n">
-        <v>20.1</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" s="8" t="n">
-        <v>78.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="Z32" s="8" t="n">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3271,13 +3277,13 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="O33" s="8" t="n">
-        <v>98.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>20.3</v>
@@ -3301,13 +3307,13 @@
         <v>17.9</v>
       </c>
       <c r="X33" s="8" t="n">
-        <v>20.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y33" s="8" t="n">
-        <v>91</v>
+        <v>86.5</v>
       </c>
       <c r="Z33" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3353,7 +3359,7 @@
         <v>16</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="N34" s="8" t="n">
         <v>17.8</v>
@@ -3386,13 +3392,13 @@
         <v>16.8</v>
       </c>
       <c r="X34" s="8" t="n">
-        <v>19.1</v>
+        <v>17.8</v>
       </c>
       <c r="Y34" s="8" t="n">
-        <v>88.7</v>
+        <v>82.7</v>
       </c>
       <c r="Z34" s="8" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3441,13 +3447,13 @@
         <v>12.9</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="O35" s="8" t="n">
-        <v>99.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>23.8</v>
@@ -3471,13 +3477,13 @@
         <v>16.7</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>19</v>
+        <v>16.2</v>
       </c>
       <c r="Y35" s="8" t="n">
-        <v>77.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="Z35" s="8" t="n">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3526,13 +3532,13 @@
         <v>10.5</v>
       </c>
       <c r="N36" s="8" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="O36" s="8" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>23.5</v>
@@ -3556,13 +3562,13 @@
         <v>14.6</v>
       </c>
       <c r="X36" s="8" t="n">
-        <v>16.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" s="8" t="n">
-        <v>68.5</v>
+        <v>51.7</v>
       </c>
       <c r="Z36" s="8" t="n">
-        <v>7.6</v>
+        <v>11.7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3607,7 +3613,7 @@
       <c r="L37" s="8" t="n">
         <v>65</v>
       </c>
-      <c r="M37" s="13" t="n">
+      <c r="M37" s="8" t="n">
         <v>64.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3694,13 +3700,13 @@
         <v>12.8</v>
       </c>
       <c r="N38" s="8" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="O38" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q38" s="13" t="n">
         <v>23.1</v>
@@ -3724,13 +3730,13 @@
         <v>16.6</v>
       </c>
       <c r="X38" s="8" t="n">
-        <v>18.9</v>
+        <v>16.4</v>
       </c>
       <c r="Y38" s="8" t="n">
-        <v>79.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Z38" s="8" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3779,13 +3785,13 @@
         <v>12.5</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="O39" s="8" t="n">
-        <v>98.7</v>
+        <v>97.8</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q39" s="8" t="n">
         <v>26.6</v>
@@ -3794,13 +3800,13 @@
         <v>18</v>
       </c>
       <c r="S39" s="8" t="n">
-        <v>20.6</v>
+        <v>14.8</v>
       </c>
       <c r="T39" s="8" t="n">
-        <v>59.2</v>
+        <v>42.4</v>
       </c>
       <c r="U39" s="8" t="n">
-        <v>14.2</v>
+        <v>20.1</v>
       </c>
       <c r="V39" s="8" t="n">
         <v>21.7</v>
@@ -3809,13 +3815,13 @@
         <v>15.7</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>17.8</v>
+        <v>13.7</v>
       </c>
       <c r="Y39" s="8" t="n">
-        <v>68.7</v>
+        <v>52.9</v>
       </c>
       <c r="Z39" s="8" t="n">
-        <v>8.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3864,19 +3870,19 @@
         <v>10.3</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="O40" s="8" t="n">
-        <v>98</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" s="8" t="n">
         <v>22</v>
       </c>
       <c r="R40" s="8" t="n">
-        <v>16.2</v>
+        <v>18</v>
       </c>
       <c r="S40" s="8" t="n">
         <v>18.4</v>
@@ -3894,13 +3900,13 @@
         <v>16.8</v>
       </c>
       <c r="X40" s="8" t="n">
-        <v>19.1</v>
+        <v>17.1</v>
       </c>
       <c r="Y40" s="8" t="n">
-        <v>83.3</v>
+        <v>74.7</v>
       </c>
       <c r="Z40" s="8" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3949,13 +3955,13 @@
         <v>8.6</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="O41" s="8" t="n">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q41" s="8" t="n">
         <v>23.4</v>
@@ -3964,13 +3970,13 @@
         <v>17.4</v>
       </c>
       <c r="S41" s="8" t="n">
-        <v>19.9</v>
+        <v>15.8</v>
       </c>
       <c r="T41" s="8" t="n">
-        <v>69</v>
+        <v>54.8</v>
       </c>
       <c r="U41" s="8" t="n">
-        <v>8.9</v>
+        <v>13</v>
       </c>
       <c r="V41" s="8" t="n">
         <v>22</v>
@@ -3979,13 +3985,13 @@
         <v>18.5</v>
       </c>
       <c r="X41" s="8" t="n">
-        <v>21.3</v>
+        <v>18.9</v>
       </c>
       <c r="Y41" s="8" t="n">
-        <v>80.5</v>
+        <v>71.5</v>
       </c>
       <c r="Z41" s="8" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4034,13 +4040,13 @@
         <v>11.3</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="O42" s="8" t="n">
-        <v>96.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="Q42" s="8" t="n">
         <v>26.6</v>
@@ -4049,13 +4055,13 @@
         <v>17.6</v>
       </c>
       <c r="S42" s="8" t="n">
-        <v>20.1</v>
+        <v>14</v>
       </c>
       <c r="T42" s="8" t="n">
-        <v>57.7</v>
+        <v>40.1</v>
       </c>
       <c r="U42" s="8" t="n">
-        <v>14.7</v>
+        <v>20.9</v>
       </c>
       <c r="V42" s="8" t="n">
         <v>22</v>
@@ -4094,7 +4100,7 @@
       <c r="O43" s="3" t="inlineStr"/>
       <c r="P43" s="3" t="inlineStr"/>
       <c r="Q43" s="8" t="inlineStr"/>
-      <c r="R43" s="19" t="inlineStr"/>
+      <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="3" t="inlineStr"/>
       <c r="T43" s="3" t="inlineStr"/>
       <c r="U43" s="3" t="inlineStr"/>
@@ -4133,7 +4139,7 @@
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="8" t="inlineStr"/>
-      <c r="R44" s="19" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
@@ -4200,7 +4206,7 @@
       <c r="Q45" s="8" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="R45" s="13" t="n">
+      <c r="R45" s="8" t="n">
         <v>71</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4273,7 +4279,7 @@
       <c r="M46" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="N46" s="8" t="n">
+      <c r="N46" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="O46" s="3" t="n">
@@ -4285,17 +4291,17 @@
       <c r="Q46" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R46" s="13" t="n">
+      <c r="R46" s="8" t="n">
         <v>17.7</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>20.2</v>
+        <v>15.5</v>
       </c>
       <c r="T46" s="8" t="n">
-        <v>65.09999999999999</v>
+        <v>49.7</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>10.9</v>
+        <v>15.6</v>
       </c>
       <c r="V46" s="8" t="n">
         <v>21.3</v>
@@ -4304,13 +4310,13 @@
         <v>16.8</v>
       </c>
       <c r="X46" s="8" t="n">
-        <v>19.1</v>
+        <v>16.1</v>
       </c>
       <c r="Y46" s="8" t="n">
-        <v>75.5</v>
+        <v>63.4</v>
       </c>
       <c r="Z46" s="8" t="n">
-        <v>6.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/702/702_196402_SF.JPG_post_QA_QC.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1230,7 +1230,7 @@
       <c r="J9" s="3" t="n">
         <v>13.3</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="16" t="n">
         <v>7.7</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1808,7 +1808,7 @@
       <c r="J16" s="3" t="n">
         <v>139.8</v>
       </c>
-      <c r="K16" s="3" t="n"/>
+      <c r="K16" s="13" t="n"/>
       <c r="L16" s="3" t="n">
         <v>59.9</v>
       </c>
@@ -1951,7 +1951,7 @@
       <c r="C18" s="3" t="n">
         <v>455.6</v>
       </c>
-      <c r="D18" s="13" t="n"/>
+      <c r="D18" s="14" t="n"/>
       <c r="E18" s="12" t="n">
         <v>0.1</v>
       </c>
@@ -2138,7 +2138,7 @@
       <c r="J20" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="K20" s="3" t="n"/>
+      <c r="K20" s="14" t="n"/>
       <c r="L20" s="3" t="n">
         <v>0.2</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="D22" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E22" s="13" t="n"/>
+      <c r="E22" s="14" t="n"/>
       <c r="F22" s="12" t="n">
         <v>81.7</v>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="J23" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2628,7 +2628,7 @@
       <c r="J26" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="K26" s="3" t="n"/>
+      <c r="K26" s="14" t="n"/>
       <c r="L26" s="3" t="n">
         <v>10.4</v>
       </c>
@@ -2962,7 +2962,7 @@
       <c r="J30" s="3" t="n">
         <v>119.5</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="16" t="n">
         <v>13.5</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3549,7 +3549,7 @@
       <c r="J37" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="13" t="n"/>
       <c r="L37" s="3" t="n">
         <v>10.6</v>
       </c>
@@ -3798,7 +3798,7 @@
       <c r="J40" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K40" s="3" t="n"/>
+      <c r="K40" s="14" t="n"/>
       <c r="L40" s="3" t="n">
         <v>12.7</v>
       </c>
@@ -4111,8 +4111,8 @@
       <c r="D44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="13" t="n"/>
+      <c r="E44" s="14" t="n"/>
+      <c r="F44" s="14" t="n"/>
       <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n">
         <v>0.1</v>
@@ -4194,7 +4194,7 @@
       <c r="J45" s="3" t="n">
         <v>221.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="16" t="n">
         <v>1.1</v>
       </c>
       <c r="L45" s="3" t="n"/>
@@ -4250,8 +4250,8 @@
       <c r="C46" s="3" t="n">
         <v>477.8</v>
       </c>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="13" t="n"/>
       <c r="F46" s="16" t="n">
         <v>18.9</v>
       </c>
